--- a/output/企業リスト_作業中.xlsx
+++ b/output/企業リスト_作業中.xlsx
@@ -122,7 +122,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -145,6 +145,7 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -4496,17 +4497,22 @@
       </c>
     </row>
     <row r="39" ht="12.5" customHeight="1">
-      <c r="A39" s="1" t="inlineStr">
+      <c r="A39" s="13" t="inlineStr">
         <is>
           <t>JA帯広かわにし</t>
         </is>
       </c>
-      <c r="C39" s="1" t="inlineStr">
-        <is>
-          <t>帯広市</t>
-        </is>
-      </c>
-      <c r="D39" s="1" t="inlineStr">
+      <c r="B39" s="12" t="inlineStr">
+        <is>
+          <t>https://www.jaobihirokawanisi.or.jp/</t>
+        </is>
+      </c>
+      <c r="C39" s="13" t="inlineStr">
+        <is>
+          <t>北海道帯広市川西町西2線61番地の1 (〒089-1198)</t>
+        </is>
+      </c>
+      <c r="D39" s="13" t="inlineStr">
         <is>
           <t>0155-59-2111</t>
         </is>
@@ -4581,19 +4587,20 @@
       </c>
     </row>
     <row r="40" ht="12.5" customHeight="1">
-      <c r="A40" s="1" t="inlineStr">
-        <is>
-          <t>JAおびひろ</t>
-        </is>
-      </c>
-      <c r="C40" s="1" t="inlineStr">
-        <is>
-          <t>帯広市</t>
-        </is>
-      </c>
-      <c r="D40" s="1" t="inlineStr">
-        <is>
-          <t>0155-24-3161</t>
+      <c r="A40" s="13" t="inlineStr">
+        <is>
+          <t>JAおびひろ ※2003年JA帯広かわにしへ合併・現存せず</t>
+        </is>
+      </c>
+      <c r="B40" s="14" t="inlineStr"/>
+      <c r="C40" s="13" t="inlineStr">
+        <is>
+          <t>※旧帯広市農協はJA帯広かわにしに統合済み (Row 39参照)</t>
+        </is>
+      </c>
+      <c r="D40" s="13" t="inlineStr">
+        <is>
+          <t>※存続団体: JA帯広かわにし 0155-59-2111</t>
         </is>
       </c>
       <c r="E40" s="1" t="inlineStr">
@@ -4666,19 +4673,24 @@
       </c>
     </row>
     <row r="41" ht="12.5" customHeight="1">
-      <c r="A41" s="1" t="inlineStr">
+      <c r="A41" s="13" t="inlineStr">
         <is>
           <t>JAおとふけ</t>
         </is>
       </c>
-      <c r="C41" s="1" t="inlineStr">
-        <is>
-          <t>音更町</t>
-        </is>
-      </c>
-      <c r="D41" s="1" t="inlineStr">
-        <is>
-          <t>0155-42-8721</t>
+      <c r="B41" s="12" t="inlineStr">
+        <is>
+          <t>https://www.ja-otofuke.jp/</t>
+        </is>
+      </c>
+      <c r="C41" s="13" t="inlineStr">
+        <is>
+          <t>北海道河東郡音更町大通5丁目1番地 (〒080-0101) ※2024/7移転</t>
+        </is>
+      </c>
+      <c r="D41" s="13" t="inlineStr">
+        <is>
+          <t>0155-42-8725</t>
         </is>
       </c>
       <c r="E41" s="1" t="inlineStr">
@@ -4751,17 +4763,22 @@
       </c>
     </row>
     <row r="42" ht="12.5" customHeight="1">
-      <c r="A42" s="1" t="inlineStr">
+      <c r="A42" s="13" t="inlineStr">
         <is>
           <t>JA木野</t>
         </is>
       </c>
-      <c r="C42" s="1" t="inlineStr">
-        <is>
-          <t>音更町</t>
-        </is>
-      </c>
-      <c r="D42" s="1" t="inlineStr">
+      <c r="B42" s="12" t="inlineStr">
+        <is>
+          <t>https://ja-kino.com/</t>
+        </is>
+      </c>
+      <c r="C42" s="13" t="inlineStr">
+        <is>
+          <t>北海道河東郡音更町木野大通西7-1</t>
+        </is>
+      </c>
+      <c r="D42" s="13" t="inlineStr">
         <is>
           <t>0155-31-2143</t>
         </is>
@@ -4836,17 +4853,22 @@
       </c>
     </row>
     <row r="43" ht="12.5" customHeight="1">
-      <c r="A43" s="1" t="inlineStr">
+      <c r="A43" s="13" t="inlineStr">
         <is>
           <t>JA士幌町</t>
         </is>
       </c>
-      <c r="C43" s="1" t="inlineStr">
-        <is>
-          <t>士幌町</t>
-        </is>
-      </c>
-      <c r="D43" s="1" t="inlineStr">
+      <c r="B43" s="12" t="inlineStr">
+        <is>
+          <t>https://www.ja-shihoro.or.jp/</t>
+        </is>
+      </c>
+      <c r="C43" s="13" t="inlineStr">
+        <is>
+          <t>北海道河東郡士幌町字士幌西2線159番地</t>
+        </is>
+      </c>
+      <c r="D43" s="13" t="inlineStr">
         <is>
           <t>01564-5-2311</t>
         </is>
@@ -4921,19 +4943,24 @@
       </c>
     </row>
     <row r="44" ht="12.5" customHeight="1">
-      <c r="A44" s="1" t="inlineStr">
+      <c r="A44" s="13" t="inlineStr">
         <is>
           <t>JA上士幌町</t>
         </is>
       </c>
-      <c r="C44" s="1" t="inlineStr">
-        <is>
-          <t>上士幌町</t>
-        </is>
-      </c>
-      <c r="D44" s="1" t="inlineStr">
-        <is>
-          <t>01564-2-2111</t>
+      <c r="B44" s="12" t="inlineStr">
+        <is>
+          <t>https://ja-kamishihoro.or.jp/</t>
+        </is>
+      </c>
+      <c r="C44" s="13" t="inlineStr">
+        <is>
+          <t>北海道河東郡上士幌町字上士幌東2線238 (〒080-1493)</t>
+        </is>
+      </c>
+      <c r="D44" s="13" t="inlineStr">
+        <is>
+          <t>01564-2-2131</t>
         </is>
       </c>
       <c r="E44" s="1" t="inlineStr">
@@ -5006,17 +5033,22 @@
       </c>
     </row>
     <row r="45" ht="12.5" customHeight="1">
-      <c r="A45" s="1" t="inlineStr">
+      <c r="A45" s="13" t="inlineStr">
         <is>
           <t>JA鹿追町</t>
         </is>
       </c>
-      <c r="C45" s="1" t="inlineStr">
-        <is>
-          <t>鹿追町</t>
-        </is>
-      </c>
-      <c r="D45" s="1" t="inlineStr">
+      <c r="B45" s="12" t="inlineStr">
+        <is>
+          <t>https://www.ja-shikaoi.com/</t>
+        </is>
+      </c>
+      <c r="C45" s="13" t="inlineStr">
+        <is>
+          <t>北海道河東郡鹿追町新町4丁目51番地 (〒081-0293)</t>
+        </is>
+      </c>
+      <c r="D45" s="13" t="inlineStr">
         <is>
           <t>0156-66-2131</t>
         </is>
@@ -5091,19 +5123,24 @@
       </c>
     </row>
     <row r="46" ht="12.5" customHeight="1">
-      <c r="A46" s="1" t="inlineStr">
+      <c r="A46" s="13" t="inlineStr">
         <is>
           <t>JA新得町</t>
         </is>
       </c>
-      <c r="C46" s="1" t="inlineStr">
-        <is>
-          <t>新得町</t>
-        </is>
-      </c>
-      <c r="D46" s="1" t="inlineStr">
-        <is>
-          <t>0156-64-5821</t>
+      <c r="B46" s="12" t="inlineStr">
+        <is>
+          <t>https://www.ja-shintoku.or.jp/</t>
+        </is>
+      </c>
+      <c r="C46" s="13" t="inlineStr">
+        <is>
+          <t>北海道上川郡新得町1条南3丁目1</t>
+        </is>
+      </c>
+      <c r="D46" s="13" t="inlineStr">
+        <is>
+          <t>0156-64-5021</t>
         </is>
       </c>
       <c r="E46" s="1" t="inlineStr">
@@ -5176,19 +5213,24 @@
       </c>
     </row>
     <row r="47" ht="12.5" customHeight="1">
-      <c r="A47" s="1" t="inlineStr">
+      <c r="A47" s="13" t="inlineStr">
         <is>
           <t>JA阿寒</t>
         </is>
       </c>
-      <c r="C47" s="1" t="inlineStr">
-        <is>
-          <t>釧路市</t>
-        </is>
-      </c>
-      <c r="D47" s="1" t="inlineStr">
-        <is>
-          <t>0154-66-3111</t>
+      <c r="B47" s="12" t="inlineStr">
+        <is>
+          <t>http://www.ja-akan.or.jp/</t>
+        </is>
+      </c>
+      <c r="C47" s="13" t="inlineStr">
+        <is>
+          <t>北海道釧路市阿寒町北新町1-4-1 (〒085-0216)</t>
+        </is>
+      </c>
+      <c r="D47" s="13" t="inlineStr">
+        <is>
+          <t>0154-66-3211</t>
         </is>
       </c>
       <c r="E47" s="1" t="inlineStr">
@@ -5261,19 +5303,24 @@
       </c>
     </row>
     <row r="48" ht="12.5" customHeight="1">
-      <c r="A48" s="1" t="inlineStr">
+      <c r="A48" s="13" t="inlineStr">
         <is>
           <t>JAしべちゃ</t>
         </is>
       </c>
-      <c r="C48" s="1" t="inlineStr">
-        <is>
-          <t>標茶町</t>
-        </is>
-      </c>
-      <c r="D48" s="1" t="inlineStr">
-        <is>
-          <t>015-485-2111</t>
+      <c r="B48" s="12" t="inlineStr">
+        <is>
+          <t>https://www.sip.jp/~ja-shibecya/</t>
+        </is>
+      </c>
+      <c r="C48" s="13" t="inlineStr">
+        <is>
+          <t>北海道川上郡標茶町開運9丁目6番地 (〒088-2311)</t>
+        </is>
+      </c>
+      <c r="D48" s="13" t="inlineStr">
+        <is>
+          <t>015-485-2103</t>
         </is>
       </c>
       <c r="E48" s="1" t="inlineStr">
@@ -5346,19 +5393,24 @@
       </c>
     </row>
     <row r="49" ht="12.5" customHeight="1">
-      <c r="A49" s="1" t="inlineStr">
+      <c r="A49" s="13" t="inlineStr">
         <is>
           <t>JA道東あさひ</t>
         </is>
       </c>
-      <c r="C49" s="1" t="inlineStr">
-        <is>
-          <t>別海町</t>
-        </is>
-      </c>
-      <c r="D49" s="1" t="inlineStr">
-        <is>
-          <t>0153-75-2311</t>
+      <c r="B49" s="12" t="inlineStr">
+        <is>
+          <t>https://www.ja-doutouasahi.or.jp/</t>
+        </is>
+      </c>
+      <c r="C49" s="13" t="inlineStr">
+        <is>
+          <t>北海道野付郡別海町別海緑町116番地9 (〒086-0214)</t>
+        </is>
+      </c>
+      <c r="D49" s="13" t="inlineStr">
+        <is>
+          <t>0153-75-2201</t>
         </is>
       </c>
       <c r="E49" s="1" t="inlineStr">
@@ -5431,19 +5483,24 @@
       </c>
     </row>
     <row r="50" ht="12.5" customHeight="1">
-      <c r="A50" s="1" t="inlineStr">
-        <is>
-          <t>JAなかしゅんべつ</t>
-        </is>
-      </c>
-      <c r="C50" s="1" t="inlineStr">
-        <is>
-          <t>別海町</t>
-        </is>
-      </c>
-      <c r="D50" s="1" t="inlineStr">
-        <is>
-          <t>0153-76-2311</t>
+      <c r="A50" s="13" t="inlineStr">
+        <is>
+          <t>JAなかしゅんべつ (中春別農業協同組合)</t>
+        </is>
+      </c>
+      <c r="B50" s="12" t="inlineStr">
+        <is>
+          <t>http://ja-nks.jp/</t>
+        </is>
+      </c>
+      <c r="C50" s="13" t="inlineStr">
+        <is>
+          <t>北海道野付郡別海町中春別南町3 (〒086-0652)</t>
+        </is>
+      </c>
+      <c r="D50" s="13" t="inlineStr">
+        <is>
+          <t>01537-6-2311</t>
         </is>
       </c>
       <c r="E50" s="1" t="inlineStr">
@@ -5516,19 +5573,24 @@
       </c>
     </row>
     <row r="51" ht="12.5" customHeight="1">
-      <c r="A51" s="1" t="inlineStr">
+      <c r="A51" s="13" t="inlineStr">
         <is>
           <t>JA標津</t>
         </is>
       </c>
-      <c r="C51" s="1" t="inlineStr">
-        <is>
-          <t>標津町</t>
-        </is>
-      </c>
-      <c r="D51" s="1" t="inlineStr">
-        <is>
-          <t>0153-82-2141</t>
+      <c r="B51" s="12" t="inlineStr">
+        <is>
+          <t>https://www.ja-shibetsu.com/</t>
+        </is>
+      </c>
+      <c r="C51" s="13" t="inlineStr">
+        <is>
+          <t>北海道標津郡標津町字川北基線西2番地</t>
+        </is>
+      </c>
+      <c r="D51" s="13" t="inlineStr">
+        <is>
+          <t>0153-85-2121</t>
         </is>
       </c>
       <c r="E51" s="1" t="inlineStr">
@@ -5693,11 +5755,23 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B36" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B37" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B38" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B39" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B41" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B42" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B43" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B44" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B45" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B46" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B47" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B48" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B49" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B50" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B51" r:id="rId21"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId10"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId22"/>
   </tableParts>
 </worksheet>
 </file>

--- a/output/企業リスト_作業中.xlsx
+++ b/output/企業リスト_作業中.xlsx
@@ -86,7 +86,7 @@
       <u val="single"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -109,6 +109,11 @@
         <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -122,7 +127,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -146,6 +151,9 @@
     <xf numFmtId="0" fontId="9" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -5663,12 +5671,41 @@
       </c>
     </row>
     <row r="52" ht="12.5" customHeight="1">
-      <c r="A52" s="1" t="n"/>
-      <c r="C52" s="1" t="n"/>
-      <c r="D52" s="1" t="n"/>
-      <c r="E52" s="1" t="n"/>
-      <c r="F52" s="1" t="n"/>
-      <c r="G52" s="1" t="n"/>
+      <c r="A52" s="17" t="inlineStr">
+        <is>
+          <t>JAオホーツク網走</t>
+        </is>
+      </c>
+      <c r="B52" s="16" t="inlineStr">
+        <is>
+          <t>https://ja-okhotskabashiri.or.jp/</t>
+        </is>
+      </c>
+      <c r="C52" s="17" t="inlineStr">
+        <is>
+          <t>北海道網走市南4条東2丁目10番地 (〒093-8728)</t>
+        </is>
+      </c>
+      <c r="D52" s="17" t="inlineStr">
+        <is>
+          <t>0152-43-2311</t>
+        </is>
+      </c>
+      <c r="E52" s="17" t="inlineStr">
+        <is>
+          <t>網走市・大空町(女満別)・東藻琴の広域JA。米・小麦・じゃがいも・てんさい・玉ねぎ・ブランド牛「オホーツクあばしり和牛」。</t>
+        </is>
+      </c>
+      <c r="F52" s="17" t="inlineStr">
+        <is>
+          <t>畑作と畜産の複合経営、選果場での労働力不足。</t>
+        </is>
+      </c>
+      <c r="G52" s="17" t="inlineStr">
+        <is>
+          <t>オホーツク地域の主要JAとして、補助金活用と完全成果報酬型を提示しながら、広域組合員への一斉アプローチを提案。</t>
+        </is>
+      </c>
       <c r="H52" s="1" t="n"/>
       <c r="I52" s="1" t="n"/>
       <c r="J52" s="1" t="n"/>
@@ -5702,6 +5739,18 @@
       <c r="AL52" s="1" t="n"/>
       <c r="AM52" s="1" t="n"/>
       <c r="AN52" s="1" t="n"/>
+      <c r="AO52">
+        <f>COUNTIFS(加電履歴!$F:$F,A52,加電履歴!$E:$E,"JAリスト")</f>
+        <v/>
+      </c>
+      <c r="AP52" s="10">
+        <f>IFERROR(IF(COUNTIFS(加電履歴!$F:$F,A52,加電履歴!$E:$E,"JAリスト")=0,"",MAXIFS(加電履歴!$B:$B,加電履歴!$F:$F,A52,加電履歴!$E:$E,"JAリスト")),"")</f>
+        <v/>
+      </c>
+      <c r="AQ52">
+        <f>IFERROR(IF(COUNTIFS(加電履歴!$F:$F,A52,加電履歴!$E:$E,"JAリスト")=0,"",INDEX(加電履歴!$I:$I,MATCH(1,(加電履歴!$F:$F=A52)*(加電履歴!$E:$E="JAリスト")*(加電履歴!$B:$B=MAXIFS(加電履歴!$B:$B,加電履歴!$F:$F,A52,加電履歴!$E:$E,"JAリスト")),0))),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="53" ht="12.5" customHeight="1">
       <c r="A53" s="1" t="n"/>
@@ -5767,11 +5816,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B49" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B50" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B51" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B52" r:id="rId22"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId22"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId23"/>
   </tableParts>
 </worksheet>
 </file>
@@ -5782,7 +5832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AS85"/>
+  <dimension ref="A1:AS98"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.6328125" defaultRowHeight="12.5"/>
   <cols>
     <col width="6.453125" customWidth="1" min="1" max="1"/>
@@ -14335,7 +14385,708 @@
         <v/>
       </c>
     </row>
+    <row r="86">
+      <c r="A86" s="15" t="inlineStr">
+        <is>
+          <t>道東(網走)</t>
+        </is>
+      </c>
+      <c r="B86" s="15" t="inlineStr">
+        <is>
+          <t>株式会社楠目牧場</t>
+        </is>
+      </c>
+      <c r="C86" s="15" t="inlineStr"/>
+      <c r="D86" s="15" t="inlineStr">
+        <is>
+          <t>北海道網走市字潮見213番地</t>
+        </is>
+      </c>
+      <c r="E86" s="15" t="inlineStr">
+        <is>
+          <t>※要確認</t>
+        </is>
+      </c>
+      <c r="F86" s="15" t="inlineStr">
+        <is>
+          <t>網走市の畜産経営/オホーツク海近郊</t>
+        </is>
+      </c>
+      <c r="G86" s="15" t="inlineStr">
+        <is>
+          <t>労働力確保と日常飼養管理</t>
+        </is>
+      </c>
+      <c r="H86" s="15" t="inlineStr">
+        <is>
+          <t>採用コストを抑えた即戦力人材の提供</t>
+        </is>
+      </c>
+      <c r="AQ86">
+        <f>COUNTIFS(加電履歴!$F:$F,B86,加電履歴!$E:$E,"畜種農業")</f>
+        <v/>
+      </c>
+      <c r="AR86" s="10">
+        <f>IFERROR(IF(COUNTIFS(加電履歴!$F:$F,B86,加電履歴!$E:$E,"畜種農業")=0,"",MAXIFS(加電履歴!$B:$B,加電履歴!$F:$F,B86,加電履歴!$E:$E,"畜種農業")),"")</f>
+        <v/>
+      </c>
+      <c r="AS86">
+        <f>IFERROR(IF(COUNTIFS(加電履歴!$F:$F,B86,加電履歴!$E:$E,"畜種農業")=0,"",INDEX(加電履歴!$I:$I,MATCH(1,(加電履歴!$F:$F=B86)*(加電履歴!$E:$E="畜種農業")*(加電履歴!$B:$B=MAXIFS(加電履歴!$B:$B,加電履歴!$F:$F,B86,加電履歴!$E:$E,"畜種農業")),0))),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="15" t="inlineStr">
+        <is>
+          <t>道東(網走)</t>
+        </is>
+      </c>
+      <c r="B87" s="15" t="inlineStr">
+        <is>
+          <t>有限会社網走原生牧場観光センター</t>
+        </is>
+      </c>
+      <c r="C87" s="16" t="inlineStr">
+        <is>
+          <t>http://www.genseibokujou.co.jp/</t>
+        </is>
+      </c>
+      <c r="D87" s="15" t="inlineStr">
+        <is>
+          <t>北海道網走市藻琴225番地</t>
+        </is>
+      </c>
+      <c r="E87" s="15" t="inlineStr">
+        <is>
+          <t>0152-46-2121</t>
+        </is>
+      </c>
+      <c r="F87" s="15" t="inlineStr">
+        <is>
+          <t>観光牧場/乗馬体験/ホーストレッキング</t>
+        </is>
+      </c>
+      <c r="G87" s="15" t="inlineStr">
+        <is>
+          <t>観光対応と飼養管理の両立</t>
+        </is>
+      </c>
+      <c r="H87" s="15" t="inlineStr">
+        <is>
+          <t>バックヤード飼育を即戦力に任せ、接客・観光サービスに注力できる体制構築</t>
+        </is>
+      </c>
+      <c r="AQ87">
+        <f>COUNTIFS(加電履歴!$F:$F,B87,加電履歴!$E:$E,"畜種農業")</f>
+        <v/>
+      </c>
+      <c r="AR87" s="10">
+        <f>IFERROR(IF(COUNTIFS(加電履歴!$F:$F,B87,加電履歴!$E:$E,"畜種農業")=0,"",MAXIFS(加電履歴!$B:$B,加電履歴!$F:$F,B87,加電履歴!$E:$E,"畜種農業")),"")</f>
+        <v/>
+      </c>
+      <c r="AS87">
+        <f>IFERROR(IF(COUNTIFS(加電履歴!$F:$F,B87,加電履歴!$E:$E,"畜種農業")=0,"",INDEX(加電履歴!$I:$I,MATCH(1,(加電履歴!$F:$F=B87)*(加電履歴!$E:$E="畜種農業")*(加電履歴!$B:$B=MAXIFS(加電履歴!$B:$B,加電履歴!$F:$F,B87,加電履歴!$E:$E,"畜種農業")),0))),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="15" t="inlineStr">
+        <is>
+          <t>道東(北見)</t>
+        </is>
+      </c>
+      <c r="B88" s="15" t="inlineStr">
+        <is>
+          <t>株式会社協同畜産経営センター</t>
+        </is>
+      </c>
+      <c r="C88" s="16" t="inlineStr">
+        <is>
+          <t>https://www.hokkaido-pork.jp/farm/feedone/farm_kyodo/</t>
+        </is>
+      </c>
+      <c r="D88" s="15" t="inlineStr">
+        <is>
+          <t>北海道北見市大正763番地</t>
+        </is>
+      </c>
+      <c r="E88" s="15" t="inlineStr">
+        <is>
+          <t>0157-36-6006</t>
+        </is>
+      </c>
+      <c r="F88" s="15" t="inlineStr">
+        <is>
+          <t>オニオンポーク生産/繁殖550頭一貫生産</t>
+        </is>
+      </c>
+      <c r="G88" s="15" t="inlineStr">
+        <is>
+          <t>大規模養豚における安定的な人員配置</t>
+        </is>
+      </c>
+      <c r="H88" s="15" t="inlineStr">
+        <is>
+          <t>養豚現場で即戦力となる特定技能人材の配置でブランド維持を支援</t>
+        </is>
+      </c>
+      <c r="AQ88">
+        <f>COUNTIFS(加電履歴!$F:$F,B88,加電履歴!$E:$E,"畜種農業")</f>
+        <v/>
+      </c>
+      <c r="AR88" s="10">
+        <f>IFERROR(IF(COUNTIFS(加電履歴!$F:$F,B88,加電履歴!$E:$E,"畜種農業")=0,"",MAXIFS(加電履歴!$B:$B,加電履歴!$F:$F,B88,加電履歴!$E:$E,"畜種農業")),"")</f>
+        <v/>
+      </c>
+      <c r="AS88">
+        <f>IFERROR(IF(COUNTIFS(加電履歴!$F:$F,B88,加電履歴!$E:$E,"畜種農業")=0,"",INDEX(加電履歴!$I:$I,MATCH(1,(加電履歴!$F:$F=B88)*(加電履歴!$E:$E="畜種農業")*(加電履歴!$B:$B=MAXIFS(加電履歴!$B:$B,加電履歴!$F:$F,B88,加電履歴!$E:$E,"畜種農業")),0))),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="15" t="inlineStr">
+        <is>
+          <t>道東(北見)</t>
+        </is>
+      </c>
+      <c r="B89" s="15" t="inlineStr">
+        <is>
+          <t>株式会社北きつね牧場</t>
+        </is>
+      </c>
+      <c r="C89" s="16" t="inlineStr">
+        <is>
+          <t>https://kitakitsune-farm.com/</t>
+        </is>
+      </c>
+      <c r="D89" s="15" t="inlineStr">
+        <is>
+          <t>北海道北見市留辺蘂町花丘52-1</t>
+        </is>
+      </c>
+      <c r="E89" s="15" t="inlineStr">
+        <is>
+          <t>0157-45-2249</t>
+        </is>
+      </c>
+      <c r="F89" s="15" t="inlineStr">
+        <is>
+          <t>観光牧場/キタキツネ・エゾタヌキ飼育</t>
+        </is>
+      </c>
+      <c r="G89" s="15" t="inlineStr">
+        <is>
+          <t>観光来場者対応と動物飼育の兼務</t>
+        </is>
+      </c>
+      <c r="H89" s="15" t="inlineStr">
+        <is>
+          <t>飼育管理を即戦力が担い、接客・施設運営に注力できる体制構築</t>
+        </is>
+      </c>
+      <c r="AQ89">
+        <f>COUNTIFS(加電履歴!$F:$F,B89,加電履歴!$E:$E,"畜種農業")</f>
+        <v/>
+      </c>
+      <c r="AR89" s="10">
+        <f>IFERROR(IF(COUNTIFS(加電履歴!$F:$F,B89,加電履歴!$E:$E,"畜種農業")=0,"",MAXIFS(加電履歴!$B:$B,加電履歴!$F:$F,B89,加電履歴!$E:$E,"畜種農業")),"")</f>
+        <v/>
+      </c>
+      <c r="AS89">
+        <f>IFERROR(IF(COUNTIFS(加電履歴!$F:$F,B89,加電履歴!$E:$E,"畜種農業")=0,"",INDEX(加電履歴!$I:$I,MATCH(1,(加電履歴!$F:$F=B89)*(加電履歴!$E:$E="畜種農業")*(加電履歴!$B:$B=MAXIFS(加電履歴!$B:$B,加電履歴!$F:$F,B89,加電履歴!$E:$E,"畜種農業")),0))),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="15" t="inlineStr">
+        <is>
+          <t>道東(美幌)</t>
+        </is>
+      </c>
+      <c r="B90" s="15" t="inlineStr">
+        <is>
+          <t>株式会社美幌牛肥育センター</t>
+        </is>
+      </c>
+      <c r="C90" s="16" t="inlineStr">
+        <is>
+          <t>http://www.bihoro-gyu.com/</t>
+        </is>
+      </c>
+      <c r="D90" s="15" t="inlineStr">
+        <is>
+          <t>北海道網走郡美幌町字都橋211番地</t>
+        </is>
+      </c>
+      <c r="E90" s="15" t="inlineStr">
+        <is>
+          <t>0152-72-3373</t>
+        </is>
+      </c>
+      <c r="F90" s="15" t="inlineStr">
+        <is>
+          <t>ブランド牛「びほろ牛」肥育/肉牛飼育・販売・堆肥販売</t>
+        </is>
+      </c>
+      <c r="G90" s="15" t="inlineStr">
+        <is>
+          <t>ブランド維持のための丁寧な肥育管理と人員確保</t>
+        </is>
+      </c>
+      <c r="H90" s="15" t="inlineStr">
+        <is>
+          <t>肥育ルーティンを即戦力で支援しブランド維持に貢献</t>
+        </is>
+      </c>
+      <c r="AQ90">
+        <f>COUNTIFS(加電履歴!$F:$F,B90,加電履歴!$E:$E,"畜種農業")</f>
+        <v/>
+      </c>
+      <c r="AR90" s="10">
+        <f>IFERROR(IF(COUNTIFS(加電履歴!$F:$F,B90,加電履歴!$E:$E,"畜種農業")=0,"",MAXIFS(加電履歴!$B:$B,加電履歴!$F:$F,B90,加電履歴!$E:$E,"畜種農業")),"")</f>
+        <v/>
+      </c>
+      <c r="AS90">
+        <f>IFERROR(IF(COUNTIFS(加電履歴!$F:$F,B90,加電履歴!$E:$E,"畜種農業")=0,"",INDEX(加電履歴!$I:$I,MATCH(1,(加電履歴!$F:$F=B90)*(加電履歴!$E:$E="畜種農業")*(加電履歴!$B:$B=MAXIFS(加電履歴!$B:$B,加電履歴!$F:$F,B90,加電履歴!$E:$E,"畜種農業")),0))),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="15" t="inlineStr">
+        <is>
+          <t>道東(美幌)</t>
+        </is>
+      </c>
+      <c r="B91" s="15" t="inlineStr">
+        <is>
+          <t>株式会社美幌ファーム</t>
+        </is>
+      </c>
+      <c r="C91" s="15" t="inlineStr">
+        <is>
+          <t>※要確認</t>
+        </is>
+      </c>
+      <c r="D91" s="15" t="inlineStr">
+        <is>
+          <t>北海道網走郡美幌町 ※詳細要確認</t>
+        </is>
+      </c>
+      <c r="E91" s="15" t="inlineStr">
+        <is>
+          <t>※要確認</t>
+        </is>
+      </c>
+      <c r="F91" s="15" t="inlineStr">
+        <is>
+          <t>びほろ牛の素牛育成(6-12カ月齢)/美幌牛肥育センター系列</t>
+        </is>
+      </c>
+      <c r="G91" s="15" t="inlineStr">
+        <is>
+          <t>グループ会社との連携と素牛育成の労働力確保</t>
+        </is>
+      </c>
+      <c r="H91" s="15" t="inlineStr">
+        <is>
+          <t>系列会社と一体での人材紹介、安定した育成オペレーション支援</t>
+        </is>
+      </c>
+      <c r="AQ91">
+        <f>COUNTIFS(加電履歴!$F:$F,B91,加電履歴!$E:$E,"畜種農業")</f>
+        <v/>
+      </c>
+      <c r="AR91" s="10">
+        <f>IFERROR(IF(COUNTIFS(加電履歴!$F:$F,B91,加電履歴!$E:$E,"畜種農業")=0,"",MAXIFS(加電履歴!$B:$B,加電履歴!$F:$F,B91,加電履歴!$E:$E,"畜種農業")),"")</f>
+        <v/>
+      </c>
+      <c r="AS91">
+        <f>IFERROR(IF(COUNTIFS(加電履歴!$F:$F,B91,加電履歴!$E:$E,"畜種農業")=0,"",INDEX(加電履歴!$I:$I,MATCH(1,(加電履歴!$F:$F=B91)*(加電履歴!$E:$E="畜種農業")*(加電履歴!$B:$B=MAXIFS(加電履歴!$B:$B,加電履歴!$F:$F,B91,加電履歴!$E:$E,"畜種農業")),0))),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="15" t="inlineStr">
+        <is>
+          <t>道東(斜里)</t>
+        </is>
+      </c>
+      <c r="B92" s="15" t="inlineStr">
+        <is>
+          <t>有限会社佐々木種畜牧場</t>
+        </is>
+      </c>
+      <c r="C92" s="16" t="inlineStr">
+        <is>
+          <t>https://sasaki-web.net/</t>
+        </is>
+      </c>
+      <c r="D92" s="15" t="inlineStr">
+        <is>
+          <t>北海道斜里郡斜里町字美咲69</t>
+        </is>
+      </c>
+      <c r="E92" s="15" t="inlineStr">
+        <is>
+          <t>0152-23-0429</t>
+        </is>
+      </c>
+      <c r="F92" s="15" t="inlineStr">
+        <is>
+          <t>サチク麦王ブランド豚/麦主体飼料/直売店併設</t>
+        </is>
+      </c>
+      <c r="G92" s="15" t="inlineStr">
+        <is>
+          <t>養豚と直売店の両立</t>
+        </is>
+      </c>
+      <c r="H92" s="15" t="inlineStr">
+        <is>
+          <t>養豚現場の即戦力配置で代表が販売・加工に注力できる体制構築</t>
+        </is>
+      </c>
+      <c r="AQ92">
+        <f>COUNTIFS(加電履歴!$F:$F,B92,加電履歴!$E:$E,"畜種農業")</f>
+        <v/>
+      </c>
+      <c r="AR92" s="10">
+        <f>IFERROR(IF(COUNTIFS(加電履歴!$F:$F,B92,加電履歴!$E:$E,"畜種農業")=0,"",MAXIFS(加電履歴!$B:$B,加電履歴!$F:$F,B92,加電履歴!$E:$E,"畜種農業")),"")</f>
+        <v/>
+      </c>
+      <c r="AS92">
+        <f>IFERROR(IF(COUNTIFS(加電履歴!$F:$F,B92,加電履歴!$E:$E,"畜種農業")=0,"",INDEX(加電履歴!$I:$I,MATCH(1,(加電履歴!$F:$F=B92)*(加電履歴!$E:$E="畜種農業")*(加電履歴!$B:$B=MAXIFS(加電履歴!$B:$B,加電履歴!$F:$F,B92,加電履歴!$E:$E,"畜種農業")),0))),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="15" t="inlineStr">
+        <is>
+          <t>道東(網走)</t>
+        </is>
+      </c>
+      <c r="B93" s="15" t="inlineStr">
+        <is>
+          <t>株式会社オホーツクファーム33</t>
+        </is>
+      </c>
+      <c r="C93" s="15" t="inlineStr"/>
+      <c r="D93" s="15" t="inlineStr">
+        <is>
+          <t>北海道網走市字北浜273番地の4</t>
+        </is>
+      </c>
+      <c r="E93" s="15" t="inlineStr">
+        <is>
+          <t>※要確認</t>
+        </is>
+      </c>
+      <c r="F93" s="15" t="inlineStr">
+        <is>
+          <t>網走市での牧場経営</t>
+        </is>
+      </c>
+      <c r="G93" s="15" t="inlineStr">
+        <is>
+          <t>日常飼養管理の労働力確保</t>
+        </is>
+      </c>
+      <c r="H93" s="15" t="inlineStr">
+        <is>
+          <t>採用コストを抑えた即戦力人材の提供</t>
+        </is>
+      </c>
+      <c r="AQ93">
+        <f>COUNTIFS(加電履歴!$F:$F,B93,加電履歴!$E:$E,"畜種農業")</f>
+        <v/>
+      </c>
+      <c r="AR93" s="10">
+        <f>IFERROR(IF(COUNTIFS(加電履歴!$F:$F,B93,加電履歴!$E:$E,"畜種農業")=0,"",MAXIFS(加電履歴!$B:$B,加電履歴!$F:$F,B93,加電履歴!$E:$E,"畜種農業")),"")</f>
+        <v/>
+      </c>
+      <c r="AS93">
+        <f>IFERROR(IF(COUNTIFS(加電履歴!$F:$F,B93,加電履歴!$E:$E,"畜種農業")=0,"",INDEX(加電履歴!$I:$I,MATCH(1,(加電履歴!$F:$F=B93)*(加電履歴!$E:$E="畜種農業")*(加電履歴!$B:$B=MAXIFS(加電履歴!$B:$B,加電履歴!$F:$F,B93,加電履歴!$E:$E,"畜種農業")),0))),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="15" t="inlineStr">
+        <is>
+          <t>道東(網走)</t>
+        </is>
+      </c>
+      <c r="B94" s="15" t="inlineStr">
+        <is>
+          <t>有限会社網走ふる里牧場</t>
+        </is>
+      </c>
+      <c r="C94" s="15" t="inlineStr"/>
+      <c r="D94" s="15" t="inlineStr">
+        <is>
+          <t>北海道網走市字稲富83</t>
+        </is>
+      </c>
+      <c r="E94" s="15" t="inlineStr">
+        <is>
+          <t>※要確認</t>
+        </is>
+      </c>
+      <c r="F94" s="15" t="inlineStr">
+        <is>
+          <t>網走市の畜産業</t>
+        </is>
+      </c>
+      <c r="G94" s="15" t="inlineStr">
+        <is>
+          <t>通常飼養管理の担い手不足</t>
+        </is>
+      </c>
+      <c r="H94" s="15" t="inlineStr">
+        <is>
+          <t>即戦力配置による飼養管理の安定化</t>
+        </is>
+      </c>
+      <c r="AQ94">
+        <f>COUNTIFS(加電履歴!$F:$F,B94,加電履歴!$E:$E,"畜種農業")</f>
+        <v/>
+      </c>
+      <c r="AR94" s="10">
+        <f>IFERROR(IF(COUNTIFS(加電履歴!$F:$F,B94,加電履歴!$E:$E,"畜種農業")=0,"",MAXIFS(加電履歴!$B:$B,加電履歴!$F:$F,B94,加電履歴!$E:$E,"畜種農業")),"")</f>
+        <v/>
+      </c>
+      <c r="AS94">
+        <f>IFERROR(IF(COUNTIFS(加電履歴!$F:$F,B94,加電履歴!$E:$E,"畜種農業")=0,"",INDEX(加電履歴!$I:$I,MATCH(1,(加電履歴!$F:$F=B94)*(加電履歴!$E:$E="畜種農業")*(加電履歴!$B:$B=MAXIFS(加電履歴!$B:$B,加電履歴!$F:$F,B94,加電履歴!$E:$E,"畜種農業")),0))),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="15" t="inlineStr">
+        <is>
+          <t>道東(大空)</t>
+        </is>
+      </c>
+      <c r="B95" s="15" t="inlineStr">
+        <is>
+          <t>株式会社北海道畜産公社 道東事業所 北見工場</t>
+        </is>
+      </c>
+      <c r="C95" s="16" t="inlineStr">
+        <is>
+          <t>https://tikusan.securesite.jp/</t>
+        </is>
+      </c>
+      <c r="D95" s="15" t="inlineStr">
+        <is>
+          <t>北海道網走郡大空町東藻琴西倉280-3 (〒099-3202)</t>
+        </is>
+      </c>
+      <c r="E95" s="15" t="inlineStr">
+        <is>
+          <t>※要確認</t>
+        </is>
+      </c>
+      <c r="F95" s="15" t="inlineStr">
+        <is>
+          <t>オホーツク地区主要食肉処理工場/牛・豚加工/海外輸出認定</t>
+        </is>
+      </c>
+      <c r="G95" s="15" t="inlineStr">
+        <is>
+          <t>大規模食肉処理ラインにおける慢性的人員不足</t>
+        </is>
+      </c>
+      <c r="H95" s="15" t="inlineStr">
+        <is>
+          <t>食肉加工現場で即戦力となる特定技能人材を通年で提供</t>
+        </is>
+      </c>
+      <c r="AQ95">
+        <f>COUNTIFS(加電履歴!$F:$F,B95,加電履歴!$E:$E,"畜種農業")</f>
+        <v/>
+      </c>
+      <c r="AR95" s="10">
+        <f>IFERROR(IF(COUNTIFS(加電履歴!$F:$F,B95,加電履歴!$E:$E,"畜種農業")=0,"",MAXIFS(加電履歴!$B:$B,加電履歴!$F:$F,B95,加電履歴!$E:$E,"畜種農業")),"")</f>
+        <v/>
+      </c>
+      <c r="AS95">
+        <f>IFERROR(IF(COUNTIFS(加電履歴!$F:$F,B95,加電履歴!$E:$E,"畜種農業")=0,"",INDEX(加電履歴!$I:$I,MATCH(1,(加電履歴!$F:$F=B95)*(加電履歴!$E:$E="畜種農業")*(加電履歴!$B:$B=MAXIFS(加電履歴!$B:$B,加電履歴!$F:$F,B95,加電履歴!$E:$E,"畜種農業")),0))),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="15" t="inlineStr">
+        <is>
+          <t>道東(大空)</t>
+        </is>
+      </c>
+      <c r="B96" s="15" t="inlineStr">
+        <is>
+          <t>有限会社山口ファーム</t>
+        </is>
+      </c>
+      <c r="C96" s="16" t="inlineStr">
+        <is>
+          <t>https://www.yamaguchifarm.com/</t>
+        </is>
+      </c>
+      <c r="D96" s="15" t="inlineStr">
+        <is>
+          <t>北海道網走郡大空町東藻琴末広92番地 (〒099-3232)</t>
+        </is>
+      </c>
+      <c r="E96" s="15" t="inlineStr">
+        <is>
+          <t>0152-66-3434</t>
+        </is>
+      </c>
+      <c r="F96" s="15" t="inlineStr">
+        <is>
+          <t>大空町東藻琴の農場経営</t>
+        </is>
+      </c>
+      <c r="G96" s="15" t="inlineStr">
+        <is>
+          <t>農繁期の労働力確保</t>
+        </is>
+      </c>
+      <c r="H96" s="15" t="inlineStr">
+        <is>
+          <t>即戦力人材による農作業の安定化</t>
+        </is>
+      </c>
+      <c r="AQ96">
+        <f>COUNTIFS(加電履歴!$F:$F,B96,加電履歴!$E:$E,"畜種農業")</f>
+        <v/>
+      </c>
+      <c r="AR96" s="10">
+        <f>IFERROR(IF(COUNTIFS(加電履歴!$F:$F,B96,加電履歴!$E:$E,"畜種農業")=0,"",MAXIFS(加電履歴!$B:$B,加電履歴!$F:$F,B96,加電履歴!$E:$E,"畜種農業")),"")</f>
+        <v/>
+      </c>
+      <c r="AS96">
+        <f>IFERROR(IF(COUNTIFS(加電履歴!$F:$F,B96,加電履歴!$E:$E,"畜種農業")=0,"",INDEX(加電履歴!$I:$I,MATCH(1,(加電履歴!$F:$F=B96)*(加電履歴!$E:$E="畜種農業")*(加電履歴!$B:$B=MAXIFS(加電履歴!$B:$B,加電履歴!$F:$F,B96,加電履歴!$E:$E,"畜種農業")),0))),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="15" t="inlineStr">
+        <is>
+          <t>道東(大空)</t>
+        </is>
+      </c>
+      <c r="B97" s="15" t="inlineStr">
+        <is>
+          <t>有限会社西牧場</t>
+        </is>
+      </c>
+      <c r="C97" s="16" t="inlineStr">
+        <is>
+          <t>https://www.nishi-farm.com/</t>
+        </is>
+      </c>
+      <c r="D97" s="15" t="inlineStr">
+        <is>
+          <t>北海道網走郡大空町東藻琴西倉347 (〒099-3202)</t>
+        </is>
+      </c>
+      <c r="E97" s="15" t="inlineStr">
+        <is>
+          <t>0152-66-2260</t>
+        </is>
+      </c>
+      <c r="F97" s="15" t="inlineStr">
+        <is>
+          <t>酪農・和牛素牛生産/乳牛235頭+黒毛和牛110頭</t>
+        </is>
+      </c>
+      <c r="G97" s="15" t="inlineStr">
+        <is>
+          <t>酪農と和牛繁殖の両立による多忙</t>
+        </is>
+      </c>
+      <c r="H97" s="15" t="inlineStr">
+        <is>
+          <t>飼養ルーティンを即戦力に任せ、繁殖管理に注力できる体制構築</t>
+        </is>
+      </c>
+      <c r="AQ97">
+        <f>COUNTIFS(加電履歴!$F:$F,B97,加電履歴!$E:$E,"畜種農業")</f>
+        <v/>
+      </c>
+      <c r="AR97" s="10">
+        <f>IFERROR(IF(COUNTIFS(加電履歴!$F:$F,B97,加電履歴!$E:$E,"畜種農業")=0,"",MAXIFS(加電履歴!$B:$B,加電履歴!$F:$F,B97,加電履歴!$E:$E,"畜種農業")),"")</f>
+        <v/>
+      </c>
+      <c r="AS97">
+        <f>IFERROR(IF(COUNTIFS(加電履歴!$F:$F,B97,加電履歴!$E:$E,"畜種農業")=0,"",INDEX(加電履歴!$I:$I,MATCH(1,(加電履歴!$F:$F=B97)*(加電履歴!$E:$E="畜種農業")*(加電履歴!$B:$B=MAXIFS(加電履歴!$B:$B,加電履歴!$F:$F,B97,加電履歴!$E:$E,"畜種農業")),0))),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="15" t="inlineStr">
+        <is>
+          <t>道東(津別)</t>
+        </is>
+      </c>
+      <c r="B98" s="15" t="inlineStr">
+        <is>
+          <t>株式会社津別ファーム</t>
+        </is>
+      </c>
+      <c r="C98" s="16" t="inlineStr">
+        <is>
+          <t>https://tsubetsufarm.com/</t>
+        </is>
+      </c>
+      <c r="D98" s="15" t="inlineStr">
+        <is>
+          <t>北海道網走郡津別町字栄58番地2 (〒092-0356)</t>
+        </is>
+      </c>
+      <c r="E98" s="15" t="inlineStr">
+        <is>
+          <t>0152-76-1420</t>
+        </is>
+      </c>
+      <c r="F98" s="15" t="inlineStr">
+        <is>
+          <t>黒毛和牛素牛生産/飼養3500頭(繁殖1711/育成1220/肥育568)</t>
+        </is>
+      </c>
+      <c r="G98" s="15" t="inlineStr">
+        <is>
+          <t>大規模和牛繁殖における人員確保と血統管理</t>
+        </is>
+      </c>
+      <c r="H98" s="15" t="inlineStr">
+        <is>
+          <t>繁殖・育成・肥育の各段階に即戦力を配置し品質を維持</t>
+        </is>
+      </c>
+      <c r="AQ98">
+        <f>COUNTIFS(加電履歴!$F:$F,B98,加電履歴!$E:$E,"畜種農業")</f>
+        <v/>
+      </c>
+      <c r="AR98" s="10">
+        <f>IFERROR(IF(COUNTIFS(加電履歴!$F:$F,B98,加電履歴!$E:$E,"畜種農業")=0,"",MAXIFS(加電履歴!$B:$B,加電履歴!$F:$F,B98,加電履歴!$E:$E,"畜種農業")),"")</f>
+        <v/>
+      </c>
+      <c r="AS98">
+        <f>IFERROR(IF(COUNTIFS(加電履歴!$F:$F,B98,加電履歴!$E:$E,"畜種農業")=0,"",INDEX(加電履歴!$I:$I,MATCH(1,(加電履歴!$F:$F=B98)*(加電履歴!$E:$E="畜種農業")*(加電履歴!$B:$B=MAXIFS(加電履歴!$B:$B,加電履歴!$F:$F,B98,加電履歴!$E:$E,"畜種農業")),0))),"")</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C87" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C88" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C89" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C90" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C92" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C95" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C96" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C97" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C98" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/output/企業リスト_作業中.xlsx
+++ b/output/企業リスト_作業中.xlsx
@@ -5832,7 +5832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AS98"/>
+  <dimension ref="A1:AS102"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.6328125" defaultRowHeight="12.5"/>
   <cols>
     <col width="6.453125" customWidth="1" min="1" max="1"/>
@@ -14826,9 +14826,9 @@
           <t>北海道網走市字稲富83</t>
         </is>
       </c>
-      <c r="E94" s="15" t="inlineStr">
-        <is>
-          <t>※要確認</t>
+      <c r="E94" s="14" t="inlineStr">
+        <is>
+          <t>0152-46-2402</t>
         </is>
       </c>
       <c r="F94" s="15" t="inlineStr">
@@ -15072,6 +15072,218 @@
       </c>
       <c r="AS98">
         <f>IFERROR(IF(COUNTIFS(加電履歴!$F:$F,B98,加電履歴!$E:$E,"畜種農業")=0,"",INDEX(加電履歴!$I:$I,MATCH(1,(加電履歴!$F:$F=B98)*(加電履歴!$E:$E="畜種農業")*(加電履歴!$B:$B=MAXIFS(加電履歴!$B:$B,加電履歴!$F:$F,B98,加電履歴!$E:$E,"畜種農業")),0))),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="15" t="inlineStr">
+        <is>
+          <t>道東(網走)</t>
+        </is>
+      </c>
+      <c r="B99" s="15" t="inlineStr">
+        <is>
+          <t>エミュー牧場 (オホーツクエミューらんど)</t>
+        </is>
+      </c>
+      <c r="C99" s="16" t="inlineStr">
+        <is>
+          <t>https://zoo.hokkaido.jp/okhotsctemu/</t>
+        </is>
+      </c>
+      <c r="D99" s="15" t="inlineStr">
+        <is>
+          <t>北海道網走市字稲富462 (〒099-3115)</t>
+        </is>
+      </c>
+      <c r="E99" s="15" t="inlineStr">
+        <is>
+          <t>0152-46-2644</t>
+        </is>
+      </c>
+      <c r="F99" s="15" t="inlineStr">
+        <is>
+          <t>日本最大級のエミュー牧場/観光・東京農大エミュー研究会付属</t>
+        </is>
+      </c>
+      <c r="G99" s="15" t="inlineStr">
+        <is>
+          <t>観光対応とエミュー飼育の両立</t>
+        </is>
+      </c>
+      <c r="H99" s="15" t="inlineStr">
+        <is>
+          <t>飼育・施設管理を即戦力に任せ、観光体験の質向上</t>
+        </is>
+      </c>
+      <c r="AQ99">
+        <f>COUNTIFS(加電履歴!$F:$F,B99,加電履歴!$E:$E,"畜種農業")</f>
+        <v/>
+      </c>
+      <c r="AR99" s="10">
+        <f>IFERROR(IF(COUNTIFS(加電履歴!$F:$F,B99,加電履歴!$E:$E,"畜種農業")=0,"",MAXIFS(加電履歴!$B:$B,加電履歴!$F:$F,B99,加電履歴!$E:$E,"畜種農業")),"")</f>
+        <v/>
+      </c>
+      <c r="AS99">
+        <f>IFERROR(IF(COUNTIFS(加電履歴!$F:$F,B99,加電履歴!$E:$E,"畜種農業")=0,"",INDEX(加電履歴!$I:$I,MATCH(1,(加電履歴!$F:$F=B99)*(加電履歴!$E:$E="畜種農業")*(加電履歴!$B:$B=MAXIFS(加電履歴!$B:$B,加電履歴!$F:$F,B99,加電履歴!$E:$E,"畜種農業")),0))),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="15" t="inlineStr">
+        <is>
+          <t>道東(大空)</t>
+        </is>
+      </c>
+      <c r="B100" s="15" t="inlineStr">
+        <is>
+          <t>太田ファーム (大空町)</t>
+        </is>
+      </c>
+      <c r="C100" s="15" t="inlineStr"/>
+      <c r="D100" s="15" t="inlineStr">
+        <is>
+          <t>北海道網走郡大空町東藻琴西倉179-2 (〒099-3202)</t>
+        </is>
+      </c>
+      <c r="E100" s="15" t="inlineStr">
+        <is>
+          <t>0152-66-2025</t>
+        </is>
+      </c>
+      <c r="F100" s="15" t="inlineStr">
+        <is>
+          <t>養豚経営</t>
+        </is>
+      </c>
+      <c r="G100" s="15" t="inlineStr">
+        <is>
+          <t>養豚現場の安定的な人員確保</t>
+        </is>
+      </c>
+      <c r="H100" s="15" t="inlineStr">
+        <is>
+          <t>養豚現場で即戦力となる特定技能人材の配置</t>
+        </is>
+      </c>
+      <c r="AQ100">
+        <f>COUNTIFS(加電履歴!$F:$F,B100,加電履歴!$E:$E,"畜種農業")</f>
+        <v/>
+      </c>
+      <c r="AR100" s="10">
+        <f>IFERROR(IF(COUNTIFS(加電履歴!$F:$F,B100,加電履歴!$E:$E,"畜種農業")=0,"",MAXIFS(加電履歴!$B:$B,加電履歴!$F:$F,B100,加電履歴!$E:$E,"畜種農業")),"")</f>
+        <v/>
+      </c>
+      <c r="AS100">
+        <f>IFERROR(IF(COUNTIFS(加電履歴!$F:$F,B100,加電履歴!$E:$E,"畜種農業")=0,"",INDEX(加電履歴!$I:$I,MATCH(1,(加電履歴!$F:$F=B100)*(加電履歴!$E:$E="畜種農業")*(加電履歴!$B:$B=MAXIFS(加電履歴!$B:$B,加電履歴!$F:$F,B100,加電履歴!$E:$E,"畜種農業")),0))),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="15" t="inlineStr">
+        <is>
+          <t>道東(大空)</t>
+        </is>
+      </c>
+      <c r="B101" s="15" t="inlineStr">
+        <is>
+          <t>有限会社長尾産業</t>
+        </is>
+      </c>
+      <c r="C101" s="16" t="inlineStr">
+        <is>
+          <t>https://nagao-sangyo.com/</t>
+        </is>
+      </c>
+      <c r="D101" s="15" t="inlineStr">
+        <is>
+          <t>北海道網走郡大空町東藻琴山園166</t>
+        </is>
+      </c>
+      <c r="E101" s="15" t="inlineStr">
+        <is>
+          <t>※要確認</t>
+        </is>
+      </c>
+      <c r="F101" s="15" t="inlineStr">
+        <is>
+          <t>大規模酪農・アイス販売（東藻琴）</t>
+        </is>
+      </c>
+      <c r="G101" s="15" t="inlineStr">
+        <is>
+          <t>大規模酪農オペレーションの担い手確保</t>
+        </is>
+      </c>
+      <c r="H101" s="15" t="inlineStr">
+        <is>
+          <t>即戦力配置で搾乳・飼養管理を安定化、6次産業に注力できる体制構築</t>
+        </is>
+      </c>
+      <c r="AQ101">
+        <f>COUNTIFS(加電履歴!$F:$F,B101,加電履歴!$E:$E,"畜種農業")</f>
+        <v/>
+      </c>
+      <c r="AR101" s="10">
+        <f>IFERROR(IF(COUNTIFS(加電履歴!$F:$F,B101,加電履歴!$E:$E,"畜種農業")=0,"",MAXIFS(加電履歴!$B:$B,加電履歴!$F:$F,B101,加電履歴!$E:$E,"畜種農業")),"")</f>
+        <v/>
+      </c>
+      <c r="AS101">
+        <f>IFERROR(IF(COUNTIFS(加電履歴!$F:$F,B101,加電履歴!$E:$E,"畜種農業")=0,"",INDEX(加電履歴!$I:$I,MATCH(1,(加電履歴!$F:$F=B101)*(加電履歴!$E:$E="畜種農業")*(加電履歴!$B:$B=MAXIFS(加電履歴!$B:$B,加電履歴!$F:$F,B101,加電履歴!$E:$E,"畜種農業")),0))),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="15" t="inlineStr">
+        <is>
+          <t>道東(小清水)</t>
+        </is>
+      </c>
+      <c r="B102" s="15" t="inlineStr">
+        <is>
+          <t>株式会社小清水農業振興公社 (アグリハートセンター)</t>
+        </is>
+      </c>
+      <c r="C102" s="16" t="inlineStr">
+        <is>
+          <t>http://agriheart.jp/</t>
+        </is>
+      </c>
+      <c r="D102" s="15" t="inlineStr">
+        <is>
+          <t>北海道斜里郡小清水町南町1丁目29番18号 (〒099-3642)</t>
+        </is>
+      </c>
+      <c r="E102" s="15" t="inlineStr">
+        <is>
+          <t>0152-67-5716</t>
+        </is>
+      </c>
+      <c r="F102" s="15" t="inlineStr">
+        <is>
+          <t>小清水町・JAこしみず等4団体出資の公社/農作業支援事業</t>
+        </is>
+      </c>
+      <c r="G102" s="15" t="inlineStr">
+        <is>
+          <t>町内農家への労働力供給のニーズ</t>
+        </is>
+      </c>
+      <c r="H102" s="15" t="inlineStr">
+        <is>
+          <t>公社窓口を通じた管内農家への一括人材紹介スキーム</t>
+        </is>
+      </c>
+      <c r="AQ102">
+        <f>COUNTIFS(加電履歴!$F:$F,B102,加電履歴!$E:$E,"畜種農業")</f>
+        <v/>
+      </c>
+      <c r="AR102" s="10">
+        <f>IFERROR(IF(COUNTIFS(加電履歴!$F:$F,B102,加電履歴!$E:$E,"畜種農業")=0,"",MAXIFS(加電履歴!$B:$B,加電履歴!$F:$F,B102,加電履歴!$E:$E,"畜種農業")),"")</f>
+        <v/>
+      </c>
+      <c r="AS102">
+        <f>IFERROR(IF(COUNTIFS(加電履歴!$F:$F,B102,加電履歴!$E:$E,"畜種農業")=0,"",INDEX(加電履歴!$I:$I,MATCH(1,(加電履歴!$F:$F=B102)*(加電履歴!$E:$E="畜種農業")*(加電履歴!$B:$B=MAXIFS(加電履歴!$B:$B,加電履歴!$F:$F,B102,加電履歴!$E:$E,"畜種農業")),0))),"")</f>
         <v/>
       </c>
     </row>
@@ -15086,6 +15298,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C96" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C97" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C98" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C99" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C101" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C102" r:id="rId12"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/output/企業リスト_作業中.xlsx
+++ b/output/企業リスト_作業中.xlsx
@@ -1315,19 +1315,24 @@
       </c>
     </row>
     <row r="2" ht="12.5" customHeight="1">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>JA道央</t>
         </is>
       </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t>恵庭市</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t>0123-33-5854</t>
+      <c r="B2" s="12" t="inlineStr">
+        <is>
+          <t>https://www.ja-douou.or.jp/</t>
+        </is>
+      </c>
+      <c r="C2" s="13" t="inlineStr">
+        <is>
+          <t>北海道恵庭市島松仲町2丁目10-1 (〒061-1352) ※本所</t>
+        </is>
+      </c>
+      <c r="D2" s="13" t="inlineStr">
+        <is>
+          <t>0123-36-1122</t>
         </is>
       </c>
       <c r="E2" s="6" t="inlineStr">
@@ -1400,19 +1405,24 @@
       </c>
     </row>
     <row r="3" ht="12.5" customHeight="1">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>JA北石狩</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>石狩市</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>0133-23-2560</t>
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>JA北いしかり (旧JA北石狩)</t>
+        </is>
+      </c>
+      <c r="B3" s="12" t="inlineStr">
+        <is>
+          <t>https://www.ja-kitaishikari.or.jp/</t>
+        </is>
+      </c>
+      <c r="C3" s="13" t="inlineStr">
+        <is>
+          <t>北海道石狩郡当別町錦町53-57 (〒061-0295) ※本所は当別町</t>
+        </is>
+      </c>
+      <c r="D3" s="13" t="inlineStr">
+        <is>
+          <t>0133-23-2530</t>
         </is>
       </c>
       <c r="E3" s="1" t="inlineStr">
@@ -1485,17 +1495,22 @@
       </c>
     </row>
     <row r="4" ht="12.5" customHeight="1">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>JA新しのつ</t>
         </is>
       </c>
-      <c r="C4" s="1" t="inlineStr">
-        <is>
-          <t>新篠津村</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="inlineStr">
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>https://www.ja-shinshinotsu.or.jp/</t>
+        </is>
+      </c>
+      <c r="C4" s="13" t="inlineStr">
+        <is>
+          <t>北海道石狩郡新篠津村第47線北13 (〒068-1193)</t>
+        </is>
+      </c>
+      <c r="D4" s="13" t="inlineStr">
         <is>
           <t>0126-57-2311</t>
         </is>
@@ -1570,19 +1585,24 @@
       </c>
     </row>
     <row r="5" ht="12.5" customHeight="1">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>JAいわみざわ</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
-        <is>
-          <t>岩見沢市</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="inlineStr">
-        <is>
-          <t>0126-25-2210</t>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>https://ja-iwamizawa.or.jp/</t>
+        </is>
+      </c>
+      <c r="C5" s="13" t="inlineStr">
+        <is>
+          <t>北海道岩見沢市2条西1丁目1番地 (〒068-0022) ※新本所</t>
+        </is>
+      </c>
+      <c r="D5" s="13" t="inlineStr">
+        <is>
+          <t>0126-25-2211</t>
         </is>
       </c>
       <c r="E5" s="1" t="inlineStr">
@@ -1655,19 +1675,24 @@
       </c>
     </row>
     <row r="6" ht="12.5" customHeight="1">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>JAみねのぶ</t>
         </is>
       </c>
-      <c r="C6" s="1" t="inlineStr">
-        <is>
-          <t>美唄市</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="inlineStr">
-        <is>
-          <t>0126-67-2331</t>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>http://www.ja-minenobu.or.jp/</t>
+        </is>
+      </c>
+      <c r="C6" s="13" t="inlineStr">
+        <is>
+          <t>北海道美唄市峰延町本町1862-1</t>
+        </is>
+      </c>
+      <c r="D6" s="13" t="inlineStr">
+        <is>
+          <t>0126-67-2111</t>
         </is>
       </c>
       <c r="E6" s="1" t="inlineStr">
@@ -1740,19 +1765,24 @@
       </c>
     </row>
     <row r="7" ht="12.5" customHeight="1">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>JAびばい</t>
         </is>
       </c>
-      <c r="C7" s="1" t="inlineStr">
-        <is>
-          <t>美唄市</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="inlineStr">
-        <is>
-          <t>0126-62-2141</t>
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>https://www.ja-bibai.or.jp/</t>
+        </is>
+      </c>
+      <c r="C7" s="13" t="inlineStr">
+        <is>
+          <t>北海道美唄市大通東1条北1-2-1</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="inlineStr">
+        <is>
+          <t>0126-63-2162</t>
         </is>
       </c>
       <c r="E7" s="1" t="inlineStr">
@@ -1825,19 +1855,24 @@
       </c>
     </row>
     <row r="8" ht="12.5" customHeight="1">
-      <c r="A8" s="1" t="inlineStr">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t>JAたきかわ</t>
         </is>
       </c>
-      <c r="C8" s="1" t="inlineStr">
-        <is>
-          <t>滝川市</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="inlineStr">
-        <is>
-          <t>0125-23-2400</t>
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>https://www.ja-takikawa.com/</t>
+        </is>
+      </c>
+      <c r="C8" s="13" t="inlineStr">
+        <is>
+          <t>北海道滝川市本町4丁目1-31</t>
+        </is>
+      </c>
+      <c r="D8" s="13" t="inlineStr">
+        <is>
+          <t>0125-22-3401</t>
         </is>
       </c>
       <c r="E8" s="1" t="inlineStr">
@@ -1910,17 +1945,22 @@
       </c>
     </row>
     <row r="9" ht="12.5" customHeight="1">
-      <c r="A9" s="1" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>JA新すながわ</t>
         </is>
       </c>
-      <c r="C9" s="1" t="inlineStr">
-        <is>
-          <t>砂川市</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="inlineStr">
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>https://jashinsunagawa.or.jp/</t>
+        </is>
+      </c>
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>北海道砂川市東1条南1-1-20</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
         <is>
           <t>0125-54-3181</t>
         </is>
@@ -1995,19 +2035,24 @@
       </c>
     </row>
     <row r="10" ht="12.5" customHeight="1">
-      <c r="A10" s="1" t="inlineStr">
+      <c r="A10" s="13" t="inlineStr">
         <is>
           <t>JA月形町</t>
         </is>
       </c>
-      <c r="C10" s="1" t="inlineStr">
-        <is>
-          <t>月形町</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="inlineStr">
-        <is>
-          <t>0126-53-2311</t>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>https://www.hamanasu.to/ja-moon/</t>
+        </is>
+      </c>
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>北海道樺戸郡月形町1069番地</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="inlineStr">
+        <is>
+          <t>0126-53-2111</t>
         </is>
       </c>
       <c r="E10" s="1" t="inlineStr">
@@ -2080,19 +2125,24 @@
       </c>
     </row>
     <row r="11" ht="12.5" customHeight="1">
-      <c r="A11" s="1" t="inlineStr">
+      <c r="A11" s="13" t="inlineStr">
         <is>
           <t>JAきたそらち</t>
         </is>
       </c>
-      <c r="C11" s="1" t="inlineStr">
-        <is>
-          <t>深川市</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="inlineStr">
-        <is>
-          <t>0164-22-6618</t>
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>https://www.ja-kitasorachi.com/</t>
+        </is>
+      </c>
+      <c r="C11" s="13" t="inlineStr">
+        <is>
+          <t>北海道深川市深川町字メム10号線山3線5850番地 (〒074-0015)</t>
+        </is>
+      </c>
+      <c r="D11" s="13" t="inlineStr">
+        <is>
+          <t>0164-22-6600</t>
         </is>
       </c>
       <c r="E11" s="1" t="inlineStr">
@@ -2165,17 +2215,22 @@
       </c>
     </row>
     <row r="12" ht="12.5" customHeight="1">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="13" t="inlineStr">
         <is>
           <t>JA北いぶき</t>
         </is>
       </c>
-      <c r="C12" s="1" t="inlineStr">
-        <is>
-          <t>秩父別町</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="inlineStr">
+      <c r="B12" s="12" t="inlineStr">
+        <is>
+          <t>https://www.ja-kitaibuki.or.jp/</t>
+        </is>
+      </c>
+      <c r="C12" s="13" t="inlineStr">
+        <is>
+          <t>北海道雨竜郡秩父別町1298-8 (〒078-2102) ※本所・秩父別支所</t>
+        </is>
+      </c>
+      <c r="D12" s="13" t="inlineStr">
         <is>
           <t>0164-33-2011</t>
         </is>
@@ -2250,17 +2305,22 @@
       </c>
     </row>
     <row r="13" ht="12.5" customHeight="1">
-      <c r="A13" s="1" t="inlineStr">
+      <c r="A13" s="13" t="inlineStr">
         <is>
           <t>JAピンネ</t>
         </is>
       </c>
-      <c r="C13" s="1" t="inlineStr">
-        <is>
-          <t>新十津川町</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="inlineStr">
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>https://www.japinne.or.jp/</t>
+        </is>
+      </c>
+      <c r="C13" s="13" t="inlineStr">
+        <is>
+          <t>北海道樺戸郡新十津川町字中央6番地29 (〒073-1103)</t>
+        </is>
+      </c>
+      <c r="D13" s="13" t="inlineStr">
         <is>
           <t>0125-76-2221</t>
         </is>
@@ -2335,17 +2395,22 @@
       </c>
     </row>
     <row r="14" ht="12.5" customHeight="1">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>JA余市町</t>
-        </is>
-      </c>
-      <c r="C14" s="1" t="inlineStr">
-        <is>
-          <t>余市町</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="inlineStr">
+      <c r="A14" s="13" t="inlineStr">
+        <is>
+          <t>JAよいち (旧JA余市町)</t>
+        </is>
+      </c>
+      <c r="B14" s="12" t="inlineStr">
+        <is>
+          <t>https://ja-yoichi.or.jp/</t>
+        </is>
+      </c>
+      <c r="C14" s="13" t="inlineStr">
+        <is>
+          <t>北海道余市郡余市町黒川町5丁目22番地</t>
+        </is>
+      </c>
+      <c r="D14" s="13" t="inlineStr">
         <is>
           <t>0135-23-3121</t>
         </is>
@@ -2420,17 +2485,22 @@
       </c>
     </row>
     <row r="15" ht="12.5" customHeight="1">
-      <c r="A15" s="1" t="inlineStr">
+      <c r="A15" s="13" t="inlineStr">
         <is>
           <t>JAきょうわ</t>
         </is>
       </c>
-      <c r="C15" s="1" t="inlineStr">
-        <is>
-          <t>共和町</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="inlineStr">
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>https://www.ja-kyouwa.jp/</t>
+        </is>
+      </c>
+      <c r="C15" s="13" t="inlineStr">
+        <is>
+          <t>北海道岩内郡共和町前田167 (〒048-2201)</t>
+        </is>
+      </c>
+      <c r="D15" s="13" t="inlineStr">
         <is>
           <t>0135-73-2121</t>
         </is>
@@ -2505,19 +2575,24 @@
       </c>
     </row>
     <row r="16" ht="12.5" customHeight="1">
-      <c r="A16" s="1" t="inlineStr">
+      <c r="A16" s="13" t="inlineStr">
         <is>
           <t>JA新おたる</t>
         </is>
       </c>
-      <c r="C16" s="1" t="inlineStr">
-        <is>
-          <t>仁木町</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="inlineStr">
-        <is>
-          <t>0135-32-2525</t>
+      <c r="B16" s="12" t="inlineStr">
+        <is>
+          <t>https://ja-sinotaru.jp/</t>
+        </is>
+      </c>
+      <c r="C16" s="13" t="inlineStr">
+        <is>
+          <t>北海道余市郡仁木町北町3丁目4番地 (〒048-2493)</t>
+        </is>
+      </c>
+      <c r="D16" s="13" t="inlineStr">
+        <is>
+          <t>0135-32-2428</t>
         </is>
       </c>
       <c r="E16" s="1" t="inlineStr">
@@ -2590,19 +2665,24 @@
       </c>
     </row>
     <row r="17" ht="12.5" customHeight="1">
-      <c r="A17" s="1" t="inlineStr">
+      <c r="A17" s="13" t="inlineStr">
         <is>
           <t>JAたいせつ</t>
         </is>
       </c>
-      <c r="C17" s="1" t="inlineStr">
-        <is>
-          <t>旭川市</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="inlineStr">
-        <is>
-          <t>0166-57-2311</t>
+      <c r="B17" s="12" t="inlineStr">
+        <is>
+          <t>http://www.jataisetu.or.jp/</t>
+        </is>
+      </c>
+      <c r="C17" s="13" t="inlineStr">
+        <is>
+          <t>北海道旭川市東鷹栖1条3-635-58 (〒071-8101)</t>
+        </is>
+      </c>
+      <c r="D17" s="13" t="inlineStr">
+        <is>
+          <t>0166-57-2345</t>
         </is>
       </c>
       <c r="E17" s="1" t="inlineStr">
@@ -2675,19 +2755,24 @@
       </c>
     </row>
     <row r="18" ht="12.5" customHeight="1">
-      <c r="A18" s="1" t="inlineStr">
+      <c r="A18" s="13" t="inlineStr">
         <is>
           <t>JA東神楽</t>
         </is>
       </c>
-      <c r="C18" s="1" t="inlineStr">
-        <is>
-          <t>東神楽町</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="inlineStr">
-        <is>
-          <t>0166-83-2322</t>
+      <c r="B18" s="12" t="inlineStr">
+        <is>
+          <t>https://www.ja-higashikagura.com/</t>
+        </is>
+      </c>
+      <c r="C18" s="13" t="inlineStr">
+        <is>
+          <t>北海道上川郡東神楽町</t>
+        </is>
+      </c>
+      <c r="D18" s="13" t="inlineStr">
+        <is>
+          <t>0166-83-2321 (本所代表) / 0166-83-2322 (金融課)</t>
         </is>
       </c>
       <c r="E18" s="1" t="inlineStr">
@@ -2760,17 +2845,22 @@
       </c>
     </row>
     <row r="19" ht="12.5" customHeight="1">
-      <c r="A19" s="1" t="inlineStr">
+      <c r="A19" s="13" t="inlineStr">
         <is>
           <t>JAひがしかわ</t>
         </is>
       </c>
-      <c r="C19" s="1" t="inlineStr">
-        <is>
-          <t>東川町</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="inlineStr">
+      <c r="B19" s="12" t="inlineStr">
+        <is>
+          <t>https://www.ja-higashikawa.or.jp/</t>
+        </is>
+      </c>
+      <c r="C19" s="13" t="inlineStr">
+        <is>
+          <t>北海道上川郡東川町西町1丁目5番1号 (〒071-1495)</t>
+        </is>
+      </c>
+      <c r="D19" s="13" t="inlineStr">
         <is>
           <t>0166-82-5010</t>
         </is>
@@ -3270,19 +3360,20 @@
       </c>
     </row>
     <row r="25" ht="12.5" customHeight="1">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>JA南るもい</t>
-        </is>
-      </c>
-      <c r="C25" s="1" t="inlineStr">
-        <is>
-          <t>留萌市</t>
-        </is>
-      </c>
-      <c r="D25" s="1" t="inlineStr">
-        <is>
-          <t>0164-42-2277</t>
+      <c r="A25" s="13" t="inlineStr">
+        <is>
+          <t>JA南るもい ※令和3年JAるもいへ合併・現存せず</t>
+        </is>
+      </c>
+      <c r="B25" s="14" t="inlineStr"/>
+      <c r="C25" s="13" t="inlineStr">
+        <is>
+          <t>※統合: JAるもい本所(羽幌町)。連絡先はJAるもい(0164-62-1212系) ※要確認</t>
+        </is>
+      </c>
+      <c r="D25" s="13" t="inlineStr">
+        <is>
+          <t>※存続: JAるもい</t>
         </is>
       </c>
       <c r="E25" s="1" t="inlineStr">
@@ -3355,19 +3446,20 @@
       </c>
     </row>
     <row r="26" ht="12.5" customHeight="1">
-      <c r="A26" s="1" t="inlineStr">
-        <is>
-          <t>JAオロロン</t>
-        </is>
-      </c>
-      <c r="C26" s="1" t="inlineStr">
-        <is>
-          <t>羽幌町</t>
-        </is>
-      </c>
-      <c r="D26" s="1" t="inlineStr">
-        <is>
-          <t>0164-62-1388</t>
+      <c r="A26" s="13" t="inlineStr">
+        <is>
+          <t>JAオロロン ※令和3年JAるもいへ合併・現存せず</t>
+        </is>
+      </c>
+      <c r="B26" s="14" t="inlineStr"/>
+      <c r="C26" s="13" t="inlineStr">
+        <is>
+          <t>※統合: JAるもい本所(羽幌町)。羽幌町字南町7-29(JAるもい本所と同位置の可能性)</t>
+        </is>
+      </c>
+      <c r="D26" s="13" t="inlineStr">
+        <is>
+          <t>※存続: JAるもい</t>
         </is>
       </c>
       <c r="E26" s="1" t="inlineStr">
@@ -3440,19 +3532,24 @@
       </c>
     </row>
     <row r="27" ht="12.5" customHeight="1">
-      <c r="A27" s="1" t="inlineStr">
+      <c r="A27" s="13" t="inlineStr">
         <is>
           <t>JA北宗谷</t>
         </is>
       </c>
-      <c r="C27" s="1" t="inlineStr">
-        <is>
-          <t>豊富町</t>
-        </is>
-      </c>
-      <c r="D27" s="1" t="inlineStr">
-        <is>
-          <t>0162-82-1025</t>
+      <c r="B27" s="12" t="inlineStr">
+        <is>
+          <t>https://ja-kitasouya.jp/</t>
+        </is>
+      </c>
+      <c r="C27" s="13" t="inlineStr">
+        <is>
+          <t>北海道天塩郡豊富町</t>
+        </is>
+      </c>
+      <c r="D27" s="13" t="inlineStr">
+        <is>
+          <t>0162-82-2112</t>
         </is>
       </c>
       <c r="E27" s="1" t="inlineStr">
@@ -3525,19 +3622,24 @@
       </c>
     </row>
     <row r="28" ht="12.5" customHeight="1">
-      <c r="A28" s="1" t="inlineStr">
+      <c r="A28" s="13" t="inlineStr">
         <is>
           <t>JA宗谷南</t>
         </is>
       </c>
-      <c r="C28" s="1" t="inlineStr">
-        <is>
-          <t>枝幸町</t>
-        </is>
-      </c>
-      <c r="D28" s="1" t="inlineStr">
-        <is>
-          <t>0163-62-4100</t>
+      <c r="B28" s="12" t="inlineStr">
+        <is>
+          <t>http://ja-souyaminami.or.jp/</t>
+        </is>
+      </c>
+      <c r="C28" s="13" t="inlineStr">
+        <is>
+          <t>北海道枝幸郡枝幸町幸町8121-3 (〒098-5805)</t>
+        </is>
+      </c>
+      <c r="D28" s="13" t="inlineStr">
+        <is>
+          <t>0163-62-1711</t>
         </is>
       </c>
       <c r="E28" s="1" t="inlineStr">
@@ -3610,19 +3712,24 @@
       </c>
     </row>
     <row r="29" ht="12.5" customHeight="1">
-      <c r="A29" s="1" t="inlineStr">
-        <is>
-          <t>JAひがし宗谷</t>
-        </is>
-      </c>
-      <c r="C29" s="1" t="inlineStr">
-        <is>
-          <t>浜頓別町</t>
-        </is>
-      </c>
-      <c r="D29" s="1" t="inlineStr">
-        <is>
-          <t>01634-2-3366</t>
+      <c r="A29" s="13" t="inlineStr">
+        <is>
+          <t>JAひがし宗谷 (東宗谷農業協同組合)</t>
+        </is>
+      </c>
+      <c r="B29" s="12" t="inlineStr">
+        <is>
+          <t>https://www.ja-esoya.com/</t>
+        </is>
+      </c>
+      <c r="C29" s="13" t="inlineStr">
+        <is>
+          <t>北海道枝幸郡浜頓別町南3条1丁目25番地</t>
+        </is>
+      </c>
+      <c r="D29" s="13" t="inlineStr">
+        <is>
+          <t>01634-2-2229 (本所) / 01634-2-3366 (金融部)</t>
         </is>
       </c>
       <c r="E29" s="1" t="inlineStr">
@@ -5795,33 +5902,54 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B30" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B31" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B32" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B33" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B34" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B35" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B36" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B37" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B38" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B39" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B41" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B42" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B43" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B44" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B45" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B46" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B47" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B48" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B49" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B50" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B51" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B52" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B27" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B28" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B29" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B30" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B31" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B32" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B33" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B34" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B35" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B36" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B37" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B38" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B39" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B41" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B42" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B43" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B44" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B45" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B46" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B47" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B48" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B49" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B50" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B51" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B52" r:id="rId43"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId23"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId44"/>
   </tableParts>
 </worksheet>
 </file>

--- a/output/企業リスト_作業中.xlsx
+++ b/output/企業リスト_作業中.xlsx
@@ -2935,19 +2935,24 @@
       </c>
     </row>
     <row r="20" ht="12.5" customHeight="1">
-      <c r="A20" s="1" t="inlineStr">
+      <c r="A20" s="13" t="inlineStr">
         <is>
           <t>JA当麻</t>
         </is>
       </c>
-      <c r="C20" s="1" t="inlineStr">
-        <is>
-          <t>当麻町</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="inlineStr">
-        <is>
-          <t>0166-84-2124</t>
+      <c r="B20" s="12" t="inlineStr">
+        <is>
+          <t>https://ja-tohma.com/</t>
+        </is>
+      </c>
+      <c r="C20" s="13" t="inlineStr">
+        <is>
+          <t>北海道上川郡当麻町4条東3丁目4番63号 (〒078-1314)</t>
+        </is>
+      </c>
+      <c r="D20" s="13" t="inlineStr">
+        <is>
+          <t>0166-84-2121</t>
         </is>
       </c>
       <c r="E20" s="1" t="inlineStr">
@@ -3020,19 +3025,24 @@
       </c>
     </row>
     <row r="21" ht="12.5" customHeight="1">
-      <c r="A21" s="1" t="inlineStr">
+      <c r="A21" s="13" t="inlineStr">
         <is>
           <t>JA上川中央</t>
         </is>
       </c>
-      <c r="C21" s="1" t="inlineStr">
-        <is>
-          <t>愛別町</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="inlineStr">
-        <is>
-          <t>01658-6-5312</t>
+      <c r="B21" s="12" t="inlineStr">
+        <is>
+          <t>http://www.ja-kamikawa.or.jp/</t>
+        </is>
+      </c>
+      <c r="C21" s="13" t="inlineStr">
+        <is>
+          <t>北海道上川郡愛別町字本町125番地 (〒078-1495)</t>
+        </is>
+      </c>
+      <c r="D21" s="13" t="inlineStr">
+        <is>
+          <t>01658-6-5311 (代表) / 01658-6-5312 (金融部)</t>
         </is>
       </c>
       <c r="E21" s="1" t="inlineStr">
@@ -3105,19 +3115,24 @@
       </c>
     </row>
     <row r="22" ht="12.5" customHeight="1">
-      <c r="A22" s="1" t="inlineStr">
+      <c r="A22" s="13" t="inlineStr">
         <is>
           <t>JAぴっぷ町</t>
         </is>
       </c>
-      <c r="C22" s="1" t="inlineStr">
-        <is>
-          <t>比布町</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="inlineStr">
-        <is>
-          <t>0166-85-2121</t>
+      <c r="B22" s="12" t="inlineStr">
+        <is>
+          <t>https://www.ja-pippu.or.jp/</t>
+        </is>
+      </c>
+      <c r="C22" s="13" t="inlineStr">
+        <is>
+          <t>北海道上川郡比布町西町3-5-14</t>
+        </is>
+      </c>
+      <c r="D22" s="13" t="inlineStr">
+        <is>
+          <t>0166-85-2121 ※公式サイトで再確認推奨</t>
         </is>
       </c>
       <c r="E22" s="1" t="inlineStr">
@@ -3275,19 +3290,24 @@
       </c>
     </row>
     <row r="24" ht="12.5" customHeight="1">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>JA名寄</t>
-        </is>
-      </c>
-      <c r="C24" s="1" t="inlineStr">
-        <is>
-          <t>名寄市</t>
-        </is>
-      </c>
-      <c r="D24" s="1" t="inlineStr">
-        <is>
-          <t>01655-3-2030</t>
+      <c r="A24" s="13" t="inlineStr">
+        <is>
+          <t>JA道北なよろ (旧JA名寄)</t>
+        </is>
+      </c>
+      <c r="B24" s="12" t="inlineStr">
+        <is>
+          <t>https://www.ja-douhokunayoro.or.jp/</t>
+        </is>
+      </c>
+      <c r="C24" s="13" t="inlineStr">
+        <is>
+          <t>北海道名寄市大通南4丁目10番地1 ※本所</t>
+        </is>
+      </c>
+      <c r="D24" s="13" t="inlineStr">
+        <is>
+          <t>01654-2-4531</t>
         </is>
       </c>
       <c r="E24" s="1" t="inlineStr">
@@ -5920,36 +5940,40 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B17" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B18" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B19" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B27" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B28" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B29" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B30" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B31" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B32" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B33" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B34" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B35" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B36" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B37" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B38" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B39" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B41" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B42" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B43" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B44" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B45" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B46" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B47" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B48" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B49" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B50" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B51" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B52" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B24" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B27" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B28" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B29" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B30" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B31" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B32" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B33" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B34" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B35" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B36" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B37" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B38" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B39" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B41" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B42" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B43" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B44" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B45" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B46" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B47" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B48" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B49" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B50" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B51" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B52" r:id="rId47"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId44"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId48"/>
   </tableParts>
 </worksheet>
 </file>

--- a/output/企業リスト_作業中.xlsx
+++ b/output/企業リスト_作業中.xlsx
@@ -127,7 +127,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -154,6 +154,7 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -10880,17 +10881,22 @@
           <t>道北</t>
         </is>
       </c>
-      <c r="B49" s="9" t="inlineStr">
+      <c r="B49" s="18" t="inlineStr">
         <is>
           <t>株式会社東武牧場</t>
         </is>
       </c>
-      <c r="D49" s="9" t="inlineStr">
-        <is>
-          <t>北海道士別市武徳町</t>
-        </is>
-      </c>
-      <c r="E49" s="9" t="inlineStr">
+      <c r="C49" s="12" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Toubufarm/</t>
+        </is>
+      </c>
+      <c r="D49" s="18" t="inlineStr">
+        <is>
+          <t>北海道士別市武徳町44線東8号 (〒095-0062)</t>
+        </is>
+      </c>
+      <c r="E49" s="18" t="inlineStr">
         <is>
           <t>0165-23-1548</t>
         </is>
@@ -10979,19 +10985,24 @@
           <t>道北</t>
         </is>
       </c>
-      <c r="B50" s="9" t="inlineStr">
-        <is>
-          <t>下士別畜産・早川牧場</t>
-        </is>
-      </c>
-      <c r="D50" s="9" t="inlineStr">
-        <is>
-          <t>北海道士別市下士別町</t>
-        </is>
-      </c>
-      <c r="E50" s="9" t="inlineStr">
-        <is>
-          <t>0165-23-4171</t>
+      <c r="B50" s="18" t="inlineStr">
+        <is>
+          <t>株式会社早川牧場 / 有限会社下士別畜産 (もろみ豚 共同販売)</t>
+        </is>
+      </c>
+      <c r="C50" s="12" t="inlineStr">
+        <is>
+          <t>http://www.moromi.co.jp/</t>
+        </is>
+      </c>
+      <c r="D50" s="18" t="inlineStr">
+        <is>
+          <t>北海道士別市下士別町41線東3 (早川牧場) / 41線18 (下士別畜産) (〒095-0061)</t>
+        </is>
+      </c>
+      <c r="E50" s="18" t="inlineStr">
+        <is>
+          <t>0165-22-4157 (早川牧場) / 0165-23-3928 (下士別畜産)</t>
         </is>
       </c>
       <c r="F50" s="9" t="inlineStr">
@@ -11078,19 +11089,24 @@
           <t>道北</t>
         </is>
       </c>
-      <c r="B51" s="9" t="inlineStr">
-        <is>
-          <t>美瑛放牧酪農場</t>
-        </is>
-      </c>
-      <c r="D51" s="9" t="inlineStr">
-        <is>
-          <t>北海道上川郡美瑛町</t>
-        </is>
-      </c>
-      <c r="E51" s="9" t="inlineStr">
-        <is>
-          <t>0166-95-2277</t>
+      <c r="B51" s="18" t="inlineStr">
+        <is>
+          <t>美瑛放牧酪農場 (株式会社美瑛ファーム)</t>
+        </is>
+      </c>
+      <c r="C51" s="12" t="inlineStr">
+        <is>
+          <t>http://biei-farm.co.jp/</t>
+        </is>
+      </c>
+      <c r="D51" s="18" t="inlineStr">
+        <is>
+          <t>北海道上川郡美瑛町新星平和5235</t>
+        </is>
+      </c>
+      <c r="E51" s="18" t="inlineStr">
+        <is>
+          <t>0166-68-6777</t>
         </is>
       </c>
       <c r="F51" s="9" t="inlineStr">
@@ -11177,19 +11193,24 @@
           <t>道北</t>
         </is>
       </c>
-      <c r="B52" s="9" t="inlineStr">
+      <c r="B52" s="18" t="inlineStr">
         <is>
           <t>ファームズ千代田</t>
         </is>
       </c>
-      <c r="D52" s="9" t="inlineStr">
-        <is>
-          <t>北海道上川郡美瑛町</t>
-        </is>
-      </c>
-      <c r="E52" s="9" t="inlineStr">
-        <is>
-          <t>0166-92-1718</t>
+      <c r="C52" s="12" t="inlineStr">
+        <is>
+          <t>https://f-chiyoda.com/</t>
+        </is>
+      </c>
+      <c r="D52" s="18" t="inlineStr">
+        <is>
+          <t>北海道上川郡美瑛町春日台4221</t>
+        </is>
+      </c>
+      <c r="E52" s="18" t="inlineStr">
+        <is>
+          <t>0166-92-7015</t>
         </is>
       </c>
       <c r="F52" s="9" t="inlineStr">
@@ -11276,19 +11297,24 @@
           <t>道北</t>
         </is>
       </c>
-      <c r="B53" s="9" t="inlineStr">
+      <c r="B53" s="18" t="inlineStr">
         <is>
           <t>富良野牧場</t>
         </is>
       </c>
-      <c r="D53" s="9" t="inlineStr">
-        <is>
-          <t>北海道富良野市</t>
-        </is>
-      </c>
-      <c r="E53" s="9" t="inlineStr">
-        <is>
-          <t>0167-22-4418</t>
+      <c r="C53" s="12" t="inlineStr">
+        <is>
+          <t>https://furanobokujo.com/</t>
+        </is>
+      </c>
+      <c r="D53" s="18" t="inlineStr">
+        <is>
+          <t>北海道富良野市東鳥沼1 (〒076-0041)</t>
+        </is>
+      </c>
+      <c r="E53" s="18" t="inlineStr">
+        <is>
+          <t>0167-22-1543</t>
         </is>
       </c>
       <c r="F53" s="9" t="inlineStr">
@@ -11375,19 +11401,20 @@
           <t>道北</t>
         </is>
       </c>
-      <c r="B54" s="9" t="inlineStr">
-        <is>
-          <t>サロベツファーム</t>
-        </is>
-      </c>
-      <c r="D54" s="9" t="inlineStr">
-        <is>
-          <t>北海道天塩郡豊富町</t>
-        </is>
-      </c>
-      <c r="E54" s="9" t="inlineStr">
-        <is>
-          <t>0162-82-3232</t>
+      <c r="B54" s="18" t="inlineStr">
+        <is>
+          <t>株式会社サロベツファーム</t>
+        </is>
+      </c>
+      <c r="C54" s="14" t="inlineStr"/>
+      <c r="D54" s="18" t="inlineStr">
+        <is>
+          <t>北海道天塩郡豊富町字上サロベツ796番地13</t>
+        </is>
+      </c>
+      <c r="E54" s="18" t="inlineStr">
+        <is>
+          <t>0162-84-2377</t>
         </is>
       </c>
       <c r="F54" s="9" t="inlineStr">
@@ -11474,19 +11501,24 @@
           <t>道北</t>
         </is>
       </c>
-      <c r="B55" s="9" t="inlineStr">
-        <is>
-          <t>豊富牛乳公社</t>
-        </is>
-      </c>
-      <c r="D55" s="9" t="inlineStr">
-        <is>
-          <t>北海道天塩郡豊富町</t>
-        </is>
-      </c>
-      <c r="E55" s="9" t="inlineStr">
-        <is>
-          <t>0162-82-1211</t>
+      <c r="B55" s="18" t="inlineStr">
+        <is>
+          <t>株式会社豊富牛乳公社</t>
+        </is>
+      </c>
+      <c r="C55" s="12" t="inlineStr">
+        <is>
+          <t>https://www.toyotomi-milk.co.jp/</t>
+        </is>
+      </c>
+      <c r="D55" s="18" t="inlineStr">
+        <is>
+          <t>北海道天塩郡豊富町上サロベツ1184 (〒098-4100)</t>
+        </is>
+      </c>
+      <c r="E55" s="18" t="inlineStr">
+        <is>
+          <t>0162-82-2576</t>
         </is>
       </c>
       <c r="F55" s="9" t="inlineStr">
@@ -11773,42 +11805,42 @@
       </c>
       <c r="B58" s="9" t="inlineStr">
         <is>
-          <t>JA北宗谷</t>
+          <t>旭川市営牧場</t>
         </is>
       </c>
       <c r="D58" s="9" t="inlineStr">
         <is>
-          <t>北海道天塩郡豊富町</t>
+          <t>北海道旭川市</t>
         </is>
       </c>
       <c r="E58" s="9" t="inlineStr">
         <is>
-          <t>0162-82-2112</t>
+          <t>0166-25-7427</t>
         </is>
       </c>
       <c r="F58" s="9" t="inlineStr">
         <is>
-          <t>豊富・稚内の酪農統括JA</t>
+          <t>市営の公共牧場</t>
         </is>
       </c>
       <c r="G58" s="9" t="inlineStr">
         <is>
-          <t>管内の生乳出荷農家の労働力底上げ</t>
+          <t>公共施設の放牧管理</t>
         </is>
       </c>
       <c r="H58" s="9" t="inlineStr">
         <is>
-          <t>組合経由での外国人材採用コスト削減モデル</t>
+          <t>施設の安定稼働を即戦力で支援</t>
         </is>
       </c>
       <c r="I58" s="9" t="inlineStr">
         <is>
-          <t>営農部</t>
+          <t>農林部</t>
         </is>
       </c>
       <c r="J58" s="9" t="inlineStr">
         <is>
-          <t>担当者</t>
+          <t>管理者</t>
         </is>
       </c>
       <c r="K58" s="9" t="inlineStr">
@@ -11872,42 +11904,42 @@
       </c>
       <c r="B59" s="9" t="inlineStr">
         <is>
-          <t>JAひがし宗谷</t>
+          <t>士別市営天塩川牧場</t>
         </is>
       </c>
       <c r="D59" s="9" t="inlineStr">
         <is>
-          <t>北海道枝幸郡浜頓別町</t>
+          <t>北海道士別市</t>
         </is>
       </c>
       <c r="E59" s="9" t="inlineStr">
         <is>
-          <t>01634-2-2229</t>
+          <t>0165-23-3121</t>
         </is>
       </c>
       <c r="F59" s="9" t="inlineStr">
         <is>
-          <t>宗谷東部エリアの農業統括</t>
+          <t>市営の育成牧場</t>
         </is>
       </c>
       <c r="G59" s="9" t="inlineStr">
         <is>
-          <t>地域農家の高齢化と後継者不足</t>
+          <t>預託牛の体調管理</t>
         </is>
       </c>
       <c r="H59" s="9" t="inlineStr">
         <is>
-          <t>特定技能人材の紹介を通じた営農基盤の維持</t>
+          <t>育成牛の飼養管理をサポート</t>
         </is>
       </c>
       <c r="I59" s="9" t="inlineStr">
         <is>
-          <t>営農部</t>
+          <t>農林課</t>
         </is>
       </c>
       <c r="J59" s="9" t="inlineStr">
         <is>
-          <t>担当者</t>
+          <t>管理者</t>
         </is>
       </c>
       <c r="K59" s="9" t="inlineStr">
@@ -11971,42 +12003,42 @@
       </c>
       <c r="B60" s="9" t="inlineStr">
         <is>
-          <t>JAわっかない</t>
+          <t>豊富町営牧場</t>
         </is>
       </c>
       <c r="D60" s="9" t="inlineStr">
         <is>
-          <t>北海道稚内市</t>
+          <t>北海道天塩郡豊富町</t>
         </is>
       </c>
       <c r="E60" s="9" t="inlineStr">
         <is>
-          <t>0162-33-5151</t>
+          <t>0162-82-1001</t>
         </is>
       </c>
       <c r="F60" s="9" t="inlineStr">
         <is>
-          <t>稚内市エリアの農業統括</t>
+          <t>町営の公共牧場</t>
         </is>
       </c>
       <c r="G60" s="9" t="inlineStr">
         <is>
-          <t>管内酪農家の労働環境改善</t>
+          <t>大規模な牧草地の維持</t>
         </is>
       </c>
       <c r="H60" s="9" t="inlineStr">
         <is>
-          <t>若手人材の供給ネットワーク構築</t>
+          <t>採用コスト不要の即戦力人材</t>
         </is>
       </c>
       <c r="I60" s="9" t="inlineStr">
         <is>
-          <t>営農部</t>
+          <t>農林水産課</t>
         </is>
       </c>
       <c r="J60" s="9" t="inlineStr">
         <is>
-          <t>担当者</t>
+          <t>管理者</t>
         </is>
       </c>
       <c r="K60" s="9" t="inlineStr">
@@ -12070,42 +12102,42 @@
       </c>
       <c r="B61" s="9" t="inlineStr">
         <is>
-          <t>JAるもい 本所</t>
+          <t>猿払村営牧場</t>
         </is>
       </c>
       <c r="D61" s="9" t="inlineStr">
         <is>
-          <t>北海道苫前郡羽幌町</t>
+          <t>北海道宗谷郡猿払村</t>
         </is>
       </c>
       <c r="E61" s="9" t="inlineStr">
         <is>
-          <t>0164-62-2141</t>
+          <t>01635-2-3131</t>
         </is>
       </c>
       <c r="F61" s="9" t="inlineStr">
         <is>
-          <t>留萌管内広域JA</t>
+          <t>村営の公共牧場</t>
         </is>
       </c>
       <c r="G61" s="9" t="inlineStr">
         <is>
-          <t>広域な組合員農家への支援拡充</t>
+          <t>酪農家からの育成牛管理</t>
         </is>
       </c>
       <c r="H61" s="9" t="inlineStr">
         <is>
-          <t>人材紹介サービスを利用したソリューション</t>
+          <t>育成牛管理における人員確保</t>
         </is>
       </c>
       <c r="I61" s="9" t="inlineStr">
         <is>
-          <t>営農部</t>
+          <t>農林課</t>
         </is>
       </c>
       <c r="J61" s="9" t="inlineStr">
         <is>
-          <t>担当者</t>
+          <t>管理者</t>
         </is>
       </c>
       <c r="K61" s="9" t="inlineStr">
@@ -12169,42 +12201,42 @@
       </c>
       <c r="B62" s="9" t="inlineStr">
         <is>
-          <t>JAるもい 遠別支所</t>
+          <t>名寄市営牧場</t>
         </is>
       </c>
       <c r="D62" s="9" t="inlineStr">
         <is>
-          <t>北海道天塩郡遠別町</t>
+          <t>北海道名寄市</t>
         </is>
       </c>
       <c r="E62" s="9" t="inlineStr">
         <is>
-          <t>01632-7-2511</t>
+          <t>01654-3-2111</t>
         </is>
       </c>
       <c r="F62" s="9" t="inlineStr">
         <is>
-          <t>留萌北部エリアの農業支援</t>
+          <t>市営の公共牧場</t>
         </is>
       </c>
       <c r="G62" s="9" t="inlineStr">
         <is>
-          <t>地域過疎化に伴う担い手不足</t>
+          <t>施設の労働力確保</t>
         </is>
       </c>
       <c r="H62" s="9" t="inlineStr">
         <is>
-          <t>長期就労可能な特定技能の提案</t>
+          <t>施設管理を即戦力として担う人材提供</t>
         </is>
       </c>
       <c r="I62" s="9" t="inlineStr">
         <is>
-          <t>営農課</t>
+          <t>農務課</t>
         </is>
       </c>
       <c r="J62" s="9" t="inlineStr">
         <is>
-          <t>担当者</t>
+          <t>管理者</t>
         </is>
       </c>
       <c r="K62" s="9" t="inlineStr">
@@ -12268,42 +12300,42 @@
       </c>
       <c r="B63" s="9" t="inlineStr">
         <is>
-          <t>JAふらの</t>
+          <t>剣淵町営牧場</t>
         </is>
       </c>
       <c r="D63" s="9" t="inlineStr">
         <is>
-          <t>北海道富良野市</t>
+          <t>北海道上川郡剣淵町</t>
         </is>
       </c>
       <c r="E63" s="9" t="inlineStr">
         <is>
-          <t>0167-23-3532</t>
+          <t>0165-34-2121</t>
         </is>
       </c>
       <c r="F63" s="9" t="inlineStr">
         <is>
-          <t>富良野エリアの農業統括</t>
+          <t>町営の公共牧場</t>
         </is>
       </c>
       <c r="G63" s="9" t="inlineStr">
         <is>
-          <t>複合農業における農繁期の重なり</t>
+          <t>放牧期間中の施設管理</t>
         </is>
       </c>
       <c r="H63" s="9" t="inlineStr">
         <is>
-          <t>柔軟に対応できる人材の管内配置</t>
+          <t>公共施設の安定稼働支援</t>
         </is>
       </c>
       <c r="I63" s="9" t="inlineStr">
         <is>
-          <t>営農部</t>
+          <t>農政課</t>
         </is>
       </c>
       <c r="J63" s="9" t="inlineStr">
         <is>
-          <t>担当者</t>
+          <t>管理者</t>
         </is>
       </c>
       <c r="K63" s="9" t="inlineStr">
@@ -12367,42 +12399,42 @@
       </c>
       <c r="B64" s="9" t="inlineStr">
         <is>
-          <t>JAあさひかわ</t>
+          <t>天塩町営牧場</t>
         </is>
       </c>
       <c r="D64" s="9" t="inlineStr">
         <is>
-          <t>北海道旭川市</t>
+          <t>北海道天塩郡天塩町</t>
         </is>
       </c>
       <c r="E64" s="9" t="inlineStr">
         <is>
-          <t>0166-48-5522</t>
+          <t>01632-2-1001</t>
         </is>
       </c>
       <c r="F64" s="9" t="inlineStr">
         <is>
-          <t>旭川エリアの農業統括</t>
+          <t>町営の公共牧場</t>
         </is>
       </c>
       <c r="G64" s="9" t="inlineStr">
         <is>
-          <t>都市近郊農業の維持と発展</t>
+          <t>広域な牧草地の管理作業</t>
         </is>
       </c>
       <c r="H64" s="9" t="inlineStr">
         <is>
-          <t>採用コスト不要の即戦力人材の提供</t>
+          <t>採用コストゼロで柔軟な即戦力</t>
         </is>
       </c>
       <c r="I64" s="9" t="inlineStr">
         <is>
-          <t>営農部</t>
+          <t>農林水産課</t>
         </is>
       </c>
       <c r="J64" s="9" t="inlineStr">
         <is>
-          <t>担当者</t>
+          <t>管理者</t>
         </is>
       </c>
       <c r="K64" s="9" t="inlineStr">
@@ -12466,42 +12498,42 @@
       </c>
       <c r="B65" s="9" t="inlineStr">
         <is>
-          <t>JAたいせつ</t>
+          <t>幌延町営牧場</t>
         </is>
       </c>
       <c r="D65" s="9" t="inlineStr">
         <is>
-          <t>北海道旭川市</t>
+          <t>北海道天塩郡幌延町</t>
         </is>
       </c>
       <c r="E65" s="9" t="inlineStr">
         <is>
-          <t>0166-57-2331</t>
+          <t>01632-5-1111</t>
         </is>
       </c>
       <c r="F65" s="9" t="inlineStr">
         <is>
-          <t>大雪エリアの農業統括</t>
+          <t>町営の公共牧場</t>
         </is>
       </c>
       <c r="G65" s="9" t="inlineStr">
         <is>
-          <t>人材不足解消策の提示</t>
+          <t>安定した育成環境の維持</t>
         </is>
       </c>
       <c r="H65" s="9" t="inlineStr">
         <is>
-          <t>営農基盤の維持に向けた人材案内</t>
+          <t>即戦力を配置しオペレーション実現</t>
         </is>
       </c>
       <c r="I65" s="9" t="inlineStr">
         <is>
-          <t>営農部</t>
+          <t>産業振興課</t>
         </is>
       </c>
       <c r="J65" s="9" t="inlineStr">
         <is>
-          <t>担当者</t>
+          <t>管理者</t>
         </is>
       </c>
       <c r="K65" s="9" t="inlineStr">
@@ -12565,42 +12597,42 @@
       </c>
       <c r="B66" s="9" t="inlineStr">
         <is>
-          <t>JAなよろ</t>
+          <t>上川町営牧場</t>
         </is>
       </c>
       <c r="D66" s="9" t="inlineStr">
         <is>
-          <t>北海道名寄市</t>
+          <t>北海道上川郡上川町</t>
         </is>
       </c>
       <c r="E66" s="9" t="inlineStr">
         <is>
-          <t>01654-2-2131</t>
+          <t>01658-2-4051</t>
         </is>
       </c>
       <c r="F66" s="9" t="inlineStr">
         <is>
-          <t>名寄エリアの農業統括</t>
+          <t>町営の公共牧場</t>
         </is>
       </c>
       <c r="G66" s="9" t="inlineStr">
         <is>
-          <t>畜産・酪農家向けの人材供給</t>
+          <t>自然環境下での牛群管理</t>
         </is>
       </c>
       <c r="H66" s="9" t="inlineStr">
         <is>
-          <t>定住型人材による地域振興</t>
+          <t>飼養管理をサポートする定住型人材</t>
         </is>
       </c>
       <c r="I66" s="9" t="inlineStr">
         <is>
-          <t>営農部</t>
+          <t>農林課</t>
         </is>
       </c>
       <c r="J66" s="9" t="inlineStr">
         <is>
-          <t>担当者</t>
+          <t>管理者</t>
         </is>
       </c>
       <c r="K66" s="9" t="inlineStr">
@@ -12664,42 +12696,42 @@
       </c>
       <c r="B67" s="9" t="inlineStr">
         <is>
-          <t>JA北ひびき</t>
+          <t>鷹栖町営牧場</t>
         </is>
       </c>
       <c r="D67" s="9" t="inlineStr">
         <is>
-          <t>北海道士別市</t>
+          <t>北海道上川郡鷹栖町</t>
         </is>
       </c>
       <c r="E67" s="9" t="inlineStr">
         <is>
-          <t>0165-23-2141</t>
+          <t>0166-87-2111</t>
         </is>
       </c>
       <c r="F67" s="9" t="inlineStr">
         <is>
-          <t>士別・剣淵エリア統括</t>
+          <t>町営の公共牧場</t>
         </is>
       </c>
       <c r="G67" s="9" t="inlineStr">
         <is>
-          <t>肉牛・酪農家への労働力底上げ</t>
+          <t>都市近郊での人材獲得競争</t>
         </is>
       </c>
       <c r="H67" s="9" t="inlineStr">
         <is>
-          <t>組合経由での労働力確保支援</t>
+          <t>コストをかけずに即戦力を確保</t>
         </is>
       </c>
       <c r="I67" s="9" t="inlineStr">
         <is>
-          <t>営農部</t>
+          <t>農業委員会</t>
         </is>
       </c>
       <c r="J67" s="9" t="inlineStr">
         <is>
-          <t>担当者</t>
+          <t>管理者</t>
         </is>
       </c>
       <c r="K67" s="9" t="inlineStr">
@@ -12763,42 +12795,42 @@
       </c>
       <c r="B68" s="9" t="inlineStr">
         <is>
-          <t>JAびえい</t>
+          <t>和寒町営牧場</t>
         </is>
       </c>
       <c r="D68" s="9" t="inlineStr">
         <is>
-          <t>北海道上川郡美瑛町</t>
+          <t>北海道上川郡和寒町</t>
         </is>
       </c>
       <c r="E68" s="9" t="inlineStr">
         <is>
-          <t>0166-92-3111</t>
+          <t>0165-32-2421</t>
         </is>
       </c>
       <c r="F68" s="9" t="inlineStr">
         <is>
-          <t>美瑛エリアの農業統括</t>
+          <t>町営の公共牧場</t>
         </is>
       </c>
       <c r="G68" s="9" t="inlineStr">
         <is>
-          <t>畑作と畜産の複合経営支援</t>
+          <t>夏季放牧管理の省力化</t>
         </is>
       </c>
       <c r="H68" s="9" t="inlineStr">
         <is>
-          <t>多様な作業に対応できる人材の提案</t>
+          <t>安定稼働を即戦力で支援</t>
         </is>
       </c>
       <c r="I68" s="9" t="inlineStr">
         <is>
-          <t>営農部</t>
+          <t>産業振興課</t>
         </is>
       </c>
       <c r="J68" s="9" t="inlineStr">
         <is>
-          <t>担当者</t>
+          <t>管理者</t>
         </is>
       </c>
       <c r="K68" s="9" t="inlineStr">
@@ -12862,42 +12894,42 @@
       </c>
       <c r="B69" s="9" t="inlineStr">
         <is>
-          <t>JA当麻</t>
+          <t>有限会社きしかわ畜産</t>
         </is>
       </c>
       <c r="D69" s="9" t="inlineStr">
         <is>
-          <t>北海道上川郡当麻町</t>
+          <t>北海道名寄市</t>
         </is>
       </c>
       <c r="E69" s="9" t="inlineStr">
         <is>
-          <t>0166-84-3311</t>
+          <t>01654-2-2555</t>
         </is>
       </c>
       <c r="F69" s="9" t="inlineStr">
         <is>
-          <t>当麻エリアの農業統括</t>
+          <t>素牛農家</t>
         </is>
       </c>
       <c r="G69" s="9" t="inlineStr">
         <is>
-          <t>安定した地域農業の担い手確保</t>
+          <t>現場作業の効率化</t>
         </is>
       </c>
       <c r="H69" s="9" t="inlineStr">
         <is>
-          <t>採用コストを抑えた人材紹介モデル</t>
+          <t>若手人材の紹介による基盤提供</t>
         </is>
       </c>
       <c r="I69" s="9" t="inlineStr">
         <is>
-          <t>営農部</t>
+          <t>経営陣</t>
         </is>
       </c>
       <c r="J69" s="9" t="inlineStr">
         <is>
-          <t>担当者</t>
+          <t>代表</t>
         </is>
       </c>
       <c r="K69" s="9" t="inlineStr">
@@ -12961,42 +12993,42 @@
       </c>
       <c r="B70" s="9" t="inlineStr">
         <is>
-          <t>ホクレン 旭川支所</t>
+          <t>株式会社大雪牧場</t>
         </is>
       </c>
       <c r="D70" s="9" t="inlineStr">
         <is>
-          <t>北海道旭川市</t>
+          <t>北海道上川郡上川町</t>
         </is>
       </c>
       <c r="E70" s="9" t="inlineStr">
         <is>
-          <t>0166-23-4171</t>
+          <t>不明</t>
         </is>
       </c>
       <c r="F70" s="9" t="inlineStr">
         <is>
-          <t>上川エリアのホクレン拠点</t>
+          <t>肉牛・乳牛生産</t>
         </is>
       </c>
       <c r="G70" s="9" t="inlineStr">
         <is>
-          <t>広域エリアの流通を支える基盤</t>
+          <t>多頭数飼育における日常業務</t>
         </is>
       </c>
       <c r="H70" s="9" t="inlineStr">
         <is>
-          <t>人材確保モデルの情報提供</t>
+          <t>給餌・清掃を担う即戦力人材</t>
         </is>
       </c>
       <c r="I70" s="9" t="inlineStr">
         <is>
-          <t>管理部</t>
+          <t>経営陣</t>
         </is>
       </c>
       <c r="J70" s="9" t="inlineStr">
         <is>
-          <t>担当者</t>
+          <t>代表</t>
         </is>
       </c>
       <c r="K70" s="9" t="inlineStr">
@@ -13053,89 +13085,40 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="9" t="inlineStr">
-        <is>
-          <t>道北</t>
-        </is>
-      </c>
-      <c r="B71" s="9" t="inlineStr">
-        <is>
-          <t>ホクレン 稚内支所</t>
-        </is>
-      </c>
-      <c r="D71" s="9" t="inlineStr">
-        <is>
-          <t>北海道稚内市</t>
-        </is>
-      </c>
-      <c r="E71" s="9" t="inlineStr">
-        <is>
-          <t>0162-23-3456</t>
-        </is>
-      </c>
-      <c r="F71" s="9" t="inlineStr">
-        <is>
-          <t>宗谷エリアのホクレン拠点</t>
-        </is>
-      </c>
-      <c r="G71" s="9" t="inlineStr">
-        <is>
-          <t>酪農地帯における集約的支援</t>
-        </is>
-      </c>
-      <c r="H71" s="9" t="inlineStr">
-        <is>
-          <t>メガファーム等への人材供給網構築</t>
-        </is>
-      </c>
-      <c r="I71" s="9" t="inlineStr">
-        <is>
-          <t>管理部</t>
-        </is>
-      </c>
-      <c r="J71" s="9" t="inlineStr">
-        <is>
-          <t>担当者</t>
-        </is>
-      </c>
-      <c r="K71" s="9" t="inlineStr">
-        <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="L71" s="9" t="inlineStr">
-        <is>
-          <t>未確認</t>
-        </is>
-      </c>
-      <c r="Q71" s="9" t="inlineStr">
-        <is>
-          <t>未開拓</t>
-        </is>
-      </c>
-      <c r="R71" s="9" t="inlineStr">
-        <is>
-          <t>ターゲット</t>
-        </is>
-      </c>
-      <c r="S71" s="9" t="inlineStr">
-        <is>
-          <t>リストアップ</t>
-        </is>
-      </c>
-      <c r="AG71" s="9" t="inlineStr">
-        <is>
-          <t>営業推進部</t>
-        </is>
-      </c>
-      <c r="AH71" s="9" t="inlineStr">
-        <is>
-          <t>武田 悦郎</t>
-        </is>
-      </c>
-      <c r="AN71" s="9" t="inlineStr">
-        <is>
-          <t>未定</t>
+      <c r="A71" s="15" t="inlineStr">
+        <is>
+          <t>道東(網走)</t>
+        </is>
+      </c>
+      <c r="B71" s="15" t="inlineStr">
+        <is>
+          <t>株式会社楠目牧場</t>
+        </is>
+      </c>
+      <c r="C71" s="15" t="inlineStr"/>
+      <c r="D71" s="15" t="inlineStr">
+        <is>
+          <t>北海道網走市字潮見213番地</t>
+        </is>
+      </c>
+      <c r="E71" s="15" t="inlineStr">
+        <is>
+          <t>※要確認</t>
+        </is>
+      </c>
+      <c r="F71" s="15" t="inlineStr">
+        <is>
+          <t>網走市の畜産経営/オホーツク海近郊</t>
+        </is>
+      </c>
+      <c r="G71" s="15" t="inlineStr">
+        <is>
+          <t>労働力確保と日常飼養管理</t>
+        </is>
+      </c>
+      <c r="H71" s="15" t="inlineStr">
+        <is>
+          <t>採用コストを抑えた即戦力人材の提供</t>
         </is>
       </c>
       <c r="AQ71">
@@ -13152,89 +13135,44 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="9" t="inlineStr">
-        <is>
-          <t>道北</t>
-        </is>
-      </c>
-      <c r="B72" s="9" t="inlineStr">
-        <is>
-          <t>北海道農政事務所 旭川支局</t>
-        </is>
-      </c>
-      <c r="D72" s="9" t="inlineStr">
-        <is>
-          <t>北海道旭川市</t>
-        </is>
-      </c>
-      <c r="E72" s="9" t="inlineStr">
-        <is>
-          <t>0166-22-2615</t>
-        </is>
-      </c>
-      <c r="F72" s="9" t="inlineStr">
-        <is>
-          <t>行政機関</t>
-        </is>
-      </c>
-      <c r="G72" s="9" t="inlineStr">
-        <is>
-          <t>地域の畜産環境整備</t>
-        </is>
-      </c>
-      <c r="H72" s="9" t="inlineStr">
-        <is>
-          <t>人材不足解消ソリューションとしての情報提供</t>
-        </is>
-      </c>
-      <c r="I72" s="9" t="inlineStr">
-        <is>
-          <t>農政推進</t>
-        </is>
-      </c>
-      <c r="J72" s="9" t="inlineStr">
-        <is>
-          <t>担当者</t>
-        </is>
-      </c>
-      <c r="K72" s="9" t="inlineStr">
-        <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="L72" s="9" t="inlineStr">
-        <is>
-          <t>未確認</t>
-        </is>
-      </c>
-      <c r="Q72" s="9" t="inlineStr">
-        <is>
-          <t>未開拓</t>
-        </is>
-      </c>
-      <c r="R72" s="9" t="inlineStr">
-        <is>
-          <t>ターゲット</t>
-        </is>
-      </c>
-      <c r="S72" s="9" t="inlineStr">
-        <is>
-          <t>リストアップ</t>
-        </is>
-      </c>
-      <c r="AG72" s="9" t="inlineStr">
-        <is>
-          <t>営業推進部</t>
-        </is>
-      </c>
-      <c r="AH72" s="9" t="inlineStr">
-        <is>
-          <t>武田 悦郎</t>
-        </is>
-      </c>
-      <c r="AN72" s="9" t="inlineStr">
-        <is>
-          <t>未定</t>
+      <c r="A72" s="15" t="inlineStr">
+        <is>
+          <t>道東(網走)</t>
+        </is>
+      </c>
+      <c r="B72" s="15" t="inlineStr">
+        <is>
+          <t>有限会社網走原生牧場観光センター</t>
+        </is>
+      </c>
+      <c r="C72" s="16" t="inlineStr">
+        <is>
+          <t>http://www.genseibokujou.co.jp/</t>
+        </is>
+      </c>
+      <c r="D72" s="15" t="inlineStr">
+        <is>
+          <t>北海道網走市藻琴225番地</t>
+        </is>
+      </c>
+      <c r="E72" s="15" t="inlineStr">
+        <is>
+          <t>0152-46-2121</t>
+        </is>
+      </c>
+      <c r="F72" s="15" t="inlineStr">
+        <is>
+          <t>観光牧場/乗馬体験/ホーストレッキング</t>
+        </is>
+      </c>
+      <c r="G72" s="15" t="inlineStr">
+        <is>
+          <t>観光対応と飼養管理の両立</t>
+        </is>
+      </c>
+      <c r="H72" s="15" t="inlineStr">
+        <is>
+          <t>バックヤード飼育を即戦力に任せ、接客・観光サービスに注力できる体制構築</t>
         </is>
       </c>
       <c r="AQ72">
@@ -13251,89 +13189,44 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="9" t="inlineStr">
-        <is>
-          <t>道北</t>
-        </is>
-      </c>
-      <c r="B73" s="9" t="inlineStr">
-        <is>
-          <t>旭川市営牧場</t>
-        </is>
-      </c>
-      <c r="D73" s="9" t="inlineStr">
-        <is>
-          <t>北海道旭川市</t>
-        </is>
-      </c>
-      <c r="E73" s="9" t="inlineStr">
-        <is>
-          <t>0166-25-7427</t>
-        </is>
-      </c>
-      <c r="F73" s="9" t="inlineStr">
-        <is>
-          <t>市営の公共牧場</t>
-        </is>
-      </c>
-      <c r="G73" s="9" t="inlineStr">
-        <is>
-          <t>公共施設の放牧管理</t>
-        </is>
-      </c>
-      <c r="H73" s="9" t="inlineStr">
-        <is>
-          <t>施設の安定稼働を即戦力で支援</t>
-        </is>
-      </c>
-      <c r="I73" s="9" t="inlineStr">
-        <is>
-          <t>農林部</t>
-        </is>
-      </c>
-      <c r="J73" s="9" t="inlineStr">
-        <is>
-          <t>管理者</t>
-        </is>
-      </c>
-      <c r="K73" s="9" t="inlineStr">
-        <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="L73" s="9" t="inlineStr">
-        <is>
-          <t>未確認</t>
-        </is>
-      </c>
-      <c r="Q73" s="9" t="inlineStr">
-        <is>
-          <t>未開拓</t>
-        </is>
-      </c>
-      <c r="R73" s="9" t="inlineStr">
-        <is>
-          <t>ターゲット</t>
-        </is>
-      </c>
-      <c r="S73" s="9" t="inlineStr">
-        <is>
-          <t>リストアップ</t>
-        </is>
-      </c>
-      <c r="AG73" s="9" t="inlineStr">
-        <is>
-          <t>営業推進部</t>
-        </is>
-      </c>
-      <c r="AH73" s="9" t="inlineStr">
-        <is>
-          <t>武田 悦郎</t>
-        </is>
-      </c>
-      <c r="AN73" s="9" t="inlineStr">
-        <is>
-          <t>未定</t>
+      <c r="A73" s="15" t="inlineStr">
+        <is>
+          <t>道東(北見)</t>
+        </is>
+      </c>
+      <c r="B73" s="15" t="inlineStr">
+        <is>
+          <t>株式会社協同畜産経営センター</t>
+        </is>
+      </c>
+      <c r="C73" s="16" t="inlineStr">
+        <is>
+          <t>https://www.hokkaido-pork.jp/farm/feedone/farm_kyodo/</t>
+        </is>
+      </c>
+      <c r="D73" s="15" t="inlineStr">
+        <is>
+          <t>北海道北見市大正763番地</t>
+        </is>
+      </c>
+      <c r="E73" s="15" t="inlineStr">
+        <is>
+          <t>0157-36-6006</t>
+        </is>
+      </c>
+      <c r="F73" s="15" t="inlineStr">
+        <is>
+          <t>オニオンポーク生産/繁殖550頭一貫生産</t>
+        </is>
+      </c>
+      <c r="G73" s="15" t="inlineStr">
+        <is>
+          <t>大規模養豚における安定的な人員配置</t>
+        </is>
+      </c>
+      <c r="H73" s="15" t="inlineStr">
+        <is>
+          <t>養豚現場で即戦力となる特定技能人材の配置でブランド維持を支援</t>
         </is>
       </c>
       <c r="AQ73">
@@ -13350,89 +13243,44 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="9" t="inlineStr">
-        <is>
-          <t>道北</t>
-        </is>
-      </c>
-      <c r="B74" s="9" t="inlineStr">
-        <is>
-          <t>士別市営天塩川牧場</t>
-        </is>
-      </c>
-      <c r="D74" s="9" t="inlineStr">
-        <is>
-          <t>北海道士別市</t>
-        </is>
-      </c>
-      <c r="E74" s="9" t="inlineStr">
-        <is>
-          <t>0165-23-3121</t>
-        </is>
-      </c>
-      <c r="F74" s="9" t="inlineStr">
-        <is>
-          <t>市営の育成牧場</t>
-        </is>
-      </c>
-      <c r="G74" s="9" t="inlineStr">
-        <is>
-          <t>預託牛の体調管理</t>
-        </is>
-      </c>
-      <c r="H74" s="9" t="inlineStr">
-        <is>
-          <t>育成牛の飼養管理をサポート</t>
-        </is>
-      </c>
-      <c r="I74" s="9" t="inlineStr">
-        <is>
-          <t>農林課</t>
-        </is>
-      </c>
-      <c r="J74" s="9" t="inlineStr">
-        <is>
-          <t>管理者</t>
-        </is>
-      </c>
-      <c r="K74" s="9" t="inlineStr">
-        <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="L74" s="9" t="inlineStr">
-        <is>
-          <t>未確認</t>
-        </is>
-      </c>
-      <c r="Q74" s="9" t="inlineStr">
-        <is>
-          <t>未開拓</t>
-        </is>
-      </c>
-      <c r="R74" s="9" t="inlineStr">
-        <is>
-          <t>ターゲット</t>
-        </is>
-      </c>
-      <c r="S74" s="9" t="inlineStr">
-        <is>
-          <t>リストアップ</t>
-        </is>
-      </c>
-      <c r="AG74" s="9" t="inlineStr">
-        <is>
-          <t>営業推進部</t>
-        </is>
-      </c>
-      <c r="AH74" s="9" t="inlineStr">
-        <is>
-          <t>武田 悦郎</t>
-        </is>
-      </c>
-      <c r="AN74" s="9" t="inlineStr">
-        <is>
-          <t>未定</t>
+      <c r="A74" s="15" t="inlineStr">
+        <is>
+          <t>道東(北見)</t>
+        </is>
+      </c>
+      <c r="B74" s="15" t="inlineStr">
+        <is>
+          <t>株式会社北きつね牧場</t>
+        </is>
+      </c>
+      <c r="C74" s="16" t="inlineStr">
+        <is>
+          <t>https://kitakitsune-farm.com/</t>
+        </is>
+      </c>
+      <c r="D74" s="15" t="inlineStr">
+        <is>
+          <t>北海道北見市留辺蘂町花丘52-1</t>
+        </is>
+      </c>
+      <c r="E74" s="15" t="inlineStr">
+        <is>
+          <t>0157-45-2249</t>
+        </is>
+      </c>
+      <c r="F74" s="15" t="inlineStr">
+        <is>
+          <t>観光牧場/キタキツネ・エゾタヌキ飼育</t>
+        </is>
+      </c>
+      <c r="G74" s="15" t="inlineStr">
+        <is>
+          <t>観光来場者対応と動物飼育の兼務</t>
+        </is>
+      </c>
+      <c r="H74" s="15" t="inlineStr">
+        <is>
+          <t>飼育管理を即戦力が担い、接客・施設運営に注力できる体制構築</t>
         </is>
       </c>
       <c r="AQ74">
@@ -13449,89 +13297,44 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="9" t="inlineStr">
-        <is>
-          <t>道北</t>
-        </is>
-      </c>
-      <c r="B75" s="9" t="inlineStr">
-        <is>
-          <t>豊富町営牧場</t>
-        </is>
-      </c>
-      <c r="D75" s="9" t="inlineStr">
-        <is>
-          <t>北海道天塩郡豊富町</t>
-        </is>
-      </c>
-      <c r="E75" s="9" t="inlineStr">
-        <is>
-          <t>0162-82-1001</t>
-        </is>
-      </c>
-      <c r="F75" s="9" t="inlineStr">
-        <is>
-          <t>町営の公共牧場</t>
-        </is>
-      </c>
-      <c r="G75" s="9" t="inlineStr">
-        <is>
-          <t>大規模な牧草地の維持</t>
-        </is>
-      </c>
-      <c r="H75" s="9" t="inlineStr">
-        <is>
-          <t>採用コスト不要の即戦力人材</t>
-        </is>
-      </c>
-      <c r="I75" s="9" t="inlineStr">
-        <is>
-          <t>農林水産課</t>
-        </is>
-      </c>
-      <c r="J75" s="9" t="inlineStr">
-        <is>
-          <t>管理者</t>
-        </is>
-      </c>
-      <c r="K75" s="9" t="inlineStr">
-        <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="L75" s="9" t="inlineStr">
-        <is>
-          <t>未確認</t>
-        </is>
-      </c>
-      <c r="Q75" s="9" t="inlineStr">
-        <is>
-          <t>未開拓</t>
-        </is>
-      </c>
-      <c r="R75" s="9" t="inlineStr">
-        <is>
-          <t>ターゲット</t>
-        </is>
-      </c>
-      <c r="S75" s="9" t="inlineStr">
-        <is>
-          <t>リストアップ</t>
-        </is>
-      </c>
-      <c r="AG75" s="9" t="inlineStr">
-        <is>
-          <t>営業推進部</t>
-        </is>
-      </c>
-      <c r="AH75" s="9" t="inlineStr">
-        <is>
-          <t>武田 悦郎</t>
-        </is>
-      </c>
-      <c r="AN75" s="9" t="inlineStr">
-        <is>
-          <t>未定</t>
+      <c r="A75" s="15" t="inlineStr">
+        <is>
+          <t>道東(美幌)</t>
+        </is>
+      </c>
+      <c r="B75" s="15" t="inlineStr">
+        <is>
+          <t>株式会社美幌牛肥育センター</t>
+        </is>
+      </c>
+      <c r="C75" s="16" t="inlineStr">
+        <is>
+          <t>http://www.bihoro-gyu.com/</t>
+        </is>
+      </c>
+      <c r="D75" s="15" t="inlineStr">
+        <is>
+          <t>北海道網走郡美幌町字都橋211番地</t>
+        </is>
+      </c>
+      <c r="E75" s="15" t="inlineStr">
+        <is>
+          <t>0152-72-3373</t>
+        </is>
+      </c>
+      <c r="F75" s="15" t="inlineStr">
+        <is>
+          <t>ブランド牛「びほろ牛」肥育/肉牛飼育・販売・堆肥販売</t>
+        </is>
+      </c>
+      <c r="G75" s="15" t="inlineStr">
+        <is>
+          <t>ブランド維持のための丁寧な肥育管理と人員確保</t>
+        </is>
+      </c>
+      <c r="H75" s="15" t="inlineStr">
+        <is>
+          <t>肥育ルーティンを即戦力で支援しブランド維持に貢献</t>
         </is>
       </c>
       <c r="AQ75">
@@ -13548,89 +13351,44 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="9" t="inlineStr">
-        <is>
-          <t>道北</t>
-        </is>
-      </c>
-      <c r="B76" s="9" t="inlineStr">
-        <is>
-          <t>猿払村営牧場</t>
-        </is>
-      </c>
-      <c r="D76" s="9" t="inlineStr">
-        <is>
-          <t>北海道宗谷郡猿払村</t>
-        </is>
-      </c>
-      <c r="E76" s="9" t="inlineStr">
-        <is>
-          <t>01635-2-3131</t>
-        </is>
-      </c>
-      <c r="F76" s="9" t="inlineStr">
-        <is>
-          <t>村営の公共牧場</t>
-        </is>
-      </c>
-      <c r="G76" s="9" t="inlineStr">
-        <is>
-          <t>酪農家からの育成牛管理</t>
-        </is>
-      </c>
-      <c r="H76" s="9" t="inlineStr">
-        <is>
-          <t>育成牛管理における人員確保</t>
-        </is>
-      </c>
-      <c r="I76" s="9" t="inlineStr">
-        <is>
-          <t>農林課</t>
-        </is>
-      </c>
-      <c r="J76" s="9" t="inlineStr">
-        <is>
-          <t>管理者</t>
-        </is>
-      </c>
-      <c r="K76" s="9" t="inlineStr">
-        <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="L76" s="9" t="inlineStr">
-        <is>
-          <t>未確認</t>
-        </is>
-      </c>
-      <c r="Q76" s="9" t="inlineStr">
-        <is>
-          <t>未開拓</t>
-        </is>
-      </c>
-      <c r="R76" s="9" t="inlineStr">
-        <is>
-          <t>ターゲット</t>
-        </is>
-      </c>
-      <c r="S76" s="9" t="inlineStr">
-        <is>
-          <t>リストアップ</t>
-        </is>
-      </c>
-      <c r="AG76" s="9" t="inlineStr">
-        <is>
-          <t>営業推進部</t>
-        </is>
-      </c>
-      <c r="AH76" s="9" t="inlineStr">
-        <is>
-          <t>武田 悦郎</t>
-        </is>
-      </c>
-      <c r="AN76" s="9" t="inlineStr">
-        <is>
-          <t>未定</t>
+      <c r="A76" s="15" t="inlineStr">
+        <is>
+          <t>道東(美幌)</t>
+        </is>
+      </c>
+      <c r="B76" s="15" t="inlineStr">
+        <is>
+          <t>株式会社美幌ファーム</t>
+        </is>
+      </c>
+      <c r="C76" s="15" t="inlineStr">
+        <is>
+          <t>※要確認</t>
+        </is>
+      </c>
+      <c r="D76" s="15" t="inlineStr">
+        <is>
+          <t>北海道網走郡美幌町 ※詳細要確認</t>
+        </is>
+      </c>
+      <c r="E76" s="15" t="inlineStr">
+        <is>
+          <t>※要確認</t>
+        </is>
+      </c>
+      <c r="F76" s="15" t="inlineStr">
+        <is>
+          <t>びほろ牛の素牛育成(6-12カ月齢)/美幌牛肥育センター系列</t>
+        </is>
+      </c>
+      <c r="G76" s="15" t="inlineStr">
+        <is>
+          <t>グループ会社との連携と素牛育成の労働力確保</t>
+        </is>
+      </c>
+      <c r="H76" s="15" t="inlineStr">
+        <is>
+          <t>系列会社と一体での人材紹介、安定した育成オペレーション支援</t>
         </is>
       </c>
       <c r="AQ76">
@@ -13647,89 +13405,44 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="9" t="inlineStr">
-        <is>
-          <t>道北</t>
-        </is>
-      </c>
-      <c r="B77" s="9" t="inlineStr">
-        <is>
-          <t>名寄市営牧場</t>
-        </is>
-      </c>
-      <c r="D77" s="9" t="inlineStr">
-        <is>
-          <t>北海道名寄市</t>
-        </is>
-      </c>
-      <c r="E77" s="9" t="inlineStr">
-        <is>
-          <t>01654-3-2111</t>
-        </is>
-      </c>
-      <c r="F77" s="9" t="inlineStr">
-        <is>
-          <t>市営の公共牧場</t>
-        </is>
-      </c>
-      <c r="G77" s="9" t="inlineStr">
-        <is>
-          <t>施設の労働力確保</t>
-        </is>
-      </c>
-      <c r="H77" s="9" t="inlineStr">
-        <is>
-          <t>施設管理を即戦力として担う人材提供</t>
-        </is>
-      </c>
-      <c r="I77" s="9" t="inlineStr">
-        <is>
-          <t>農務課</t>
-        </is>
-      </c>
-      <c r="J77" s="9" t="inlineStr">
-        <is>
-          <t>管理者</t>
-        </is>
-      </c>
-      <c r="K77" s="9" t="inlineStr">
-        <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="L77" s="9" t="inlineStr">
-        <is>
-          <t>未確認</t>
-        </is>
-      </c>
-      <c r="Q77" s="9" t="inlineStr">
-        <is>
-          <t>未開拓</t>
-        </is>
-      </c>
-      <c r="R77" s="9" t="inlineStr">
-        <is>
-          <t>ターゲット</t>
-        </is>
-      </c>
-      <c r="S77" s="9" t="inlineStr">
-        <is>
-          <t>リストアップ</t>
-        </is>
-      </c>
-      <c r="AG77" s="9" t="inlineStr">
-        <is>
-          <t>営業推進部</t>
-        </is>
-      </c>
-      <c r="AH77" s="9" t="inlineStr">
-        <is>
-          <t>武田 悦郎</t>
-        </is>
-      </c>
-      <c r="AN77" s="9" t="inlineStr">
-        <is>
-          <t>未定</t>
+      <c r="A77" s="15" t="inlineStr">
+        <is>
+          <t>道東(斜里)</t>
+        </is>
+      </c>
+      <c r="B77" s="15" t="inlineStr">
+        <is>
+          <t>有限会社佐々木種畜牧場</t>
+        </is>
+      </c>
+      <c r="C77" s="16" t="inlineStr">
+        <is>
+          <t>https://sasaki-web.net/</t>
+        </is>
+      </c>
+      <c r="D77" s="15" t="inlineStr">
+        <is>
+          <t>北海道斜里郡斜里町字美咲69</t>
+        </is>
+      </c>
+      <c r="E77" s="15" t="inlineStr">
+        <is>
+          <t>0152-23-0429</t>
+        </is>
+      </c>
+      <c r="F77" s="15" t="inlineStr">
+        <is>
+          <t>サチク麦王ブランド豚/麦主体飼料/直売店併設</t>
+        </is>
+      </c>
+      <c r="G77" s="15" t="inlineStr">
+        <is>
+          <t>養豚と直売店の両立</t>
+        </is>
+      </c>
+      <c r="H77" s="15" t="inlineStr">
+        <is>
+          <t>養豚現場の即戦力配置で代表が販売・加工に注力できる体制構築</t>
         </is>
       </c>
       <c r="AQ77">
@@ -13746,89 +13459,40 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="9" t="inlineStr">
-        <is>
-          <t>道北</t>
-        </is>
-      </c>
-      <c r="B78" s="9" t="inlineStr">
-        <is>
-          <t>剣淵町営牧場</t>
-        </is>
-      </c>
-      <c r="D78" s="9" t="inlineStr">
-        <is>
-          <t>北海道上川郡剣淵町</t>
-        </is>
-      </c>
-      <c r="E78" s="9" t="inlineStr">
-        <is>
-          <t>0165-34-2121</t>
-        </is>
-      </c>
-      <c r="F78" s="9" t="inlineStr">
-        <is>
-          <t>町営の公共牧場</t>
-        </is>
-      </c>
-      <c r="G78" s="9" t="inlineStr">
-        <is>
-          <t>放牧期間中の施設管理</t>
-        </is>
-      </c>
-      <c r="H78" s="9" t="inlineStr">
-        <is>
-          <t>公共施設の安定稼働支援</t>
-        </is>
-      </c>
-      <c r="I78" s="9" t="inlineStr">
-        <is>
-          <t>農政課</t>
-        </is>
-      </c>
-      <c r="J78" s="9" t="inlineStr">
-        <is>
-          <t>管理者</t>
-        </is>
-      </c>
-      <c r="K78" s="9" t="inlineStr">
-        <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="L78" s="9" t="inlineStr">
-        <is>
-          <t>未確認</t>
-        </is>
-      </c>
-      <c r="Q78" s="9" t="inlineStr">
-        <is>
-          <t>未開拓</t>
-        </is>
-      </c>
-      <c r="R78" s="9" t="inlineStr">
-        <is>
-          <t>ターゲット</t>
-        </is>
-      </c>
-      <c r="S78" s="9" t="inlineStr">
-        <is>
-          <t>リストアップ</t>
-        </is>
-      </c>
-      <c r="AG78" s="9" t="inlineStr">
-        <is>
-          <t>営業推進部</t>
-        </is>
-      </c>
-      <c r="AH78" s="9" t="inlineStr">
-        <is>
-          <t>武田 悦郎</t>
-        </is>
-      </c>
-      <c r="AN78" s="9" t="inlineStr">
-        <is>
-          <t>未定</t>
+      <c r="A78" s="15" t="inlineStr">
+        <is>
+          <t>道東(網走)</t>
+        </is>
+      </c>
+      <c r="B78" s="15" t="inlineStr">
+        <is>
+          <t>株式会社オホーツクファーム33</t>
+        </is>
+      </c>
+      <c r="C78" s="15" t="inlineStr"/>
+      <c r="D78" s="15" t="inlineStr">
+        <is>
+          <t>北海道網走市字北浜273番地の4</t>
+        </is>
+      </c>
+      <c r="E78" s="15" t="inlineStr">
+        <is>
+          <t>※要確認</t>
+        </is>
+      </c>
+      <c r="F78" s="15" t="inlineStr">
+        <is>
+          <t>網走市での牧場経営</t>
+        </is>
+      </c>
+      <c r="G78" s="15" t="inlineStr">
+        <is>
+          <t>日常飼養管理の労働力確保</t>
+        </is>
+      </c>
+      <c r="H78" s="15" t="inlineStr">
+        <is>
+          <t>採用コストを抑えた即戦力人材の提供</t>
         </is>
       </c>
       <c r="AQ78">
@@ -13845,89 +13509,40 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="9" t="inlineStr">
-        <is>
-          <t>道北</t>
-        </is>
-      </c>
-      <c r="B79" s="9" t="inlineStr">
-        <is>
-          <t>天塩町営牧場</t>
-        </is>
-      </c>
-      <c r="D79" s="9" t="inlineStr">
-        <is>
-          <t>北海道天塩郡天塩町</t>
-        </is>
-      </c>
-      <c r="E79" s="9" t="inlineStr">
-        <is>
-          <t>01632-2-1001</t>
-        </is>
-      </c>
-      <c r="F79" s="9" t="inlineStr">
-        <is>
-          <t>町営の公共牧場</t>
-        </is>
-      </c>
-      <c r="G79" s="9" t="inlineStr">
-        <is>
-          <t>広域な牧草地の管理作業</t>
-        </is>
-      </c>
-      <c r="H79" s="9" t="inlineStr">
-        <is>
-          <t>採用コストゼロで柔軟な即戦力</t>
-        </is>
-      </c>
-      <c r="I79" s="9" t="inlineStr">
-        <is>
-          <t>農林水産課</t>
-        </is>
-      </c>
-      <c r="J79" s="9" t="inlineStr">
-        <is>
-          <t>管理者</t>
-        </is>
-      </c>
-      <c r="K79" s="9" t="inlineStr">
-        <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="L79" s="9" t="inlineStr">
-        <is>
-          <t>未確認</t>
-        </is>
-      </c>
-      <c r="Q79" s="9" t="inlineStr">
-        <is>
-          <t>未開拓</t>
-        </is>
-      </c>
-      <c r="R79" s="9" t="inlineStr">
-        <is>
-          <t>ターゲット</t>
-        </is>
-      </c>
-      <c r="S79" s="9" t="inlineStr">
-        <is>
-          <t>リストアップ</t>
-        </is>
-      </c>
-      <c r="AG79" s="9" t="inlineStr">
-        <is>
-          <t>営業推進部</t>
-        </is>
-      </c>
-      <c r="AH79" s="9" t="inlineStr">
-        <is>
-          <t>武田 悦郎</t>
-        </is>
-      </c>
-      <c r="AN79" s="9" t="inlineStr">
-        <is>
-          <t>未定</t>
+      <c r="A79" s="15" t="inlineStr">
+        <is>
+          <t>道東(網走)</t>
+        </is>
+      </c>
+      <c r="B79" s="15" t="inlineStr">
+        <is>
+          <t>有限会社網走ふる里牧場</t>
+        </is>
+      </c>
+      <c r="C79" s="15" t="inlineStr"/>
+      <c r="D79" s="15" t="inlineStr">
+        <is>
+          <t>北海道網走市字稲富83</t>
+        </is>
+      </c>
+      <c r="E79" s="14" t="inlineStr">
+        <is>
+          <t>0152-46-2402</t>
+        </is>
+      </c>
+      <c r="F79" s="15" t="inlineStr">
+        <is>
+          <t>網走市の畜産業</t>
+        </is>
+      </c>
+      <c r="G79" s="15" t="inlineStr">
+        <is>
+          <t>通常飼養管理の担い手不足</t>
+        </is>
+      </c>
+      <c r="H79" s="15" t="inlineStr">
+        <is>
+          <t>即戦力配置による飼養管理の安定化</t>
         </is>
       </c>
       <c r="AQ79">
@@ -13944,89 +13559,44 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="9" t="inlineStr">
-        <is>
-          <t>道北</t>
-        </is>
-      </c>
-      <c r="B80" s="9" t="inlineStr">
-        <is>
-          <t>幌延町営牧場</t>
-        </is>
-      </c>
-      <c r="D80" s="9" t="inlineStr">
-        <is>
-          <t>北海道天塩郡幌延町</t>
-        </is>
-      </c>
-      <c r="E80" s="9" t="inlineStr">
-        <is>
-          <t>01632-5-1111</t>
-        </is>
-      </c>
-      <c r="F80" s="9" t="inlineStr">
-        <is>
-          <t>町営の公共牧場</t>
-        </is>
-      </c>
-      <c r="G80" s="9" t="inlineStr">
-        <is>
-          <t>安定した育成環境の維持</t>
-        </is>
-      </c>
-      <c r="H80" s="9" t="inlineStr">
-        <is>
-          <t>即戦力を配置しオペレーション実現</t>
-        </is>
-      </c>
-      <c r="I80" s="9" t="inlineStr">
-        <is>
-          <t>産業振興課</t>
-        </is>
-      </c>
-      <c r="J80" s="9" t="inlineStr">
-        <is>
-          <t>管理者</t>
-        </is>
-      </c>
-      <c r="K80" s="9" t="inlineStr">
-        <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="L80" s="9" t="inlineStr">
-        <is>
-          <t>未確認</t>
-        </is>
-      </c>
-      <c r="Q80" s="9" t="inlineStr">
-        <is>
-          <t>未開拓</t>
-        </is>
-      </c>
-      <c r="R80" s="9" t="inlineStr">
-        <is>
-          <t>ターゲット</t>
-        </is>
-      </c>
-      <c r="S80" s="9" t="inlineStr">
-        <is>
-          <t>リストアップ</t>
-        </is>
-      </c>
-      <c r="AG80" s="9" t="inlineStr">
-        <is>
-          <t>営業推進部</t>
-        </is>
-      </c>
-      <c r="AH80" s="9" t="inlineStr">
-        <is>
-          <t>武田 悦郎</t>
-        </is>
-      </c>
-      <c r="AN80" s="9" t="inlineStr">
-        <is>
-          <t>未定</t>
+      <c r="A80" s="15" t="inlineStr">
+        <is>
+          <t>道東(大空)</t>
+        </is>
+      </c>
+      <c r="B80" s="15" t="inlineStr">
+        <is>
+          <t>株式会社北海道畜産公社 道東事業所 北見工場</t>
+        </is>
+      </c>
+      <c r="C80" s="16" t="inlineStr">
+        <is>
+          <t>https://tikusan.securesite.jp/</t>
+        </is>
+      </c>
+      <c r="D80" s="15" t="inlineStr">
+        <is>
+          <t>北海道網走郡大空町東藻琴西倉280-3 (〒099-3202)</t>
+        </is>
+      </c>
+      <c r="E80" s="15" t="inlineStr">
+        <is>
+          <t>※要確認</t>
+        </is>
+      </c>
+      <c r="F80" s="15" t="inlineStr">
+        <is>
+          <t>オホーツク地区主要食肉処理工場/牛・豚加工/海外輸出認定</t>
+        </is>
+      </c>
+      <c r="G80" s="15" t="inlineStr">
+        <is>
+          <t>大規模食肉処理ラインにおける慢性的人員不足</t>
+        </is>
+      </c>
+      <c r="H80" s="15" t="inlineStr">
+        <is>
+          <t>食肉加工現場で即戦力となる特定技能人材を通年で提供</t>
         </is>
       </c>
       <c r="AQ80">
@@ -14043,89 +13613,44 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="9" t="inlineStr">
-        <is>
-          <t>道北</t>
-        </is>
-      </c>
-      <c r="B81" s="9" t="inlineStr">
-        <is>
-          <t>上川町営牧場</t>
-        </is>
-      </c>
-      <c r="D81" s="9" t="inlineStr">
-        <is>
-          <t>北海道上川郡上川町</t>
-        </is>
-      </c>
-      <c r="E81" s="9" t="inlineStr">
-        <is>
-          <t>01658-2-4051</t>
-        </is>
-      </c>
-      <c r="F81" s="9" t="inlineStr">
-        <is>
-          <t>町営の公共牧場</t>
-        </is>
-      </c>
-      <c r="G81" s="9" t="inlineStr">
-        <is>
-          <t>自然環境下での牛群管理</t>
-        </is>
-      </c>
-      <c r="H81" s="9" t="inlineStr">
-        <is>
-          <t>飼養管理をサポートする定住型人材</t>
-        </is>
-      </c>
-      <c r="I81" s="9" t="inlineStr">
-        <is>
-          <t>農林課</t>
-        </is>
-      </c>
-      <c r="J81" s="9" t="inlineStr">
-        <is>
-          <t>管理者</t>
-        </is>
-      </c>
-      <c r="K81" s="9" t="inlineStr">
-        <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="L81" s="9" t="inlineStr">
-        <is>
-          <t>未確認</t>
-        </is>
-      </c>
-      <c r="Q81" s="9" t="inlineStr">
-        <is>
-          <t>未開拓</t>
-        </is>
-      </c>
-      <c r="R81" s="9" t="inlineStr">
-        <is>
-          <t>ターゲット</t>
-        </is>
-      </c>
-      <c r="S81" s="9" t="inlineStr">
-        <is>
-          <t>リストアップ</t>
-        </is>
-      </c>
-      <c r="AG81" s="9" t="inlineStr">
-        <is>
-          <t>営業推進部</t>
-        </is>
-      </c>
-      <c r="AH81" s="9" t="inlineStr">
-        <is>
-          <t>武田 悦郎</t>
-        </is>
-      </c>
-      <c r="AN81" s="9" t="inlineStr">
-        <is>
-          <t>未定</t>
+      <c r="A81" s="15" t="inlineStr">
+        <is>
+          <t>道東(大空)</t>
+        </is>
+      </c>
+      <c r="B81" s="15" t="inlineStr">
+        <is>
+          <t>有限会社山口ファーム</t>
+        </is>
+      </c>
+      <c r="C81" s="16" t="inlineStr">
+        <is>
+          <t>https://www.yamaguchifarm.com/</t>
+        </is>
+      </c>
+      <c r="D81" s="15" t="inlineStr">
+        <is>
+          <t>北海道網走郡大空町東藻琴末広92番地 (〒099-3232)</t>
+        </is>
+      </c>
+      <c r="E81" s="15" t="inlineStr">
+        <is>
+          <t>0152-66-3434</t>
+        </is>
+      </c>
+      <c r="F81" s="15" t="inlineStr">
+        <is>
+          <t>大空町東藻琴の農場経営</t>
+        </is>
+      </c>
+      <c r="G81" s="15" t="inlineStr">
+        <is>
+          <t>農繁期の労働力確保</t>
+        </is>
+      </c>
+      <c r="H81" s="15" t="inlineStr">
+        <is>
+          <t>即戦力人材による農作業の安定化</t>
         </is>
       </c>
       <c r="AQ81">
@@ -14142,89 +13667,44 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="9" t="inlineStr">
-        <is>
-          <t>道北</t>
-        </is>
-      </c>
-      <c r="B82" s="9" t="inlineStr">
-        <is>
-          <t>鷹栖町営牧場</t>
-        </is>
-      </c>
-      <c r="D82" s="9" t="inlineStr">
-        <is>
-          <t>北海道上川郡鷹栖町</t>
-        </is>
-      </c>
-      <c r="E82" s="9" t="inlineStr">
-        <is>
-          <t>0166-87-2111</t>
-        </is>
-      </c>
-      <c r="F82" s="9" t="inlineStr">
-        <is>
-          <t>町営の公共牧場</t>
-        </is>
-      </c>
-      <c r="G82" s="9" t="inlineStr">
-        <is>
-          <t>都市近郊での人材獲得競争</t>
-        </is>
-      </c>
-      <c r="H82" s="9" t="inlineStr">
-        <is>
-          <t>コストをかけずに即戦力を確保</t>
-        </is>
-      </c>
-      <c r="I82" s="9" t="inlineStr">
-        <is>
-          <t>農業委員会</t>
-        </is>
-      </c>
-      <c r="J82" s="9" t="inlineStr">
-        <is>
-          <t>管理者</t>
-        </is>
-      </c>
-      <c r="K82" s="9" t="inlineStr">
-        <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="L82" s="9" t="inlineStr">
-        <is>
-          <t>未確認</t>
-        </is>
-      </c>
-      <c r="Q82" s="9" t="inlineStr">
-        <is>
-          <t>未開拓</t>
-        </is>
-      </c>
-      <c r="R82" s="9" t="inlineStr">
-        <is>
-          <t>ターゲット</t>
-        </is>
-      </c>
-      <c r="S82" s="9" t="inlineStr">
-        <is>
-          <t>リストアップ</t>
-        </is>
-      </c>
-      <c r="AG82" s="9" t="inlineStr">
-        <is>
-          <t>営業推進部</t>
-        </is>
-      </c>
-      <c r="AH82" s="9" t="inlineStr">
-        <is>
-          <t>武田 悦郎</t>
-        </is>
-      </c>
-      <c r="AN82" s="9" t="inlineStr">
-        <is>
-          <t>未定</t>
+      <c r="A82" s="15" t="inlineStr">
+        <is>
+          <t>道東(大空)</t>
+        </is>
+      </c>
+      <c r="B82" s="15" t="inlineStr">
+        <is>
+          <t>有限会社西牧場</t>
+        </is>
+      </c>
+      <c r="C82" s="16" t="inlineStr">
+        <is>
+          <t>https://www.nishi-farm.com/</t>
+        </is>
+      </c>
+      <c r="D82" s="15" t="inlineStr">
+        <is>
+          <t>北海道網走郡大空町東藻琴西倉347 (〒099-3202)</t>
+        </is>
+      </c>
+      <c r="E82" s="15" t="inlineStr">
+        <is>
+          <t>0152-66-2260</t>
+        </is>
+      </c>
+      <c r="F82" s="15" t="inlineStr">
+        <is>
+          <t>酪農・和牛素牛生産/乳牛235頭+黒毛和牛110頭</t>
+        </is>
+      </c>
+      <c r="G82" s="15" t="inlineStr">
+        <is>
+          <t>酪農と和牛繁殖の両立による多忙</t>
+        </is>
+      </c>
+      <c r="H82" s="15" t="inlineStr">
+        <is>
+          <t>飼養ルーティンを即戦力に任せ、繁殖管理に注力できる体制構築</t>
         </is>
       </c>
       <c r="AQ82">
@@ -14241,89 +13721,44 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="9" t="inlineStr">
-        <is>
-          <t>道北</t>
-        </is>
-      </c>
-      <c r="B83" s="9" t="inlineStr">
-        <is>
-          <t>和寒町営牧場</t>
-        </is>
-      </c>
-      <c r="D83" s="9" t="inlineStr">
-        <is>
-          <t>北海道上川郡和寒町</t>
-        </is>
-      </c>
-      <c r="E83" s="9" t="inlineStr">
-        <is>
-          <t>0165-32-2421</t>
-        </is>
-      </c>
-      <c r="F83" s="9" t="inlineStr">
-        <is>
-          <t>町営の公共牧場</t>
-        </is>
-      </c>
-      <c r="G83" s="9" t="inlineStr">
-        <is>
-          <t>夏季放牧管理の省力化</t>
-        </is>
-      </c>
-      <c r="H83" s="9" t="inlineStr">
-        <is>
-          <t>安定稼働を即戦力で支援</t>
-        </is>
-      </c>
-      <c r="I83" s="9" t="inlineStr">
-        <is>
-          <t>産業振興課</t>
-        </is>
-      </c>
-      <c r="J83" s="9" t="inlineStr">
-        <is>
-          <t>管理者</t>
-        </is>
-      </c>
-      <c r="K83" s="9" t="inlineStr">
-        <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="L83" s="9" t="inlineStr">
-        <is>
-          <t>未確認</t>
-        </is>
-      </c>
-      <c r="Q83" s="9" t="inlineStr">
-        <is>
-          <t>未開拓</t>
-        </is>
-      </c>
-      <c r="R83" s="9" t="inlineStr">
-        <is>
-          <t>ターゲット</t>
-        </is>
-      </c>
-      <c r="S83" s="9" t="inlineStr">
-        <is>
-          <t>リストアップ</t>
-        </is>
-      </c>
-      <c r="AG83" s="9" t="inlineStr">
-        <is>
-          <t>営業推進部</t>
-        </is>
-      </c>
-      <c r="AH83" s="9" t="inlineStr">
-        <is>
-          <t>武田 悦郎</t>
-        </is>
-      </c>
-      <c r="AN83" s="9" t="inlineStr">
-        <is>
-          <t>未定</t>
+      <c r="A83" s="15" t="inlineStr">
+        <is>
+          <t>道東(津別)</t>
+        </is>
+      </c>
+      <c r="B83" s="15" t="inlineStr">
+        <is>
+          <t>株式会社津別ファーム</t>
+        </is>
+      </c>
+      <c r="C83" s="16" t="inlineStr">
+        <is>
+          <t>https://tsubetsufarm.com/</t>
+        </is>
+      </c>
+      <c r="D83" s="15" t="inlineStr">
+        <is>
+          <t>北海道網走郡津別町字栄58番地2 (〒092-0356)</t>
+        </is>
+      </c>
+      <c r="E83" s="15" t="inlineStr">
+        <is>
+          <t>0152-76-1420</t>
+        </is>
+      </c>
+      <c r="F83" s="15" t="inlineStr">
+        <is>
+          <t>黒毛和牛素牛生産/飼養3500頭(繁殖1711/育成1220/肥育568)</t>
+        </is>
+      </c>
+      <c r="G83" s="15" t="inlineStr">
+        <is>
+          <t>大規模和牛繁殖における人員確保と血統管理</t>
+        </is>
+      </c>
+      <c r="H83" s="15" t="inlineStr">
+        <is>
+          <t>繁殖・育成・肥育の各段階に即戦力を配置し品質を維持</t>
         </is>
       </c>
       <c r="AQ83">
@@ -14340,89 +13775,44 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="9" t="inlineStr">
-        <is>
-          <t>道北</t>
-        </is>
-      </c>
-      <c r="B84" s="9" t="inlineStr">
-        <is>
-          <t>有限会社きしかわ畜産</t>
-        </is>
-      </c>
-      <c r="D84" s="9" t="inlineStr">
-        <is>
-          <t>北海道名寄市</t>
-        </is>
-      </c>
-      <c r="E84" s="9" t="inlineStr">
-        <is>
-          <t>01654-2-2555</t>
-        </is>
-      </c>
-      <c r="F84" s="9" t="inlineStr">
-        <is>
-          <t>素牛農家</t>
-        </is>
-      </c>
-      <c r="G84" s="9" t="inlineStr">
-        <is>
-          <t>現場作業の効率化</t>
-        </is>
-      </c>
-      <c r="H84" s="9" t="inlineStr">
-        <is>
-          <t>若手人材の紹介による基盤提供</t>
-        </is>
-      </c>
-      <c r="I84" s="9" t="inlineStr">
-        <is>
-          <t>経営陣</t>
-        </is>
-      </c>
-      <c r="J84" s="9" t="inlineStr">
-        <is>
-          <t>代表</t>
-        </is>
-      </c>
-      <c r="K84" s="9" t="inlineStr">
-        <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="L84" s="9" t="inlineStr">
-        <is>
-          <t>未確認</t>
-        </is>
-      </c>
-      <c r="Q84" s="9" t="inlineStr">
-        <is>
-          <t>未開拓</t>
-        </is>
-      </c>
-      <c r="R84" s="9" t="inlineStr">
-        <is>
-          <t>ターゲット</t>
-        </is>
-      </c>
-      <c r="S84" s="9" t="inlineStr">
-        <is>
-          <t>リストアップ</t>
-        </is>
-      </c>
-      <c r="AG84" s="9" t="inlineStr">
-        <is>
-          <t>営業推進部</t>
-        </is>
-      </c>
-      <c r="AH84" s="9" t="inlineStr">
-        <is>
-          <t>武田 悦郎</t>
-        </is>
-      </c>
-      <c r="AN84" s="9" t="inlineStr">
-        <is>
-          <t>未定</t>
+      <c r="A84" s="15" t="inlineStr">
+        <is>
+          <t>道東(網走)</t>
+        </is>
+      </c>
+      <c r="B84" s="15" t="inlineStr">
+        <is>
+          <t>エミュー牧場 (オホーツクエミューらんど)</t>
+        </is>
+      </c>
+      <c r="C84" s="16" t="inlineStr">
+        <is>
+          <t>https://zoo.hokkaido.jp/okhotsctemu/</t>
+        </is>
+      </c>
+      <c r="D84" s="15" t="inlineStr">
+        <is>
+          <t>北海道網走市字稲富462 (〒099-3115)</t>
+        </is>
+      </c>
+      <c r="E84" s="15" t="inlineStr">
+        <is>
+          <t>0152-46-2644</t>
+        </is>
+      </c>
+      <c r="F84" s="15" t="inlineStr">
+        <is>
+          <t>日本最大級のエミュー牧場/観光・東京農大エミュー研究会付属</t>
+        </is>
+      </c>
+      <c r="G84" s="15" t="inlineStr">
+        <is>
+          <t>観光対応とエミュー飼育の両立</t>
+        </is>
+      </c>
+      <c r="H84" s="15" t="inlineStr">
+        <is>
+          <t>飼育・施設管理を即戦力に任せ、観光体験の質向上</t>
         </is>
       </c>
       <c r="AQ84">
@@ -14439,89 +13829,40 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="9" t="inlineStr">
-        <is>
-          <t>道北</t>
-        </is>
-      </c>
-      <c r="B85" s="9" t="inlineStr">
-        <is>
-          <t>株式会社大雪牧場</t>
-        </is>
-      </c>
-      <c r="D85" s="9" t="inlineStr">
-        <is>
-          <t>北海道上川郡上川町</t>
-        </is>
-      </c>
-      <c r="E85" s="9" t="inlineStr">
-        <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="F85" s="9" t="inlineStr">
-        <is>
-          <t>肉牛・乳牛生産</t>
-        </is>
-      </c>
-      <c r="G85" s="9" t="inlineStr">
-        <is>
-          <t>多頭数飼育における日常業務</t>
-        </is>
-      </c>
-      <c r="H85" s="9" t="inlineStr">
-        <is>
-          <t>給餌・清掃を担う即戦力人材</t>
-        </is>
-      </c>
-      <c r="I85" s="9" t="inlineStr">
-        <is>
-          <t>経営陣</t>
-        </is>
-      </c>
-      <c r="J85" s="9" t="inlineStr">
-        <is>
-          <t>代表</t>
-        </is>
-      </c>
-      <c r="K85" s="9" t="inlineStr">
-        <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="L85" s="9" t="inlineStr">
-        <is>
-          <t>未確認</t>
-        </is>
-      </c>
-      <c r="Q85" s="9" t="inlineStr">
-        <is>
-          <t>未開拓</t>
-        </is>
-      </c>
-      <c r="R85" s="9" t="inlineStr">
-        <is>
-          <t>ターゲット</t>
-        </is>
-      </c>
-      <c r="S85" s="9" t="inlineStr">
-        <is>
-          <t>リストアップ</t>
-        </is>
-      </c>
-      <c r="AG85" s="9" t="inlineStr">
-        <is>
-          <t>営業推進部</t>
-        </is>
-      </c>
-      <c r="AH85" s="9" t="inlineStr">
-        <is>
-          <t>武田 悦郎</t>
-        </is>
-      </c>
-      <c r="AN85" s="9" t="inlineStr">
-        <is>
-          <t>未定</t>
+      <c r="A85" s="15" t="inlineStr">
+        <is>
+          <t>道東(大空)</t>
+        </is>
+      </c>
+      <c r="B85" s="15" t="inlineStr">
+        <is>
+          <t>太田ファーム (大空町)</t>
+        </is>
+      </c>
+      <c r="C85" s="15" t="inlineStr"/>
+      <c r="D85" s="15" t="inlineStr">
+        <is>
+          <t>北海道網走郡大空町東藻琴西倉179-2 (〒099-3202)</t>
+        </is>
+      </c>
+      <c r="E85" s="15" t="inlineStr">
+        <is>
+          <t>0152-66-2025</t>
+        </is>
+      </c>
+      <c r="F85" s="15" t="inlineStr">
+        <is>
+          <t>養豚経営</t>
+        </is>
+      </c>
+      <c r="G85" s="15" t="inlineStr">
+        <is>
+          <t>養豚現場の安定的な人員確保</t>
+        </is>
+      </c>
+      <c r="H85" s="15" t="inlineStr">
+        <is>
+          <t>養豚現場で即戦力となる特定技能人材の配置</t>
         </is>
       </c>
       <c r="AQ85">
@@ -14540,18 +13881,22 @@
     <row r="86">
       <c r="A86" s="15" t="inlineStr">
         <is>
-          <t>道東(網走)</t>
+          <t>道東(大空)</t>
         </is>
       </c>
       <c r="B86" s="15" t="inlineStr">
         <is>
-          <t>株式会社楠目牧場</t>
-        </is>
-      </c>
-      <c r="C86" s="15" t="inlineStr"/>
+          <t>有限会社長尾産業</t>
+        </is>
+      </c>
+      <c r="C86" s="16" t="inlineStr">
+        <is>
+          <t>https://nagao-sangyo.com/</t>
+        </is>
+      </c>
       <c r="D86" s="15" t="inlineStr">
         <is>
-          <t>北海道網走市字潮見213番地</t>
+          <t>北海道網走郡大空町東藻琴山園166</t>
         </is>
       </c>
       <c r="E86" s="15" t="inlineStr">
@@ -14561,17 +13906,17 @@
       </c>
       <c r="F86" s="15" t="inlineStr">
         <is>
-          <t>網走市の畜産経営/オホーツク海近郊</t>
+          <t>大規模酪農・アイス販売（東藻琴）</t>
         </is>
       </c>
       <c r="G86" s="15" t="inlineStr">
         <is>
-          <t>労働力確保と日常飼養管理</t>
+          <t>大規模酪農オペレーションの担い手確保</t>
         </is>
       </c>
       <c r="H86" s="15" t="inlineStr">
         <is>
-          <t>採用コストを抑えた即戦力人材の提供</t>
+          <t>即戦力配置で搾乳・飼養管理を安定化、6次産業に注力できる体制構築</t>
         </is>
       </c>
       <c r="AQ86">
@@ -14590,42 +13935,42 @@
     <row r="87">
       <c r="A87" s="15" t="inlineStr">
         <is>
-          <t>道東(網走)</t>
+          <t>道東(小清水)</t>
         </is>
       </c>
       <c r="B87" s="15" t="inlineStr">
         <is>
-          <t>有限会社網走原生牧場観光センター</t>
+          <t>株式会社小清水農業振興公社 (アグリハートセンター)</t>
         </is>
       </c>
       <c r="C87" s="16" t="inlineStr">
         <is>
-          <t>http://www.genseibokujou.co.jp/</t>
+          <t>http://agriheart.jp/</t>
         </is>
       </c>
       <c r="D87" s="15" t="inlineStr">
         <is>
-          <t>北海道網走市藻琴225番地</t>
+          <t>北海道斜里郡小清水町南町1丁目29番18号 (〒099-3642)</t>
         </is>
       </c>
       <c r="E87" s="15" t="inlineStr">
         <is>
-          <t>0152-46-2121</t>
+          <t>0152-67-5716</t>
         </is>
       </c>
       <c r="F87" s="15" t="inlineStr">
         <is>
-          <t>観光牧場/乗馬体験/ホーストレッキング</t>
+          <t>小清水町・JAこしみず等4団体出資の公社/農作業支援事業</t>
         </is>
       </c>
       <c r="G87" s="15" t="inlineStr">
         <is>
-          <t>観光対応と飼養管理の両立</t>
+          <t>町内農家への労働力供給のニーズ</t>
         </is>
       </c>
       <c r="H87" s="15" t="inlineStr">
         <is>
-          <t>バックヤード飼育を即戦力に任せ、接客・観光サービスに注力できる体制構築</t>
+          <t>公社窓口を通じた管内農家への一括人材紹介スキーム</t>
         </is>
       </c>
       <c r="AQ87">
@@ -14642,817 +13987,102 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="15" t="inlineStr">
-        <is>
-          <t>道東(北見)</t>
-        </is>
-      </c>
-      <c r="B88" s="15" t="inlineStr">
-        <is>
-          <t>株式会社協同畜産経営センター</t>
-        </is>
-      </c>
-      <c r="C88" s="16" t="inlineStr">
+      <c r="C88" t="inlineStr">
         <is>
           <t>https://www.hokkaido-pork.jp/farm/feedone/farm_kyodo/</t>
         </is>
       </c>
-      <c r="D88" s="15" t="inlineStr">
-        <is>
-          <t>北海道北見市大正763番地</t>
-        </is>
-      </c>
-      <c r="E88" s="15" t="inlineStr">
-        <is>
-          <t>0157-36-6006</t>
-        </is>
-      </c>
-      <c r="F88" s="15" t="inlineStr">
-        <is>
-          <t>オニオンポーク生産/繁殖550頭一貫生産</t>
-        </is>
-      </c>
-      <c r="G88" s="15" t="inlineStr">
-        <is>
-          <t>大規模養豚における安定的な人員配置</t>
-        </is>
-      </c>
-      <c r="H88" s="15" t="inlineStr">
-        <is>
-          <t>養豚現場で即戦力となる特定技能人材の配置でブランド維持を支援</t>
-        </is>
-      </c>
-      <c r="AQ88">
-        <f>COUNTIFS(加電履歴!$F:$F,B88,加電履歴!$E:$E,"畜種農業")</f>
-        <v/>
-      </c>
-      <c r="AR88" s="10">
-        <f>IFERROR(IF(COUNTIFS(加電履歴!$F:$F,B88,加電履歴!$E:$E,"畜種農業")=0,"",MAXIFS(加電履歴!$B:$B,加電履歴!$F:$F,B88,加電履歴!$E:$E,"畜種農業")),"")</f>
-        <v/>
-      </c>
-      <c r="AS88">
-        <f>IFERROR(IF(COUNTIFS(加電履歴!$F:$F,B88,加電履歴!$E:$E,"畜種農業")=0,"",INDEX(加電履歴!$I:$I,MATCH(1,(加電履歴!$F:$F=B88)*(加電履歴!$E:$E="畜種農業")*(加電履歴!$B:$B=MAXIFS(加電履歴!$B:$B,加電履歴!$F:$F,B88,加電履歴!$E:$E,"畜種農業")),0))),"")</f>
-        <v/>
-      </c>
     </row>
     <row r="89">
-      <c r="A89" s="15" t="inlineStr">
-        <is>
-          <t>道東(北見)</t>
-        </is>
-      </c>
-      <c r="B89" s="15" t="inlineStr">
-        <is>
-          <t>株式会社北きつね牧場</t>
-        </is>
-      </c>
-      <c r="C89" s="16" t="inlineStr">
+      <c r="C89" t="inlineStr">
         <is>
           <t>https://kitakitsune-farm.com/</t>
         </is>
       </c>
-      <c r="D89" s="15" t="inlineStr">
-        <is>
-          <t>北海道北見市留辺蘂町花丘52-1</t>
-        </is>
-      </c>
-      <c r="E89" s="15" t="inlineStr">
-        <is>
-          <t>0157-45-2249</t>
-        </is>
-      </c>
-      <c r="F89" s="15" t="inlineStr">
-        <is>
-          <t>観光牧場/キタキツネ・エゾタヌキ飼育</t>
-        </is>
-      </c>
-      <c r="G89" s="15" t="inlineStr">
-        <is>
-          <t>観光来場者対応と動物飼育の兼務</t>
-        </is>
-      </c>
-      <c r="H89" s="15" t="inlineStr">
-        <is>
-          <t>飼育管理を即戦力が担い、接客・施設運営に注力できる体制構築</t>
-        </is>
-      </c>
-      <c r="AQ89">
-        <f>COUNTIFS(加電履歴!$F:$F,B89,加電履歴!$E:$E,"畜種農業")</f>
-        <v/>
-      </c>
-      <c r="AR89" s="10">
-        <f>IFERROR(IF(COUNTIFS(加電履歴!$F:$F,B89,加電履歴!$E:$E,"畜種農業")=0,"",MAXIFS(加電履歴!$B:$B,加電履歴!$F:$F,B89,加電履歴!$E:$E,"畜種農業")),"")</f>
-        <v/>
-      </c>
-      <c r="AS89">
-        <f>IFERROR(IF(COUNTIFS(加電履歴!$F:$F,B89,加電履歴!$E:$E,"畜種農業")=0,"",INDEX(加電履歴!$I:$I,MATCH(1,(加電履歴!$F:$F=B89)*(加電履歴!$E:$E="畜種農業")*(加電履歴!$B:$B=MAXIFS(加電履歴!$B:$B,加電履歴!$F:$F,B89,加電履歴!$E:$E,"畜種農業")),0))),"")</f>
-        <v/>
-      </c>
     </row>
     <row r="90">
-      <c r="A90" s="15" t="inlineStr">
-        <is>
-          <t>道東(美幌)</t>
-        </is>
-      </c>
-      <c r="B90" s="15" t="inlineStr">
-        <is>
-          <t>株式会社美幌牛肥育センター</t>
-        </is>
-      </c>
-      <c r="C90" s="16" t="inlineStr">
+      <c r="C90" t="inlineStr">
         <is>
           <t>http://www.bihoro-gyu.com/</t>
         </is>
       </c>
-      <c r="D90" s="15" t="inlineStr">
-        <is>
-          <t>北海道網走郡美幌町字都橋211番地</t>
-        </is>
-      </c>
-      <c r="E90" s="15" t="inlineStr">
-        <is>
-          <t>0152-72-3373</t>
-        </is>
-      </c>
-      <c r="F90" s="15" t="inlineStr">
-        <is>
-          <t>ブランド牛「びほろ牛」肥育/肉牛飼育・販売・堆肥販売</t>
-        </is>
-      </c>
-      <c r="G90" s="15" t="inlineStr">
-        <is>
-          <t>ブランド維持のための丁寧な肥育管理と人員確保</t>
-        </is>
-      </c>
-      <c r="H90" s="15" t="inlineStr">
-        <is>
-          <t>肥育ルーティンを即戦力で支援しブランド維持に貢献</t>
-        </is>
-      </c>
-      <c r="AQ90">
-        <f>COUNTIFS(加電履歴!$F:$F,B90,加電履歴!$E:$E,"畜種農業")</f>
-        <v/>
-      </c>
-      <c r="AR90" s="10">
-        <f>IFERROR(IF(COUNTIFS(加電履歴!$F:$F,B90,加電履歴!$E:$E,"畜種農業")=0,"",MAXIFS(加電履歴!$B:$B,加電履歴!$F:$F,B90,加電履歴!$E:$E,"畜種農業")),"")</f>
-        <v/>
-      </c>
-      <c r="AS90">
-        <f>IFERROR(IF(COUNTIFS(加電履歴!$F:$F,B90,加電履歴!$E:$E,"畜種農業")=0,"",INDEX(加電履歴!$I:$I,MATCH(1,(加電履歴!$F:$F=B90)*(加電履歴!$E:$E="畜種農業")*(加電履歴!$B:$B=MAXIFS(加電履歴!$B:$B,加電履歴!$F:$F,B90,加電履歴!$E:$E,"畜種農業")),0))),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="15" t="inlineStr">
-        <is>
-          <t>道東(美幌)</t>
-        </is>
-      </c>
-      <c r="B91" s="15" t="inlineStr">
-        <is>
-          <t>株式会社美幌ファーム</t>
-        </is>
-      </c>
-      <c r="C91" s="15" t="inlineStr">
-        <is>
-          <t>※要確認</t>
-        </is>
-      </c>
-      <c r="D91" s="15" t="inlineStr">
-        <is>
-          <t>北海道網走郡美幌町 ※詳細要確認</t>
-        </is>
-      </c>
-      <c r="E91" s="15" t="inlineStr">
-        <is>
-          <t>※要確認</t>
-        </is>
-      </c>
-      <c r="F91" s="15" t="inlineStr">
-        <is>
-          <t>びほろ牛の素牛育成(6-12カ月齢)/美幌牛肥育センター系列</t>
-        </is>
-      </c>
-      <c r="G91" s="15" t="inlineStr">
-        <is>
-          <t>グループ会社との連携と素牛育成の労働力確保</t>
-        </is>
-      </c>
-      <c r="H91" s="15" t="inlineStr">
-        <is>
-          <t>系列会社と一体での人材紹介、安定した育成オペレーション支援</t>
-        </is>
-      </c>
-      <c r="AQ91">
-        <f>COUNTIFS(加電履歴!$F:$F,B91,加電履歴!$E:$E,"畜種農業")</f>
-        <v/>
-      </c>
-      <c r="AR91" s="10">
-        <f>IFERROR(IF(COUNTIFS(加電履歴!$F:$F,B91,加電履歴!$E:$E,"畜種農業")=0,"",MAXIFS(加電履歴!$B:$B,加電履歴!$F:$F,B91,加電履歴!$E:$E,"畜種農業")),"")</f>
-        <v/>
-      </c>
-      <c r="AS91">
-        <f>IFERROR(IF(COUNTIFS(加電履歴!$F:$F,B91,加電履歴!$E:$E,"畜種農業")=0,"",INDEX(加電履歴!$I:$I,MATCH(1,(加電履歴!$F:$F=B91)*(加電履歴!$E:$E="畜種農業")*(加電履歴!$B:$B=MAXIFS(加電履歴!$B:$B,加電履歴!$F:$F,B91,加電履歴!$E:$E,"畜種農業")),0))),"")</f>
-        <v/>
-      </c>
     </row>
     <row r="92">
-      <c r="A92" s="15" t="inlineStr">
-        <is>
-          <t>道東(斜里)</t>
-        </is>
-      </c>
-      <c r="B92" s="15" t="inlineStr">
-        <is>
-          <t>有限会社佐々木種畜牧場</t>
-        </is>
-      </c>
-      <c r="C92" s="16" t="inlineStr">
+      <c r="C92" t="inlineStr">
         <is>
           <t>https://sasaki-web.net/</t>
         </is>
       </c>
-      <c r="D92" s="15" t="inlineStr">
-        <is>
-          <t>北海道斜里郡斜里町字美咲69</t>
-        </is>
-      </c>
-      <c r="E92" s="15" t="inlineStr">
-        <is>
-          <t>0152-23-0429</t>
-        </is>
-      </c>
-      <c r="F92" s="15" t="inlineStr">
-        <is>
-          <t>サチク麦王ブランド豚/麦主体飼料/直売店併設</t>
-        </is>
-      </c>
-      <c r="G92" s="15" t="inlineStr">
-        <is>
-          <t>養豚と直売店の両立</t>
-        </is>
-      </c>
-      <c r="H92" s="15" t="inlineStr">
-        <is>
-          <t>養豚現場の即戦力配置で代表が販売・加工に注力できる体制構築</t>
-        </is>
-      </c>
-      <c r="AQ92">
-        <f>COUNTIFS(加電履歴!$F:$F,B92,加電履歴!$E:$E,"畜種農業")</f>
-        <v/>
-      </c>
-      <c r="AR92" s="10">
-        <f>IFERROR(IF(COUNTIFS(加電履歴!$F:$F,B92,加電履歴!$E:$E,"畜種農業")=0,"",MAXIFS(加電履歴!$B:$B,加電履歴!$F:$F,B92,加電履歴!$E:$E,"畜種農業")),"")</f>
-        <v/>
-      </c>
-      <c r="AS92">
-        <f>IFERROR(IF(COUNTIFS(加電履歴!$F:$F,B92,加電履歴!$E:$E,"畜種農業")=0,"",INDEX(加電履歴!$I:$I,MATCH(1,(加電履歴!$F:$F=B92)*(加電履歴!$E:$E="畜種農業")*(加電履歴!$B:$B=MAXIFS(加電履歴!$B:$B,加電履歴!$F:$F,B92,加電履歴!$E:$E,"畜種農業")),0))),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="15" t="inlineStr">
-        <is>
-          <t>道東(網走)</t>
-        </is>
-      </c>
-      <c r="B93" s="15" t="inlineStr">
-        <is>
-          <t>株式会社オホーツクファーム33</t>
-        </is>
-      </c>
-      <c r="C93" s="15" t="inlineStr"/>
-      <c r="D93" s="15" t="inlineStr">
-        <is>
-          <t>北海道網走市字北浜273番地の4</t>
-        </is>
-      </c>
-      <c r="E93" s="15" t="inlineStr">
-        <is>
-          <t>※要確認</t>
-        </is>
-      </c>
-      <c r="F93" s="15" t="inlineStr">
-        <is>
-          <t>網走市での牧場経営</t>
-        </is>
-      </c>
-      <c r="G93" s="15" t="inlineStr">
-        <is>
-          <t>日常飼養管理の労働力確保</t>
-        </is>
-      </c>
-      <c r="H93" s="15" t="inlineStr">
-        <is>
-          <t>採用コストを抑えた即戦力人材の提供</t>
-        </is>
-      </c>
-      <c r="AQ93">
-        <f>COUNTIFS(加電履歴!$F:$F,B93,加電履歴!$E:$E,"畜種農業")</f>
-        <v/>
-      </c>
-      <c r="AR93" s="10">
-        <f>IFERROR(IF(COUNTIFS(加電履歴!$F:$F,B93,加電履歴!$E:$E,"畜種農業")=0,"",MAXIFS(加電履歴!$B:$B,加電履歴!$F:$F,B93,加電履歴!$E:$E,"畜種農業")),"")</f>
-        <v/>
-      </c>
-      <c r="AS93">
-        <f>IFERROR(IF(COUNTIFS(加電履歴!$F:$F,B93,加電履歴!$E:$E,"畜種農業")=0,"",INDEX(加電履歴!$I:$I,MATCH(1,(加電履歴!$F:$F=B93)*(加電履歴!$E:$E="畜種農業")*(加電履歴!$B:$B=MAXIFS(加電履歴!$B:$B,加電履歴!$F:$F,B93,加電履歴!$E:$E,"畜種農業")),0))),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="15" t="inlineStr">
-        <is>
-          <t>道東(網走)</t>
-        </is>
-      </c>
-      <c r="B94" s="15" t="inlineStr">
-        <is>
-          <t>有限会社網走ふる里牧場</t>
-        </is>
-      </c>
-      <c r="C94" s="15" t="inlineStr"/>
-      <c r="D94" s="15" t="inlineStr">
-        <is>
-          <t>北海道網走市字稲富83</t>
-        </is>
-      </c>
-      <c r="E94" s="14" t="inlineStr">
-        <is>
-          <t>0152-46-2402</t>
-        </is>
-      </c>
-      <c r="F94" s="15" t="inlineStr">
-        <is>
-          <t>網走市の畜産業</t>
-        </is>
-      </c>
-      <c r="G94" s="15" t="inlineStr">
-        <is>
-          <t>通常飼養管理の担い手不足</t>
-        </is>
-      </c>
-      <c r="H94" s="15" t="inlineStr">
-        <is>
-          <t>即戦力配置による飼養管理の安定化</t>
-        </is>
-      </c>
-      <c r="AQ94">
-        <f>COUNTIFS(加電履歴!$F:$F,B94,加電履歴!$E:$E,"畜種農業")</f>
-        <v/>
-      </c>
-      <c r="AR94" s="10">
-        <f>IFERROR(IF(COUNTIFS(加電履歴!$F:$F,B94,加電履歴!$E:$E,"畜種農業")=0,"",MAXIFS(加電履歴!$B:$B,加電履歴!$F:$F,B94,加電履歴!$E:$E,"畜種農業")),"")</f>
-        <v/>
-      </c>
-      <c r="AS94">
-        <f>IFERROR(IF(COUNTIFS(加電履歴!$F:$F,B94,加電履歴!$E:$E,"畜種農業")=0,"",INDEX(加電履歴!$I:$I,MATCH(1,(加電履歴!$F:$F=B94)*(加電履歴!$E:$E="畜種農業")*(加電履歴!$B:$B=MAXIFS(加電履歴!$B:$B,加電履歴!$F:$F,B94,加電履歴!$E:$E,"畜種農業")),0))),"")</f>
-        <v/>
-      </c>
     </row>
     <row r="95">
-      <c r="A95" s="15" t="inlineStr">
-        <is>
-          <t>道東(大空)</t>
-        </is>
-      </c>
-      <c r="B95" s="15" t="inlineStr">
-        <is>
-          <t>株式会社北海道畜産公社 道東事業所 北見工場</t>
-        </is>
-      </c>
-      <c r="C95" s="16" t="inlineStr">
+      <c r="C95" t="inlineStr">
         <is>
           <t>https://tikusan.securesite.jp/</t>
         </is>
       </c>
-      <c r="D95" s="15" t="inlineStr">
-        <is>
-          <t>北海道網走郡大空町東藻琴西倉280-3 (〒099-3202)</t>
-        </is>
-      </c>
-      <c r="E95" s="15" t="inlineStr">
-        <is>
-          <t>※要確認</t>
-        </is>
-      </c>
-      <c r="F95" s="15" t="inlineStr">
-        <is>
-          <t>オホーツク地区主要食肉処理工場/牛・豚加工/海外輸出認定</t>
-        </is>
-      </c>
-      <c r="G95" s="15" t="inlineStr">
-        <is>
-          <t>大規模食肉処理ラインにおける慢性的人員不足</t>
-        </is>
-      </c>
-      <c r="H95" s="15" t="inlineStr">
-        <is>
-          <t>食肉加工現場で即戦力となる特定技能人材を通年で提供</t>
-        </is>
-      </c>
-      <c r="AQ95">
-        <f>COUNTIFS(加電履歴!$F:$F,B95,加電履歴!$E:$E,"畜種農業")</f>
-        <v/>
-      </c>
-      <c r="AR95" s="10">
-        <f>IFERROR(IF(COUNTIFS(加電履歴!$F:$F,B95,加電履歴!$E:$E,"畜種農業")=0,"",MAXIFS(加電履歴!$B:$B,加電履歴!$F:$F,B95,加電履歴!$E:$E,"畜種農業")),"")</f>
-        <v/>
-      </c>
-      <c r="AS95">
-        <f>IFERROR(IF(COUNTIFS(加電履歴!$F:$F,B95,加電履歴!$E:$E,"畜種農業")=0,"",INDEX(加電履歴!$I:$I,MATCH(1,(加電履歴!$F:$F=B95)*(加電履歴!$E:$E="畜種農業")*(加電履歴!$B:$B=MAXIFS(加電履歴!$B:$B,加電履歴!$F:$F,B95,加電履歴!$E:$E,"畜種農業")),0))),"")</f>
-        <v/>
-      </c>
     </row>
     <row r="96">
-      <c r="A96" s="15" t="inlineStr">
-        <is>
-          <t>道東(大空)</t>
-        </is>
-      </c>
-      <c r="B96" s="15" t="inlineStr">
-        <is>
-          <t>有限会社山口ファーム</t>
-        </is>
-      </c>
-      <c r="C96" s="16" t="inlineStr">
+      <c r="C96" t="inlineStr">
         <is>
           <t>https://www.yamaguchifarm.com/</t>
         </is>
       </c>
-      <c r="D96" s="15" t="inlineStr">
-        <is>
-          <t>北海道網走郡大空町東藻琴末広92番地 (〒099-3232)</t>
-        </is>
-      </c>
-      <c r="E96" s="15" t="inlineStr">
-        <is>
-          <t>0152-66-3434</t>
-        </is>
-      </c>
-      <c r="F96" s="15" t="inlineStr">
-        <is>
-          <t>大空町東藻琴の農場経営</t>
-        </is>
-      </c>
-      <c r="G96" s="15" t="inlineStr">
-        <is>
-          <t>農繁期の労働力確保</t>
-        </is>
-      </c>
-      <c r="H96" s="15" t="inlineStr">
-        <is>
-          <t>即戦力人材による農作業の安定化</t>
-        </is>
-      </c>
-      <c r="AQ96">
-        <f>COUNTIFS(加電履歴!$F:$F,B96,加電履歴!$E:$E,"畜種農業")</f>
-        <v/>
-      </c>
-      <c r="AR96" s="10">
-        <f>IFERROR(IF(COUNTIFS(加電履歴!$F:$F,B96,加電履歴!$E:$E,"畜種農業")=0,"",MAXIFS(加電履歴!$B:$B,加電履歴!$F:$F,B96,加電履歴!$E:$E,"畜種農業")),"")</f>
-        <v/>
-      </c>
-      <c r="AS96">
-        <f>IFERROR(IF(COUNTIFS(加電履歴!$F:$F,B96,加電履歴!$E:$E,"畜種農業")=0,"",INDEX(加電履歴!$I:$I,MATCH(1,(加電履歴!$F:$F=B96)*(加電履歴!$E:$E="畜種農業")*(加電履歴!$B:$B=MAXIFS(加電履歴!$B:$B,加電履歴!$F:$F,B96,加電履歴!$E:$E,"畜種農業")),0))),"")</f>
-        <v/>
-      </c>
     </row>
     <row r="97">
-      <c r="A97" s="15" t="inlineStr">
-        <is>
-          <t>道東(大空)</t>
-        </is>
-      </c>
-      <c r="B97" s="15" t="inlineStr">
-        <is>
-          <t>有限会社西牧場</t>
-        </is>
-      </c>
-      <c r="C97" s="16" t="inlineStr">
+      <c r="C97" t="inlineStr">
         <is>
           <t>https://www.nishi-farm.com/</t>
         </is>
       </c>
-      <c r="D97" s="15" t="inlineStr">
-        <is>
-          <t>北海道網走郡大空町東藻琴西倉347 (〒099-3202)</t>
-        </is>
-      </c>
-      <c r="E97" s="15" t="inlineStr">
-        <is>
-          <t>0152-66-2260</t>
-        </is>
-      </c>
-      <c r="F97" s="15" t="inlineStr">
-        <is>
-          <t>酪農・和牛素牛生産/乳牛235頭+黒毛和牛110頭</t>
-        </is>
-      </c>
-      <c r="G97" s="15" t="inlineStr">
-        <is>
-          <t>酪農と和牛繁殖の両立による多忙</t>
-        </is>
-      </c>
-      <c r="H97" s="15" t="inlineStr">
-        <is>
-          <t>飼養ルーティンを即戦力に任せ、繁殖管理に注力できる体制構築</t>
-        </is>
-      </c>
-      <c r="AQ97">
-        <f>COUNTIFS(加電履歴!$F:$F,B97,加電履歴!$E:$E,"畜種農業")</f>
-        <v/>
-      </c>
-      <c r="AR97" s="10">
-        <f>IFERROR(IF(COUNTIFS(加電履歴!$F:$F,B97,加電履歴!$E:$E,"畜種農業")=0,"",MAXIFS(加電履歴!$B:$B,加電履歴!$F:$F,B97,加電履歴!$E:$E,"畜種農業")),"")</f>
-        <v/>
-      </c>
-      <c r="AS97">
-        <f>IFERROR(IF(COUNTIFS(加電履歴!$F:$F,B97,加電履歴!$E:$E,"畜種農業")=0,"",INDEX(加電履歴!$I:$I,MATCH(1,(加電履歴!$F:$F=B97)*(加電履歴!$E:$E="畜種農業")*(加電履歴!$B:$B=MAXIFS(加電履歴!$B:$B,加電履歴!$F:$F,B97,加電履歴!$E:$E,"畜種農業")),0))),"")</f>
-        <v/>
-      </c>
     </row>
     <row r="98">
-      <c r="A98" s="15" t="inlineStr">
-        <is>
-          <t>道東(津別)</t>
-        </is>
-      </c>
-      <c r="B98" s="15" t="inlineStr">
-        <is>
-          <t>株式会社津別ファーム</t>
-        </is>
-      </c>
-      <c r="C98" s="16" t="inlineStr">
+      <c r="C98" t="inlineStr">
         <is>
           <t>https://tsubetsufarm.com/</t>
         </is>
       </c>
-      <c r="D98" s="15" t="inlineStr">
-        <is>
-          <t>北海道網走郡津別町字栄58番地2 (〒092-0356)</t>
-        </is>
-      </c>
-      <c r="E98" s="15" t="inlineStr">
-        <is>
-          <t>0152-76-1420</t>
-        </is>
-      </c>
-      <c r="F98" s="15" t="inlineStr">
-        <is>
-          <t>黒毛和牛素牛生産/飼養3500頭(繁殖1711/育成1220/肥育568)</t>
-        </is>
-      </c>
-      <c r="G98" s="15" t="inlineStr">
-        <is>
-          <t>大規模和牛繁殖における人員確保と血統管理</t>
-        </is>
-      </c>
-      <c r="H98" s="15" t="inlineStr">
-        <is>
-          <t>繁殖・育成・肥育の各段階に即戦力を配置し品質を維持</t>
-        </is>
-      </c>
-      <c r="AQ98">
-        <f>COUNTIFS(加電履歴!$F:$F,B98,加電履歴!$E:$E,"畜種農業")</f>
-        <v/>
-      </c>
-      <c r="AR98" s="10">
-        <f>IFERROR(IF(COUNTIFS(加電履歴!$F:$F,B98,加電履歴!$E:$E,"畜種農業")=0,"",MAXIFS(加電履歴!$B:$B,加電履歴!$F:$F,B98,加電履歴!$E:$E,"畜種農業")),"")</f>
-        <v/>
-      </c>
-      <c r="AS98">
-        <f>IFERROR(IF(COUNTIFS(加電履歴!$F:$F,B98,加電履歴!$E:$E,"畜種農業")=0,"",INDEX(加電履歴!$I:$I,MATCH(1,(加電履歴!$F:$F=B98)*(加電履歴!$E:$E="畜種農業")*(加電履歴!$B:$B=MAXIFS(加電履歴!$B:$B,加電履歴!$F:$F,B98,加電履歴!$E:$E,"畜種農業")),0))),"")</f>
-        <v/>
-      </c>
     </row>
     <row r="99">
-      <c r="A99" s="15" t="inlineStr">
-        <is>
-          <t>道東(網走)</t>
-        </is>
-      </c>
-      <c r="B99" s="15" t="inlineStr">
-        <is>
-          <t>エミュー牧場 (オホーツクエミューらんど)</t>
-        </is>
-      </c>
-      <c r="C99" s="16" t="inlineStr">
+      <c r="C99" t="inlineStr">
         <is>
           <t>https://zoo.hokkaido.jp/okhotsctemu/</t>
         </is>
       </c>
-      <c r="D99" s="15" t="inlineStr">
-        <is>
-          <t>北海道網走市字稲富462 (〒099-3115)</t>
-        </is>
-      </c>
-      <c r="E99" s="15" t="inlineStr">
-        <is>
-          <t>0152-46-2644</t>
-        </is>
-      </c>
-      <c r="F99" s="15" t="inlineStr">
-        <is>
-          <t>日本最大級のエミュー牧場/観光・東京農大エミュー研究会付属</t>
-        </is>
-      </c>
-      <c r="G99" s="15" t="inlineStr">
-        <is>
-          <t>観光対応とエミュー飼育の両立</t>
-        </is>
-      </c>
-      <c r="H99" s="15" t="inlineStr">
-        <is>
-          <t>飼育・施設管理を即戦力に任せ、観光体験の質向上</t>
-        </is>
-      </c>
-      <c r="AQ99">
-        <f>COUNTIFS(加電履歴!$F:$F,B99,加電履歴!$E:$E,"畜種農業")</f>
-        <v/>
-      </c>
-      <c r="AR99" s="10">
-        <f>IFERROR(IF(COUNTIFS(加電履歴!$F:$F,B99,加電履歴!$E:$E,"畜種農業")=0,"",MAXIFS(加電履歴!$B:$B,加電履歴!$F:$F,B99,加電履歴!$E:$E,"畜種農業")),"")</f>
-        <v/>
-      </c>
-      <c r="AS99">
-        <f>IFERROR(IF(COUNTIFS(加電履歴!$F:$F,B99,加電履歴!$E:$E,"畜種農業")=0,"",INDEX(加電履歴!$I:$I,MATCH(1,(加電履歴!$F:$F=B99)*(加電履歴!$E:$E="畜種農業")*(加電履歴!$B:$B=MAXIFS(加電履歴!$B:$B,加電履歴!$F:$F,B99,加電履歴!$E:$E,"畜種農業")),0))),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="15" t="inlineStr">
-        <is>
-          <t>道東(大空)</t>
-        </is>
-      </c>
-      <c r="B100" s="15" t="inlineStr">
-        <is>
-          <t>太田ファーム (大空町)</t>
-        </is>
-      </c>
-      <c r="C100" s="15" t="inlineStr"/>
-      <c r="D100" s="15" t="inlineStr">
-        <is>
-          <t>北海道網走郡大空町東藻琴西倉179-2 (〒099-3202)</t>
-        </is>
-      </c>
-      <c r="E100" s="15" t="inlineStr">
-        <is>
-          <t>0152-66-2025</t>
-        </is>
-      </c>
-      <c r="F100" s="15" t="inlineStr">
-        <is>
-          <t>養豚経営</t>
-        </is>
-      </c>
-      <c r="G100" s="15" t="inlineStr">
-        <is>
-          <t>養豚現場の安定的な人員確保</t>
-        </is>
-      </c>
-      <c r="H100" s="15" t="inlineStr">
-        <is>
-          <t>養豚現場で即戦力となる特定技能人材の配置</t>
-        </is>
-      </c>
-      <c r="AQ100">
-        <f>COUNTIFS(加電履歴!$F:$F,B100,加電履歴!$E:$E,"畜種農業")</f>
-        <v/>
-      </c>
-      <c r="AR100" s="10">
-        <f>IFERROR(IF(COUNTIFS(加電履歴!$F:$F,B100,加電履歴!$E:$E,"畜種農業")=0,"",MAXIFS(加電履歴!$B:$B,加電履歴!$F:$F,B100,加電履歴!$E:$E,"畜種農業")),"")</f>
-        <v/>
-      </c>
-      <c r="AS100">
-        <f>IFERROR(IF(COUNTIFS(加電履歴!$F:$F,B100,加電履歴!$E:$E,"畜種農業")=0,"",INDEX(加電履歴!$I:$I,MATCH(1,(加電履歴!$F:$F=B100)*(加電履歴!$E:$E="畜種農業")*(加電履歴!$B:$B=MAXIFS(加電履歴!$B:$B,加電履歴!$F:$F,B100,加電履歴!$E:$E,"畜種農業")),0))),"")</f>
-        <v/>
-      </c>
     </row>
     <row r="101">
-      <c r="A101" s="15" t="inlineStr">
-        <is>
-          <t>道東(大空)</t>
-        </is>
-      </c>
-      <c r="B101" s="15" t="inlineStr">
-        <is>
-          <t>有限会社長尾産業</t>
-        </is>
-      </c>
-      <c r="C101" s="16" t="inlineStr">
+      <c r="C101" t="inlineStr">
         <is>
           <t>https://nagao-sangyo.com/</t>
         </is>
       </c>
-      <c r="D101" s="15" t="inlineStr">
-        <is>
-          <t>北海道網走郡大空町東藻琴山園166</t>
-        </is>
-      </c>
-      <c r="E101" s="15" t="inlineStr">
-        <is>
-          <t>※要確認</t>
-        </is>
-      </c>
-      <c r="F101" s="15" t="inlineStr">
-        <is>
-          <t>大規模酪農・アイス販売（東藻琴）</t>
-        </is>
-      </c>
-      <c r="G101" s="15" t="inlineStr">
-        <is>
-          <t>大規模酪農オペレーションの担い手確保</t>
-        </is>
-      </c>
-      <c r="H101" s="15" t="inlineStr">
-        <is>
-          <t>即戦力配置で搾乳・飼養管理を安定化、6次産業に注力できる体制構築</t>
-        </is>
-      </c>
-      <c r="AQ101">
-        <f>COUNTIFS(加電履歴!$F:$F,B101,加電履歴!$E:$E,"畜種農業")</f>
-        <v/>
-      </c>
-      <c r="AR101" s="10">
-        <f>IFERROR(IF(COUNTIFS(加電履歴!$F:$F,B101,加電履歴!$E:$E,"畜種農業")=0,"",MAXIFS(加電履歴!$B:$B,加電履歴!$F:$F,B101,加電履歴!$E:$E,"畜種農業")),"")</f>
-        <v/>
-      </c>
-      <c r="AS101">
-        <f>IFERROR(IF(COUNTIFS(加電履歴!$F:$F,B101,加電履歴!$E:$E,"畜種農業")=0,"",INDEX(加電履歴!$I:$I,MATCH(1,(加電履歴!$F:$F=B101)*(加電履歴!$E:$E="畜種農業")*(加電履歴!$B:$B=MAXIFS(加電履歴!$B:$B,加電履歴!$F:$F,B101,加電履歴!$E:$E,"畜種農業")),0))),"")</f>
-        <v/>
-      </c>
     </row>
     <row r="102">
-      <c r="A102" s="15" t="inlineStr">
-        <is>
-          <t>道東(小清水)</t>
-        </is>
-      </c>
-      <c r="B102" s="15" t="inlineStr">
-        <is>
-          <t>株式会社小清水農業振興公社 (アグリハートセンター)</t>
-        </is>
-      </c>
-      <c r="C102" s="16" t="inlineStr">
+      <c r="C102" t="inlineStr">
         <is>
           <t>http://agriheart.jp/</t>
         </is>
-      </c>
-      <c r="D102" s="15" t="inlineStr">
-        <is>
-          <t>北海道斜里郡小清水町南町1丁目29番18号 (〒099-3642)</t>
-        </is>
-      </c>
-      <c r="E102" s="15" t="inlineStr">
-        <is>
-          <t>0152-67-5716</t>
-        </is>
-      </c>
-      <c r="F102" s="15" t="inlineStr">
-        <is>
-          <t>小清水町・JAこしみず等4団体出資の公社/農作業支援事業</t>
-        </is>
-      </c>
-      <c r="G102" s="15" t="inlineStr">
-        <is>
-          <t>町内農家への労働力供給のニーズ</t>
-        </is>
-      </c>
-      <c r="H102" s="15" t="inlineStr">
-        <is>
-          <t>公社窓口を通じた管内農家への一括人材紹介スキーム</t>
-        </is>
-      </c>
-      <c r="AQ102">
-        <f>COUNTIFS(加電履歴!$F:$F,B102,加電履歴!$E:$E,"畜種農業")</f>
-        <v/>
-      </c>
-      <c r="AR102" s="10">
-        <f>IFERROR(IF(COUNTIFS(加電履歴!$F:$F,B102,加電履歴!$E:$E,"畜種農業")=0,"",MAXIFS(加電履歴!$B:$B,加電履歴!$F:$F,B102,加電履歴!$E:$E,"畜種農業")),"")</f>
-        <v/>
-      </c>
-      <c r="AS102">
-        <f>IFERROR(IF(COUNTIFS(加電履歴!$F:$F,B102,加電履歴!$E:$E,"畜種農業")=0,"",INDEX(加電履歴!$I:$I,MATCH(1,(加電履歴!$F:$F=B102)*(加電履歴!$E:$E="畜種農業")*(加電履歴!$B:$B=MAXIFS(加電履歴!$B:$B,加電履歴!$F:$F,B102,加電履歴!$E:$E,"畜種農業")),0))),"")</f>
-        <v/>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C87" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C88" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C89" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C90" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C92" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C95" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C96" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C97" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C98" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C99" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C101" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C102" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C49" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C50" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C51" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C52" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C53" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C55" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C87" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C88" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C89" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C90" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C92" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C95" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C96" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C97" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C98" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C99" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C101" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C102" r:id="rId18"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/output/企業リスト_作業中.xlsx
+++ b/output/企業リスト_作業中.xlsx
@@ -11605,19 +11605,24 @@
           <t>道北</t>
         </is>
       </c>
-      <c r="B56" s="9" t="inlineStr">
-        <is>
-          <t>日本ハム北海道ファクトリー 旭川工場</t>
-        </is>
-      </c>
-      <c r="D56" s="9" t="inlineStr">
-        <is>
-          <t>北海道旭川市</t>
-        </is>
-      </c>
-      <c r="E56" s="9" t="inlineStr">
-        <is>
-          <t>0166-48-1211</t>
+      <c r="B56" s="18" t="inlineStr">
+        <is>
+          <t>日本ハム北海道ファクトリー株式会社 旭川工場</t>
+        </is>
+      </c>
+      <c r="C56" s="12" t="inlineStr">
+        <is>
+          <t>https://www.nipponham-hokkaidofa.co.jp/</t>
+        </is>
+      </c>
+      <c r="D56" s="18" t="inlineStr">
+        <is>
+          <t>北海道旭川市工業団地1条3丁目1番37号 (〒078-8271)</t>
+        </is>
+      </c>
+      <c r="E56" s="18" t="inlineStr">
+        <is>
+          <t>0166-76-1186</t>
         </is>
       </c>
       <c r="F56" s="9" t="inlineStr">
@@ -11704,19 +11709,24 @@
           <t>道北</t>
         </is>
       </c>
-      <c r="B57" s="9" t="inlineStr">
-        <is>
-          <t>東宗谷農業協同組合 猿払畜産事業所</t>
-        </is>
-      </c>
-      <c r="D57" s="9" t="inlineStr">
-        <is>
-          <t>北海道宗谷郡猿払村</t>
-        </is>
-      </c>
-      <c r="E57" s="9" t="inlineStr">
-        <is>
-          <t>01635-2-3135</t>
+      <c r="B57" s="18" t="inlineStr">
+        <is>
+          <t>東宗谷農業協同組合 猿払支所/畜産事業所</t>
+        </is>
+      </c>
+      <c r="C57" s="12" t="inlineStr">
+        <is>
+          <t>https://www.ja-esoya.com/</t>
+        </is>
+      </c>
+      <c r="D57" s="18" t="inlineStr">
+        <is>
+          <t>北海道宗谷郡猿払村鬼志別西町51</t>
+        </is>
+      </c>
+      <c r="E57" s="18" t="inlineStr">
+        <is>
+          <t>01635-2-3312 (猿払支所代表)</t>
         </is>
       </c>
       <c r="F57" s="9" t="inlineStr">
@@ -12892,19 +12902,20 @@
           <t>道北</t>
         </is>
       </c>
-      <c r="B69" s="9" t="inlineStr">
+      <c r="B69" s="18" t="inlineStr">
         <is>
           <t>有限会社きしかわ畜産</t>
         </is>
       </c>
-      <c r="D69" s="9" t="inlineStr">
-        <is>
-          <t>北海道名寄市</t>
-        </is>
-      </c>
-      <c r="E69" s="9" t="inlineStr">
-        <is>
-          <t>01654-2-2555</t>
+      <c r="C69" s="14" t="inlineStr"/>
+      <c r="D69" s="18" t="inlineStr">
+        <is>
+          <t>北海道名寄市字瑞穂37番地1 (〒096-0077)</t>
+        </is>
+      </c>
+      <c r="E69" s="18" t="inlineStr">
+        <is>
+          <t>01654-3-5210</t>
         </is>
       </c>
       <c r="F69" s="9" t="inlineStr">
@@ -12991,19 +13002,24 @@
           <t>道北</t>
         </is>
       </c>
-      <c r="B70" s="9" t="inlineStr">
-        <is>
-          <t>株式会社大雪牧場</t>
-        </is>
-      </c>
-      <c r="D70" s="9" t="inlineStr">
-        <is>
-          <t>北海道上川郡上川町</t>
-        </is>
-      </c>
-      <c r="E70" s="9" t="inlineStr">
-        <is>
-          <t>不明</t>
+      <c r="B70" s="18" t="inlineStr">
+        <is>
+          <t>農事組合法人 大雪牧場</t>
+        </is>
+      </c>
+      <c r="C70" s="12" t="inlineStr">
+        <is>
+          <t>https://taisetsu-farm325.com/</t>
+        </is>
+      </c>
+      <c r="D70" s="18" t="inlineStr">
+        <is>
+          <t>北海道上川郡上川町字白川325</t>
+        </is>
+      </c>
+      <c r="E70" s="18" t="inlineStr">
+        <is>
+          <t>01658-2-3881</t>
         </is>
       </c>
       <c r="F70" s="9" t="inlineStr">
@@ -14071,18 +14087,21 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C52" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C53" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C55" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C87" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C88" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C89" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C90" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C92" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C95" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C96" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C97" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C98" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C99" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C101" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C102" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C56" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C57" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C70" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C87" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C88" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C89" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C90" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C92" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C95" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C96" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C97" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C98" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C99" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C101" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C102" r:id="rId21"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/output/企業リスト_作業中.xlsx
+++ b/output/企業リスト_作業中.xlsx
@@ -11813,19 +11813,24 @@
           <t>道北</t>
         </is>
       </c>
-      <c r="B58" s="9" t="inlineStr">
-        <is>
-          <t>旭川市営牧場</t>
-        </is>
-      </c>
-      <c r="D58" s="9" t="inlineStr">
-        <is>
-          <t>北海道旭川市</t>
-        </is>
-      </c>
-      <c r="E58" s="9" t="inlineStr">
-        <is>
-          <t>0166-25-7427</t>
+      <c r="B58" s="18" t="inlineStr">
+        <is>
+          <t>旭川市営牧場 (嵐山牧場)</t>
+        </is>
+      </c>
+      <c r="C58" s="12" t="inlineStr">
+        <is>
+          <t>https://www.city.asahikawa.hokkaido.jp/500/501/504/p005231.html</t>
+        </is>
+      </c>
+      <c r="D58" s="18" t="inlineStr">
+        <is>
+          <t>北海道旭川市江丹別町中央</t>
+        </is>
+      </c>
+      <c r="E58" s="18" t="inlineStr">
+        <is>
+          <t>0166-73-2451 (現地) / 0166-73-2036 (指定管理者:江丹別産業開発) / 0166-25-7470 (市農政部)</t>
         </is>
       </c>
       <c r="F58" s="9" t="inlineStr">
@@ -11912,19 +11917,20 @@
           <t>道北</t>
         </is>
       </c>
-      <c r="B59" s="9" t="inlineStr">
+      <c r="B59" s="18" t="inlineStr">
         <is>
           <t>士別市営天塩川牧場</t>
         </is>
       </c>
-      <c r="D59" s="9" t="inlineStr">
-        <is>
-          <t>北海道士別市</t>
-        </is>
-      </c>
-      <c r="E59" s="9" t="inlineStr">
-        <is>
-          <t>0165-23-3121</t>
+      <c r="C59" s="14" t="inlineStr"/>
+      <c r="D59" s="18" t="inlineStr">
+        <is>
+          <t>北海道士別市 ※詳細要確認、士別市農業振興課が窓口</t>
+        </is>
+      </c>
+      <c r="E59" s="18" t="inlineStr">
+        <is>
+          <t>0165-26-7030 (士別市農業振興課)</t>
         </is>
       </c>
       <c r="F59" s="9" t="inlineStr">
@@ -12011,19 +12017,20 @@
           <t>道北</t>
         </is>
       </c>
-      <c r="B60" s="9" t="inlineStr">
-        <is>
-          <t>豊富町営牧場</t>
-        </is>
-      </c>
-      <c r="D60" s="9" t="inlineStr">
-        <is>
-          <t>北海道天塩郡豊富町</t>
-        </is>
-      </c>
-      <c r="E60" s="9" t="inlineStr">
-        <is>
-          <t>0162-82-1001</t>
+      <c r="B60" s="18" t="inlineStr">
+        <is>
+          <t>豊富町大規模草地育成牧場 (町営牧場)</t>
+        </is>
+      </c>
+      <c r="C60" s="14" t="inlineStr"/>
+      <c r="D60" s="18" t="inlineStr">
+        <is>
+          <t>北海道天塩郡豊富町上福永</t>
+        </is>
+      </c>
+      <c r="E60" s="18" t="inlineStr">
+        <is>
+          <t>0162-82-2781</t>
         </is>
       </c>
       <c r="F60" s="9" t="inlineStr">
@@ -12110,19 +12117,20 @@
           <t>道北</t>
         </is>
       </c>
-      <c r="B61" s="9" t="inlineStr">
+      <c r="B61" s="18" t="inlineStr">
         <is>
           <t>猿払村営牧場</t>
         </is>
       </c>
-      <c r="D61" s="9" t="inlineStr">
-        <is>
-          <t>北海道宗谷郡猿払村</t>
-        </is>
-      </c>
-      <c r="E61" s="9" t="inlineStr">
-        <is>
-          <t>01635-2-3131</t>
+      <c r="C61" s="14" t="inlineStr"/>
+      <c r="D61" s="18" t="inlineStr">
+        <is>
+          <t>北海道宗谷郡猿払村 (国道238号沿い)</t>
+        </is>
+      </c>
+      <c r="E61" s="18" t="inlineStr">
+        <is>
+          <t>01635-2-3134 (猿払村産業課)</t>
         </is>
       </c>
       <c r="F61" s="9" t="inlineStr">
@@ -12209,19 +12217,20 @@
           <t>道北</t>
         </is>
       </c>
-      <c r="B62" s="9" t="inlineStr">
+      <c r="B62" s="18" t="inlineStr">
         <is>
           <t>名寄市営牧場</t>
         </is>
       </c>
-      <c r="D62" s="9" t="inlineStr">
-        <is>
-          <t>北海道名寄市</t>
-        </is>
-      </c>
-      <c r="E62" s="9" t="inlineStr">
-        <is>
-          <t>01654-3-2111</t>
+      <c r="C62" s="14" t="inlineStr"/>
+      <c r="D62" s="18" t="inlineStr">
+        <is>
+          <t>北海道名寄市 ※施設の存在要確認</t>
+        </is>
+      </c>
+      <c r="E62" s="18" t="inlineStr">
+        <is>
+          <t>01654-3-2111 (名寄市役所代表) ※要確認</t>
         </is>
       </c>
       <c r="F62" s="9" t="inlineStr">
@@ -12308,19 +12317,20 @@
           <t>道北</t>
         </is>
       </c>
-      <c r="B63" s="9" t="inlineStr">
+      <c r="B63" s="18" t="inlineStr">
         <is>
           <t>剣淵町営牧場</t>
         </is>
       </c>
-      <c r="D63" s="9" t="inlineStr">
-        <is>
-          <t>北海道上川郡剣淵町</t>
-        </is>
-      </c>
-      <c r="E63" s="9" t="inlineStr">
-        <is>
-          <t>0165-34-2121</t>
+      <c r="C63" s="14" t="inlineStr"/>
+      <c r="D63" s="18" t="inlineStr">
+        <is>
+          <t>北海道上川郡剣淵町 ※詳細要確認</t>
+        </is>
+      </c>
+      <c r="E63" s="18" t="inlineStr">
+        <is>
+          <t>0165-34-2121 (剣淵町役場代表) ※要確認</t>
         </is>
       </c>
       <c r="F63" s="9" t="inlineStr">
@@ -12407,19 +12417,20 @@
           <t>道北</t>
         </is>
       </c>
-      <c r="B64" s="9" t="inlineStr">
-        <is>
-          <t>天塩町営牧場</t>
-        </is>
-      </c>
-      <c r="D64" s="9" t="inlineStr">
-        <is>
-          <t>北海道天塩郡天塩町</t>
-        </is>
-      </c>
-      <c r="E64" s="9" t="inlineStr">
-        <is>
-          <t>01632-2-1001</t>
+      <c r="B64" s="18" t="inlineStr">
+        <is>
+          <t>天塩町営牧場 / 株式会社天塩町酪農振興公社</t>
+        </is>
+      </c>
+      <c r="C64" s="14" t="inlineStr"/>
+      <c r="D64" s="18" t="inlineStr">
+        <is>
+          <t>北海道天塩郡天塩町新地通6丁目2343 (公社)</t>
+        </is>
+      </c>
+      <c r="E64" s="18" t="inlineStr">
+        <is>
+          <t>01632-2-1001 ※要確認、酪農振興公社経由</t>
         </is>
       </c>
       <c r="F64" s="9" t="inlineStr">
@@ -12506,19 +12517,24 @@
           <t>道北</t>
         </is>
       </c>
-      <c r="B65" s="9" t="inlineStr">
-        <is>
-          <t>幌延町営牧場</t>
-        </is>
-      </c>
-      <c r="D65" s="9" t="inlineStr">
-        <is>
-          <t>北海道天塩郡幌延町</t>
-        </is>
-      </c>
-      <c r="E65" s="9" t="inlineStr">
-        <is>
-          <t>01632-5-1111</t>
+      <c r="B65" s="18" t="inlineStr">
+        <is>
+          <t>幌延町営牧場 (ほろのべトナカイ観光牧場)</t>
+        </is>
+      </c>
+      <c r="C65" s="12" t="inlineStr">
+        <is>
+          <t>http://www.tonakai-farm.com/</t>
+        </is>
+      </c>
+      <c r="D65" s="18" t="inlineStr">
+        <is>
+          <t>北海道天塩郡幌延町字北進398番地1</t>
+        </is>
+      </c>
+      <c r="E65" s="18" t="inlineStr">
+        <is>
+          <t>01632-5-1115 (役場産業建設課) / 01632-5-2050 (管理棟)</t>
         </is>
       </c>
       <c r="F65" s="9" t="inlineStr">
@@ -12605,19 +12621,20 @@
           <t>道北</t>
         </is>
       </c>
-      <c r="B66" s="9" t="inlineStr">
+      <c r="B66" s="18" t="inlineStr">
         <is>
           <t>上川町営牧場</t>
         </is>
       </c>
-      <c r="D66" s="9" t="inlineStr">
-        <is>
-          <t>北海道上川郡上川町</t>
-        </is>
-      </c>
-      <c r="E66" s="9" t="inlineStr">
-        <is>
-          <t>01658-2-4051</t>
+      <c r="C66" s="14" t="inlineStr"/>
+      <c r="D66" s="18" t="inlineStr">
+        <is>
+          <t>北海道上川郡上川町 ※詳細要確認</t>
+        </is>
+      </c>
+      <c r="E66" s="18" t="inlineStr">
+        <is>
+          <t>01658-2-4051 ※要確認、町役場経由</t>
         </is>
       </c>
       <c r="F66" s="9" t="inlineStr">
@@ -12704,19 +12721,20 @@
           <t>道北</t>
         </is>
       </c>
-      <c r="B67" s="9" t="inlineStr">
+      <c r="B67" s="18" t="inlineStr">
         <is>
           <t>鷹栖町営牧場</t>
         </is>
       </c>
-      <c r="D67" s="9" t="inlineStr">
-        <is>
-          <t>北海道上川郡鷹栖町</t>
-        </is>
-      </c>
-      <c r="E67" s="9" t="inlineStr">
-        <is>
-          <t>0166-87-2111</t>
+      <c r="C67" s="14" t="inlineStr"/>
+      <c r="D67" s="18" t="inlineStr">
+        <is>
+          <t>北海道上川郡鷹栖町 ※詳細要確認</t>
+        </is>
+      </c>
+      <c r="E67" s="18" t="inlineStr">
+        <is>
+          <t>0166-87-2111 (鷹栖町役場代表) ※要確認</t>
         </is>
       </c>
       <c r="F67" s="9" t="inlineStr">
@@ -12803,19 +12821,20 @@
           <t>道北</t>
         </is>
       </c>
-      <c r="B68" s="9" t="inlineStr">
+      <c r="B68" s="18" t="inlineStr">
         <is>
           <t>和寒町営牧場</t>
         </is>
       </c>
-      <c r="D68" s="9" t="inlineStr">
-        <is>
-          <t>北海道上川郡和寒町</t>
-        </is>
-      </c>
-      <c r="E68" s="9" t="inlineStr">
-        <is>
-          <t>0165-32-2421</t>
+      <c r="C68" s="14" t="inlineStr"/>
+      <c r="D68" s="18" t="inlineStr">
+        <is>
+          <t>北海道上川郡和寒町 ※詳細要確認</t>
+        </is>
+      </c>
+      <c r="E68" s="18" t="inlineStr">
+        <is>
+          <t>0165-32-2421 (和寒町役場代表) ※要確認</t>
         </is>
       </c>
       <c r="F68" s="9" t="inlineStr">
@@ -14089,19 +14108,21 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C55" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C56" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C57" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C70" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C87" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C88" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C89" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C90" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C92" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C95" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C96" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C97" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C98" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C99" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C101" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C102" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C58" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C65" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C70" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C87" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C88" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C89" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C90" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C92" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C95" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C96" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C97" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C98" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C99" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C101" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C102" r:id="rId23"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/output/企業リスト_作業中.xlsx
+++ b/output/企業リスト_作業中.xlsx
@@ -6228,19 +6228,24 @@
           <t>道央</t>
         </is>
       </c>
-      <c r="B2" s="9" t="inlineStr">
+      <c r="B2" s="18" t="inlineStr">
         <is>
           <t>株式会社Kalm角山</t>
         </is>
       </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>北海道江別市角山206</t>
-        </is>
-      </c>
-      <c r="E2" s="9" t="inlineStr">
-        <is>
-          <t>011-383-2005</t>
+      <c r="C2" s="12" t="inlineStr">
+        <is>
+          <t>https://www.kalm.co.jp/</t>
+        </is>
+      </c>
+      <c r="D2" s="18" t="inlineStr">
+        <is>
+          <t>北海道江別市角山491</t>
+        </is>
+      </c>
+      <c r="E2" s="18" t="inlineStr">
+        <is>
+          <t>011-378-6858</t>
         </is>
       </c>
       <c r="F2" s="9" t="inlineStr">
@@ -6327,17 +6332,22 @@
           <t>道央</t>
         </is>
       </c>
-      <c r="B3" s="9" t="inlineStr">
+      <c r="B3" s="18" t="inlineStr">
         <is>
           <t>株式会社町村農場</t>
         </is>
       </c>
-      <c r="D3" s="9" t="inlineStr">
-        <is>
-          <t>北海道江別市篠津183番地</t>
-        </is>
-      </c>
-      <c r="E3" s="9" t="inlineStr">
+      <c r="C3" s="12" t="inlineStr">
+        <is>
+          <t>http://www.machimura.co.jp/</t>
+        </is>
+      </c>
+      <c r="D3" s="18" t="inlineStr">
+        <is>
+          <t>北海道江別市篠津183番地 (〒067-0055)</t>
+        </is>
+      </c>
+      <c r="E3" s="18" t="inlineStr">
         <is>
           <t>011-382-2155</t>
         </is>
@@ -6426,19 +6436,24 @@
           <t>道央</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B4" s="18" t="inlineStr">
         <is>
           <t>おおやファーム株式会社</t>
         </is>
       </c>
-      <c r="D4" s="9" t="inlineStr">
-        <is>
-          <t>北海道千歳市駒里2297番地</t>
-        </is>
-      </c>
-      <c r="E4" s="9" t="inlineStr">
-        <is>
-          <t>0123-28-1008</t>
+      <c r="C4" s="12" t="inlineStr">
+        <is>
+          <t>https://ooya-farm.com/</t>
+        </is>
+      </c>
+      <c r="D4" s="18" t="inlineStr">
+        <is>
+          <t>北海道千歳市駒里2297 (〒066-0011)</t>
+        </is>
+      </c>
+      <c r="E4" s="18" t="inlineStr">
+        <is>
+          <t>0123-40-6175</t>
         </is>
       </c>
       <c r="F4" s="9" t="inlineStr">
@@ -6822,17 +6837,22 @@
           <t>道央</t>
         </is>
       </c>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="B8" s="18" t="inlineStr">
         <is>
           <t>株式会社北海道酪農公社</t>
         </is>
       </c>
-      <c r="D8" s="9" t="inlineStr">
-        <is>
-          <t>北海道江別市工栄町16番地</t>
-        </is>
-      </c>
-      <c r="E8" s="9" t="inlineStr">
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>https://www.mainichi-milk.co.jp/</t>
+        </is>
+      </c>
+      <c r="D8" s="18" t="inlineStr">
+        <is>
+          <t>北海道江別市工栄町16 (〒067-0051)</t>
+        </is>
+      </c>
+      <c r="E8" s="18" t="inlineStr">
         <is>
           <t>011-384-6930</t>
         </is>
@@ -7020,19 +7040,24 @@
           <t>道央</t>
         </is>
       </c>
-      <c r="B10" s="9" t="inlineStr">
-        <is>
-          <t>株式会社ユートピアアグリカルチャー</t>
-        </is>
-      </c>
-      <c r="D10" s="9" t="inlineStr">
-        <is>
-          <t>北海道札幌市中央区北1条西3丁目3番地</t>
-        </is>
-      </c>
-      <c r="E10" s="9" t="inlineStr">
-        <is>
-          <t>011-374-4286</t>
+      <c r="B10" s="18" t="inlineStr">
+        <is>
+          <t>株式会社ユートピアアグリカルチャー (本店:日高町豊郷916-6)</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>https://www.utopiaagriculture.com/</t>
+        </is>
+      </c>
+      <c r="D10" s="18" t="inlineStr">
+        <is>
+          <t>北海道札幌市中央区北1条西10丁目1-21 ユーネットビル2階 ※札幌事務所</t>
+        </is>
+      </c>
+      <c r="E10" s="18" t="inlineStr">
+        <is>
+          <t>011-590-4195</t>
         </is>
       </c>
       <c r="F10" s="9" t="inlineStr">
@@ -7416,17 +7441,22 @@
           <t>道央</t>
         </is>
       </c>
-      <c r="B14" s="9" t="inlineStr">
+      <c r="B14" s="18" t="inlineStr">
         <is>
           <t>株式会社ホクリヨウ(本社)</t>
         </is>
       </c>
-      <c r="D14" s="9" t="inlineStr">
-        <is>
-          <t>北海道札幌市白石区中央2条3丁目6-15</t>
-        </is>
-      </c>
-      <c r="E14" s="9" t="inlineStr">
+      <c r="C14" s="12" t="inlineStr">
+        <is>
+          <t>https://www.hokuryo.co.jp/</t>
+        </is>
+      </c>
+      <c r="D14" s="18" t="inlineStr">
+        <is>
+          <t>北海道札幌市白石区中央2条3丁目6番15号 (〒003-0012)</t>
+        </is>
+      </c>
+      <c r="E14" s="18" t="inlineStr">
         <is>
           <t>011-812-1131</t>
         </is>
@@ -8604,17 +8634,22 @@
           <t>道央</t>
         </is>
       </c>
-      <c r="B26" s="9" t="inlineStr">
-        <is>
-          <t>アースドリーム角山農場(トンデンファーム)</t>
-        </is>
-      </c>
-      <c r="D26" s="9" t="inlineStr">
-        <is>
-          <t>北海道江別市角山584-1</t>
-        </is>
-      </c>
-      <c r="E26" s="9" t="inlineStr">
+      <c r="B26" s="18" t="inlineStr">
+        <is>
+          <t>アースドリーム角山農場 (トンデンファーム)</t>
+        </is>
+      </c>
+      <c r="C26" s="12" t="inlineStr">
+        <is>
+          <t>https://www.tondenfarm.co.jp/</t>
+        </is>
+      </c>
+      <c r="D26" s="18" t="inlineStr">
+        <is>
+          <t>北海道江別市元野幌584番地1</t>
+        </is>
+      </c>
+      <c r="E26" s="18" t="inlineStr">
         <is>
           <t>011-391-2500</t>
         </is>
@@ -14100,29 +14135,36 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C49" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C50" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C51" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C52" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C53" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C55" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C56" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C57" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C58" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C65" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C70" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C87" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C88" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C89" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C90" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C92" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C95" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C96" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C97" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C98" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C99" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C101" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C102" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C26" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C49" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C50" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C51" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C52" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C53" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C55" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C56" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C57" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C58" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C65" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C70" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C87" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C88" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C89" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C90" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C92" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C95" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C96" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C97" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C98" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C99" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C101" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C102" r:id="rId30"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/output/企業リスト_作業中.xlsx
+++ b/output/企業リスト_作業中.xlsx
@@ -6540,17 +6540,22 @@
           <t>道央</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="18" t="inlineStr">
         <is>
           <t>有限会社浅野農場</t>
         </is>
       </c>
-      <c r="D5" s="9" t="inlineStr">
-        <is>
-          <t>北海道石狩郡当別町字上当別</t>
-        </is>
-      </c>
-      <c r="E5" s="9" t="inlineStr">
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>https://asanofarm.com/</t>
+        </is>
+      </c>
+      <c r="D5" s="18" t="inlineStr">
+        <is>
+          <t>北海道石狩郡当別町字上当別2190番地 (〒061-0207)</t>
+        </is>
+      </c>
+      <c r="E5" s="18" t="inlineStr">
         <is>
           <t>0133-22-4129</t>
         </is>
@@ -6639,19 +6644,24 @@
           <t>道央</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="18" t="inlineStr">
         <is>
           <t>有限会社永光農園</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>https://nagamitsufarm.com/</t>
+        </is>
+      </c>
+      <c r="D6" s="18" t="inlineStr">
         <is>
           <t>北海道札幌市清田区有明216番地</t>
         </is>
       </c>
-      <c r="E6" s="9" t="inlineStr">
-        <is>
-          <t>011-886-6595</t>
+      <c r="E6" s="18" t="inlineStr">
+        <is>
+          <t>011-886-7204</t>
         </is>
       </c>
       <c r="F6" s="9" t="inlineStr">
@@ -6738,19 +6748,24 @@
           <t>道央</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="18" t="inlineStr">
         <is>
           <t>酪農体験むらかみ牧場</t>
         </is>
       </c>
-      <c r="D7" s="9" t="inlineStr">
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>https://murakami-farm.com/</t>
+        </is>
+      </c>
+      <c r="D7" s="18" t="inlineStr">
         <is>
           <t>北海道恵庭市戸磯156番地</t>
         </is>
       </c>
-      <c r="E7" s="9" t="inlineStr">
-        <is>
-          <t>0123-32-5093</t>
+      <c r="E7" s="18" t="inlineStr">
+        <is>
+          <t>080-6061-9966</t>
         </is>
       </c>
       <c r="F7" s="9" t="inlineStr">
@@ -7144,19 +7159,24 @@
           <t>道央</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B11" s="18" t="inlineStr">
         <is>
           <t>有限会社大塚農場</t>
         </is>
       </c>
-      <c r="D11" s="9" t="inlineStr">
-        <is>
-          <t>北海道石狩郡当別町東裏2905</t>
-        </is>
-      </c>
-      <c r="E11" s="9" t="inlineStr">
-        <is>
-          <t>0133-23-2831</t>
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>https://www.oh-farm.co.jp/</t>
+        </is>
+      </c>
+      <c r="D11" s="18" t="inlineStr">
+        <is>
+          <t>北海道石狩郡当別町字東裏3122番地</t>
+        </is>
+      </c>
+      <c r="E11" s="18" t="inlineStr">
+        <is>
+          <t>※公式サイト経由 / 0133-23-2831 ※要確認</t>
         </is>
       </c>
       <c r="F11" s="9" t="inlineStr">
@@ -7243,17 +7263,22 @@
           <t>道央</t>
         </is>
       </c>
-      <c r="B12" s="9" t="inlineStr">
+      <c r="B12" s="18" t="inlineStr">
         <is>
           <t>有限会社山中畜産</t>
         </is>
       </c>
-      <c r="D12" s="9" t="inlineStr">
-        <is>
-          <t>北海道夕張郡長沼町西2線北1番地</t>
-        </is>
-      </c>
-      <c r="E12" s="9" t="inlineStr">
+      <c r="C12" s="12" t="inlineStr">
+        <is>
+          <t>http://www.yamanaka-pork.com/</t>
+        </is>
+      </c>
+      <c r="D12" s="18" t="inlineStr">
+        <is>
+          <t>北海道夕張郡長沼町西2線北1番地 (〒069-1318)</t>
+        </is>
+      </c>
+      <c r="E12" s="18" t="inlineStr">
         <is>
           <t>0123-88-2146</t>
         </is>
@@ -7342,17 +7367,22 @@
           <t>道央</t>
         </is>
       </c>
-      <c r="B13" s="9" t="inlineStr">
+      <c r="B13" s="18" t="inlineStr">
         <is>
           <t>有限会社福屋牧場</t>
         </is>
       </c>
-      <c r="D13" s="9" t="inlineStr">
-        <is>
-          <t>北海道恵庭市上山口653-4</t>
-        </is>
-      </c>
-      <c r="E13" s="9" t="inlineStr">
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>https://www.elmlane.co.jp/</t>
+        </is>
+      </c>
+      <c r="D13" s="18" t="inlineStr">
+        <is>
+          <t>北海道恵庭市上山口653-4 (〒061-1404)</t>
+        </is>
+      </c>
+      <c r="E13" s="18" t="inlineStr">
         <is>
           <t>0123-32-2157</t>
         </is>
@@ -14138,33 +14168,39 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C26" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C49" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C50" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C51" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C52" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C53" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C55" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C56" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C57" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C58" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C65" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C70" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C87" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C88" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C89" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C90" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C92" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C95" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C96" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C97" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C98" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C99" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C101" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C102" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C26" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C49" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C50" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C51" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C52" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C53" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C55" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C56" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C57" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C58" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C65" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C70" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C87" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C88" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C89" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C90" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C92" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C95" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C96" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C97" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C98" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C99" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C101" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C102" r:id="rId36"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/output/企業リスト_作業中.xlsx
+++ b/output/企業リスト_作業中.xlsx
@@ -6956,19 +6956,24 @@
           <t>道央</t>
         </is>
       </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="B9" s="18" t="inlineStr">
         <is>
           <t>株式会社太田ファーム</t>
         </is>
       </c>
-      <c r="D9" s="9" t="inlineStr">
-        <is>
-          <t>北海道江別市角山189</t>
-        </is>
-      </c>
-      <c r="E9" s="9" t="inlineStr">
-        <is>
-          <t>011-382-5410</t>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>https://ohtafarm-tamago.com/</t>
+        </is>
+      </c>
+      <c r="D9" s="18" t="inlineStr">
+        <is>
+          <t>北海道江別市角山189 (〒067-0052)</t>
+        </is>
+      </c>
+      <c r="E9" s="18" t="inlineStr">
+        <is>
+          <t>011-383-8245</t>
         </is>
       </c>
       <c r="F9" s="9" t="inlineStr">
@@ -7575,17 +7580,22 @@
           <t>道央</t>
         </is>
       </c>
-      <c r="B15" s="9" t="inlineStr">
+      <c r="B15" s="18" t="inlineStr">
         <is>
           <t>株式会社ホクリヨウ 千歳GP</t>
         </is>
       </c>
-      <c r="D15" s="9" t="inlineStr">
-        <is>
-          <t>北海道千歳市駒里2208</t>
-        </is>
-      </c>
-      <c r="E15" s="9" t="inlineStr">
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>https://www.hokuryo.co.jp/</t>
+        </is>
+      </c>
+      <c r="D15" s="18" t="inlineStr">
+        <is>
+          <t>北海道千歳市駒里2208 (〒066-0011)</t>
+        </is>
+      </c>
+      <c r="E15" s="18" t="inlineStr">
         <is>
           <t>0123-40-7575</t>
         </is>
@@ -7674,17 +7684,22 @@
           <t>道央</t>
         </is>
       </c>
-      <c r="B16" s="9" t="inlineStr">
+      <c r="B16" s="18" t="inlineStr">
         <is>
           <t>ホクレンくみあいファーム株式会社 恵庭農場</t>
         </is>
       </c>
-      <c r="D16" s="9" t="inlineStr">
+      <c r="C16" s="12" t="inlineStr">
+        <is>
+          <t>http://kumiai-farm.co.jp/</t>
+        </is>
+      </c>
+      <c r="D16" s="18" t="inlineStr">
         <is>
           <t>北海道恵庭市北島27-1</t>
         </is>
       </c>
-      <c r="E16" s="9" t="inlineStr">
+      <c r="E16" s="18" t="inlineStr">
         <is>
           <t>0123-37-2231</t>
         </is>
@@ -7773,17 +7788,22 @@
           <t>道央</t>
         </is>
       </c>
-      <c r="B17" s="9" t="inlineStr">
+      <c r="B17" s="18" t="inlineStr">
         <is>
           <t>有限会社小林牧場</t>
         </is>
       </c>
-      <c r="D17" s="9" t="inlineStr">
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>https://kobayashibokujo.com/</t>
+        </is>
+      </c>
+      <c r="D17" s="18" t="inlineStr">
         <is>
           <t>北海道江別市西野幌668番地</t>
         </is>
       </c>
-      <c r="E17" s="9" t="inlineStr">
+      <c r="E17" s="18" t="inlineStr">
         <is>
           <t>011-375-1115</t>
         </is>
@@ -7872,17 +7892,22 @@
           <t>道央</t>
         </is>
       </c>
-      <c r="B18" s="9" t="inlineStr">
+      <c r="B18" s="18" t="inlineStr">
         <is>
           <t>有限会社池端牧場</t>
         </is>
       </c>
-      <c r="D18" s="9" t="inlineStr">
-        <is>
-          <t>北海道石狩市樽川97-11</t>
-        </is>
-      </c>
-      <c r="E18" s="9" t="inlineStr">
+      <c r="C18" s="12" t="inlineStr">
+        <is>
+          <t>https://ikebata-farm.com/</t>
+        </is>
+      </c>
+      <c r="D18" s="18" t="inlineStr">
+        <is>
+          <t>北海道石狩市樽川97-11 (〒061-3251)</t>
+        </is>
+      </c>
+      <c r="E18" s="18" t="inlineStr">
         <is>
           <t>0133-73-8538</t>
         </is>
@@ -7971,17 +7996,22 @@
           <t>道央</t>
         </is>
       </c>
-      <c r="B19" s="9" t="inlineStr">
-        <is>
-          <t>一般社団法人Agricola(アグリコラ)</t>
-        </is>
-      </c>
-      <c r="D19" s="9" t="inlineStr">
+      <c r="B19" s="18" t="inlineStr">
+        <is>
+          <t>一般社団法人Agricola (ファームアグリコラ)</t>
+        </is>
+      </c>
+      <c r="C19" s="12" t="inlineStr">
+        <is>
+          <t>https://www.agricola.jp/</t>
+        </is>
+      </c>
+      <c r="D19" s="18" t="inlineStr">
         <is>
           <t>北海道石狩郡当別町字金沢1779-17</t>
         </is>
       </c>
-      <c r="E19" s="9" t="inlineStr">
+      <c r="E19" s="18" t="inlineStr">
         <is>
           <t>0133-27-5551</t>
         </is>
@@ -8070,17 +8100,22 @@
           <t>道央</t>
         </is>
       </c>
-      <c r="B20" s="9" t="inlineStr">
+      <c r="B20" s="18" t="inlineStr">
         <is>
           <t>株式会社北海道中央牧場</t>
         </is>
       </c>
-      <c r="D20" s="9" t="inlineStr">
-        <is>
-          <t>北海道北広島市北進町1丁目2-2</t>
-        </is>
-      </c>
-      <c r="E20" s="9" t="inlineStr">
+      <c r="C20" s="12" t="inlineStr">
+        <is>
+          <t>https://hokkaido-chuobokujo.com/</t>
+        </is>
+      </c>
+      <c r="D20" s="18" t="inlineStr">
+        <is>
+          <t>北海道北広島市北進町1丁目2-2 北広島ターミナルビル4階</t>
+        </is>
+      </c>
+      <c r="E20" s="18" t="inlineStr">
         <is>
           <t>011-372-0073</t>
         </is>
@@ -14172,35 +14207,42 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C26" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C49" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C50" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C51" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C52" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C53" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C55" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C56" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C57" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C58" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C65" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C70" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C87" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C88" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C89" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C90" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C92" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C95" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C96" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C97" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C98" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C99" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C101" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C102" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C26" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C49" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C50" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C51" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C52" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C53" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C55" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C56" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C57" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C58" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C65" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C70" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C87" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C88" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C89" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C90" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C92" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C95" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C96" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C97" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C98" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C99" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C101" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C102" r:id="rId43"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/output/企業リスト_作業中.xlsx
+++ b/output/企業リスト_作業中.xlsx
@@ -8204,17 +8204,22 @@
           <t>道央</t>
         </is>
       </c>
-      <c r="B21" s="9" t="inlineStr">
+      <c r="B21" s="18" t="inlineStr">
         <is>
           <t>有限会社長沼ファーム</t>
         </is>
       </c>
-      <c r="D21" s="9" t="inlineStr">
-        <is>
-          <t>北海道夕張郡長沼町東7線北5</t>
-        </is>
-      </c>
-      <c r="E21" s="9" t="inlineStr">
+      <c r="C21" s="12" t="inlineStr">
+        <is>
+          <t>https://www.naganumafarm.jp/</t>
+        </is>
+      </c>
+      <c r="D21" s="18" t="inlineStr">
+        <is>
+          <t>北海道夕張郡長沼町東7線北5 (〒069-1317)</t>
+        </is>
+      </c>
+      <c r="E21" s="18" t="inlineStr">
         <is>
           <t>0123-88-3698</t>
         </is>
@@ -8303,17 +8308,22 @@
           <t>道央</t>
         </is>
       </c>
-      <c r="B22" s="9" t="inlineStr">
-        <is>
-          <t>株式会社 肉の山本(千歳ラム工房)</t>
-        </is>
-      </c>
-      <c r="D22" s="9" t="inlineStr">
-        <is>
-          <t>北海道千歳市流通3丁目2-2</t>
-        </is>
-      </c>
-      <c r="E22" s="9" t="inlineStr">
+      <c r="B22" s="18" t="inlineStr">
+        <is>
+          <t>株式会社肉の山本 (千歳ラム工房)</t>
+        </is>
+      </c>
+      <c r="C22" s="12" t="inlineStr">
+        <is>
+          <t>https://www.29yamamoto.jp/</t>
+        </is>
+      </c>
+      <c r="D22" s="18" t="inlineStr">
+        <is>
+          <t>北海道千歳市流通3丁目2-2 (〒066-0019)</t>
+        </is>
+      </c>
+      <c r="E22" s="18" t="inlineStr">
         <is>
           <t>0123-23-7617</t>
         </is>
@@ -8402,17 +8412,22 @@
           <t>道央</t>
         </is>
       </c>
-      <c r="B23" s="9" t="inlineStr">
+      <c r="B23" s="18" t="inlineStr">
         <is>
           <t>ファームエイジ株式会社</t>
         </is>
       </c>
-      <c r="D23" s="9" t="inlineStr">
+      <c r="C23" s="12" t="inlineStr">
+        <is>
+          <t>https://farmage.co.jp/</t>
+        </is>
+      </c>
+      <c r="D23" s="18" t="inlineStr">
         <is>
           <t>北海道石狩郡当別町字金沢166-8</t>
         </is>
       </c>
-      <c r="E23" s="9" t="inlineStr">
+      <c r="E23" s="18" t="inlineStr">
         <is>
           <t>0133-22-3060</t>
         </is>
@@ -8501,17 +8516,22 @@
           <t>道央</t>
         </is>
       </c>
-      <c r="B24" s="9" t="inlineStr">
+      <c r="B24" s="18" t="inlineStr">
         <is>
           <t>株式会社ぼくはん</t>
         </is>
       </c>
-      <c r="D24" s="9" t="inlineStr">
-        <is>
-          <t>北海道北広島市西の里東3丁目9-13</t>
-        </is>
-      </c>
-      <c r="E24" s="9" t="inlineStr">
+      <c r="C24" s="12" t="inlineStr">
+        <is>
+          <t>https://bokuhan.co.jp/</t>
+        </is>
+      </c>
+      <c r="D24" s="18" t="inlineStr">
+        <is>
+          <t>北海道北広島市西の里東3丁目9-13 (〒061-1105)</t>
+        </is>
+      </c>
+      <c r="E24" s="18" t="inlineStr">
         <is>
           <t>011-802-5801</t>
         </is>
@@ -8600,17 +8620,22 @@
           <t>道央</t>
         </is>
       </c>
-      <c r="B25" s="9" t="inlineStr">
+      <c r="B25" s="18" t="inlineStr">
         <is>
           <t>北海道ホルスタイン農業協同組合</t>
         </is>
       </c>
-      <c r="D25" s="9" t="inlineStr">
+      <c r="C25" s="12" t="inlineStr">
+        <is>
+          <t>https://www.holstein.or.jp/</t>
+        </is>
+      </c>
+      <c r="D25" s="18" t="inlineStr">
         <is>
           <t>北海道札幌市北区北15条西5丁目1-5</t>
         </is>
       </c>
-      <c r="E25" s="9" t="inlineStr">
+      <c r="E25" s="18" t="inlineStr">
         <is>
           <t>011-726-3111</t>
         </is>
@@ -8803,17 +8828,18 @@
           <t>道央</t>
         </is>
       </c>
-      <c r="B27" s="9" t="inlineStr">
-        <is>
-          <t>千歳市営牧場(道央農業振興公社)</t>
-        </is>
-      </c>
-      <c r="D27" s="9" t="inlineStr">
-        <is>
-          <t>北海道千歳市駒里1032番地の1</t>
-        </is>
-      </c>
-      <c r="E27" s="9" t="inlineStr">
+      <c r="B27" s="18" t="inlineStr">
+        <is>
+          <t>千歳市営牧場 (公益財団法人道央農業振興公社)</t>
+        </is>
+      </c>
+      <c r="C27" s="14" t="inlineStr"/>
+      <c r="D27" s="18" t="inlineStr">
+        <is>
+          <t>北海道千歳市駒里1032番地の1 (駒里地区, 220ha)</t>
+        </is>
+      </c>
+      <c r="E27" s="18" t="inlineStr">
         <is>
           <t>0123-23-4170</t>
         </is>
@@ -8902,19 +8928,20 @@
           <t>道央</t>
         </is>
       </c>
-      <c r="B28" s="9" t="inlineStr">
+      <c r="B28" s="18" t="inlineStr">
         <is>
           <t>石狩ひつじ牧場</t>
         </is>
       </c>
-      <c r="D28" s="9" t="inlineStr">
-        <is>
-          <t>北海道石狩市樽川485-1</t>
-        </is>
-      </c>
-      <c r="E28" s="9" t="inlineStr">
-        <is>
-          <t>011-765-1116</t>
+      <c r="C28" s="14" t="inlineStr"/>
+      <c r="D28" s="18" t="inlineStr">
+        <is>
+          <t>北海道石狩市樽川485-1 (〒061-3251)</t>
+        </is>
+      </c>
+      <c r="E28" s="18" t="inlineStr">
+        <is>
+          <t>080-4505-1935 (スタッフ) / 070-6601-1116 (代表)</t>
         </is>
       </c>
       <c r="F28" s="9" t="inlineStr">
@@ -14219,30 +14246,35 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C19" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C26" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C49" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C50" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C51" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C52" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C53" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C55" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C56" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C57" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C58" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C65" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C70" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C87" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C88" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C89" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C90" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C92" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C95" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C96" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C97" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C98" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C99" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C101" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C102" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C49" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C50" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C51" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C52" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C53" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C55" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C56" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C57" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C58" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C65" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C70" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C87" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C88" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C89" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C90" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C92" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C95" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C96" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C97" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C98" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C99" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C101" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C102" r:id="rId48"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/output/企業リスト_作業中.xlsx
+++ b/output/企業リスト_作業中.xlsx
@@ -9028,17 +9028,22 @@
           <t>道央</t>
         </is>
       </c>
-      <c r="B29" s="9" t="inlineStr">
+      <c r="B29" s="18" t="inlineStr">
         <is>
           <t>有限会社大塚ファーム</t>
         </is>
       </c>
-      <c r="D29" s="9" t="inlineStr">
+      <c r="C29" s="12" t="inlineStr">
+        <is>
+          <t>https://otsukafarm.com/</t>
+        </is>
+      </c>
+      <c r="D29" s="18" t="inlineStr">
         <is>
           <t>北海道石狩郡新篠津村第36線南42番地</t>
         </is>
       </c>
-      <c r="E29" s="9" t="inlineStr">
+      <c r="E29" s="18" t="inlineStr">
         <is>
           <t>0126-57-2573</t>
         </is>
@@ -9127,19 +9132,24 @@
           <t>道央</t>
         </is>
       </c>
-      <c r="B30" s="9" t="inlineStr">
-        <is>
-          <t>株式会社JAKE</t>
-        </is>
-      </c>
-      <c r="D30" s="9" t="inlineStr">
+      <c r="B30" s="18" t="inlineStr">
+        <is>
+          <t>株式会社JAKE (ジェイクジャパン)</t>
+        </is>
+      </c>
+      <c r="C30" s="12" t="inlineStr">
+        <is>
+          <t>https://jake-i.com/</t>
+        </is>
+      </c>
+      <c r="D30" s="18" t="inlineStr">
         <is>
           <t>北海道岩見沢市下志文町24-11</t>
         </is>
       </c>
-      <c r="E30" s="9" t="inlineStr">
-        <is>
-          <t>0126-26-3340</t>
+      <c r="E30" s="18" t="inlineStr">
+        <is>
+          <t>0126-26-3340 ※公式サイト確認</t>
         </is>
       </c>
       <c r="F30" s="9" t="inlineStr">
@@ -9622,19 +9632,24 @@
           <t>道南</t>
         </is>
       </c>
-      <c r="B35" s="9" t="inlineStr">
+      <c r="B35" s="18" t="inlineStr">
         <is>
           <t>日本クリーンファーム株式会社 道南事業所</t>
         </is>
       </c>
-      <c r="D35" s="9" t="inlineStr">
-        <is>
-          <t>北海道二海郡八雲町</t>
-        </is>
-      </c>
-      <c r="E35" s="9" t="inlineStr">
-        <is>
-          <t>不明</t>
+      <c r="C35" s="12" t="inlineStr">
+        <is>
+          <t>https://www.nipponcleanfarm.co.jp/</t>
+        </is>
+      </c>
+      <c r="D35" s="18" t="inlineStr">
+        <is>
+          <t>北海道二海郡八雲町字立岩54-1</t>
+        </is>
+      </c>
+      <c r="E35" s="18" t="inlineStr">
+        <is>
+          <t>※要確認 (本社経由)</t>
         </is>
       </c>
       <c r="F35" s="9" t="inlineStr">
@@ -9721,17 +9736,22 @@
           <t>道南</t>
         </is>
       </c>
-      <c r="B36" s="9" t="inlineStr">
+      <c r="B36" s="18" t="inlineStr">
         <is>
           <t>株式会社山邊畜産</t>
         </is>
       </c>
-      <c r="D36" s="9" t="inlineStr">
-        <is>
-          <t>北海道函館市</t>
-        </is>
-      </c>
-      <c r="E36" s="9" t="inlineStr">
+      <c r="C36" s="12" t="inlineStr">
+        <is>
+          <t>https://www.hokkaido-pork.jp/farm/oshima-hiyama/farm_yamabe/</t>
+        </is>
+      </c>
+      <c r="D36" s="18" t="inlineStr">
+        <is>
+          <t>北海道函館市 ※詳細要確認</t>
+        </is>
+      </c>
+      <c r="E36" s="18" t="inlineStr">
         <is>
           <t>0138-58-3715</t>
         </is>
@@ -9820,19 +9840,24 @@
           <t>道南</t>
         </is>
       </c>
-      <c r="B37" s="9" t="inlineStr">
+      <c r="B37" s="18" t="inlineStr">
         <is>
           <t>有限会社サクセス森</t>
         </is>
       </c>
-      <c r="D37" s="9" t="inlineStr">
-        <is>
-          <t>北海道茅部郡森町</t>
-        </is>
-      </c>
-      <c r="E37" s="9" t="inlineStr">
-        <is>
-          <t>不明</t>
+      <c r="C37" s="12" t="inlineStr">
+        <is>
+          <t>https://www.hokkaido-pork.jp/farm/oshima-hiyama/farm_successmori/</t>
+        </is>
+      </c>
+      <c r="D37" s="18" t="inlineStr">
+        <is>
+          <t>北海道茅部郡森町字石倉町613番地1</t>
+        </is>
+      </c>
+      <c r="E37" s="18" t="inlineStr">
+        <is>
+          <t>01374-7-3939</t>
         </is>
       </c>
       <c r="F37" s="9" t="inlineStr">
@@ -9919,19 +9944,24 @@
           <t>道南</t>
         </is>
       </c>
-      <c r="B38" s="9" t="inlineStr">
-        <is>
-          <t>有限会社道南アグロ</t>
-        </is>
-      </c>
-      <c r="D38" s="9" t="inlineStr">
-        <is>
-          <t>北海道茅部郡森町</t>
-        </is>
-      </c>
-      <c r="E38" s="9" t="inlineStr">
-        <is>
-          <t>不明</t>
+      <c r="B38" s="18" t="inlineStr">
+        <is>
+          <t>有限会社道南アグロ (ひこま豚)</t>
+        </is>
+      </c>
+      <c r="C38" s="12" t="inlineStr">
+        <is>
+          <t>https://www.hikomabuta.com/</t>
+        </is>
+      </c>
+      <c r="D38" s="18" t="inlineStr">
+        <is>
+          <t>北海道茅部郡森町姫川121-45</t>
+        </is>
+      </c>
+      <c r="E38" s="18" t="inlineStr">
+        <is>
+          <t>01374-2-3939</t>
         </is>
       </c>
       <c r="F38" s="9" t="inlineStr">
@@ -10414,17 +10444,22 @@
           <t>道南</t>
         </is>
       </c>
-      <c r="B43" s="9" t="inlineStr">
-        <is>
-          <t>株式会社函館酪農公社</t>
-        </is>
-      </c>
-      <c r="D43" s="9" t="inlineStr">
-        <is>
-          <t>北海道函館市中野町</t>
-        </is>
-      </c>
-      <c r="E43" s="9" t="inlineStr">
+      <c r="B43" s="18" t="inlineStr">
+        <is>
+          <t>株式会社函館酪農公社 (函館牛乳)</t>
+        </is>
+      </c>
+      <c r="C43" s="12" t="inlineStr">
+        <is>
+          <t>https://www.e-milk.co.jp/</t>
+        </is>
+      </c>
+      <c r="D43" s="18" t="inlineStr">
+        <is>
+          <t>北海道函館市中野町118番地 (〒042-0912)</t>
+        </is>
+      </c>
+      <c r="E43" s="18" t="inlineStr">
         <is>
           <t>0138-58-4460</t>
         </is>
@@ -14252,29 +14287,36 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C24" r:id="rId23"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C25" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C26" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C49" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C50" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C51" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C52" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C53" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C55" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C56" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C57" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C58" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C65" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C70" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C87" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C88" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C89" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C90" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C92" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C95" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C96" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C97" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C98" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C99" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C101" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C102" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C29" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C30" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C35" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C36" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C37" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C38" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C43" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C49" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C50" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C51" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C52" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C53" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C55" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C56" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C57" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C58" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C65" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C70" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C87" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C88" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C89" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C90" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C92" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C95" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C96" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C97" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C98" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C99" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C101" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C102" r:id="rId55"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/output/企業リスト_作業中.xlsx
+++ b/output/企業リスト_作業中.xlsx
@@ -10048,19 +10048,24 @@
           <t>道南</t>
         </is>
       </c>
-      <c r="B39" s="9" t="inlineStr">
+      <c r="B39" s="18" t="inlineStr">
         <is>
           <t>有限会社西村畜産</t>
         </is>
       </c>
-      <c r="D39" s="9" t="inlineStr">
-        <is>
-          <t>北海道茅部郡森町</t>
-        </is>
-      </c>
-      <c r="E39" s="9" t="inlineStr">
-        <is>
-          <t>不明</t>
+      <c r="C39" s="12" t="inlineStr">
+        <is>
+          <t>https://www.hokkaido-pork.jp/farm/oshima-hiyama/farm_nishimura/</t>
+        </is>
+      </c>
+      <c r="D39" s="18" t="inlineStr">
+        <is>
+          <t>北海道茅部郡森町 ※詳細要確認</t>
+        </is>
+      </c>
+      <c r="E39" s="18" t="inlineStr">
+        <is>
+          <t>※要確認 (北海道養豚生産者協会経由)</t>
         </is>
       </c>
       <c r="F39" s="9" t="inlineStr">
@@ -10147,19 +10152,24 @@
           <t>道南</t>
         </is>
       </c>
-      <c r="B40" s="9" t="inlineStr">
-        <is>
-          <t>有限会社高橋畜産</t>
-        </is>
-      </c>
-      <c r="D40" s="9" t="inlineStr">
-        <is>
-          <t>北海道久遠郡せたな町</t>
-        </is>
-      </c>
-      <c r="E40" s="9" t="inlineStr">
-        <is>
-          <t>不明</t>
+      <c r="B40" s="18" t="inlineStr">
+        <is>
+          <t>有限会社高橋畜産 (若松ポークマン)</t>
+        </is>
+      </c>
+      <c r="C40" s="12" t="inlineStr">
+        <is>
+          <t>https://porkman.jp/</t>
+        </is>
+      </c>
+      <c r="D40" s="18" t="inlineStr">
+        <is>
+          <t>北海道久遠郡せたな町北檜山区松岡343 (〒049-4511)</t>
+        </is>
+      </c>
+      <c r="E40" s="18" t="inlineStr">
+        <is>
+          <t>0137-84-6325</t>
         </is>
       </c>
       <c r="F40" s="9" t="inlineStr">
@@ -10246,19 +10256,20 @@
           <t>道南</t>
         </is>
       </c>
-      <c r="B41" s="9" t="inlineStr">
+      <c r="B41" s="18" t="inlineStr">
         <is>
           <t>有限会社森農場</t>
         </is>
       </c>
-      <c r="D41" s="9" t="inlineStr">
-        <is>
-          <t>北海道檜山郡上ノ国町</t>
-        </is>
-      </c>
-      <c r="E41" s="9" t="inlineStr">
-        <is>
-          <t>不明</t>
+      <c r="C41" s="14" t="inlineStr"/>
+      <c r="D41" s="18" t="inlineStr">
+        <is>
+          <t>北海道檜山郡上ノ国町 ※詳細要確認</t>
+        </is>
+      </c>
+      <c r="E41" s="18" t="inlineStr">
+        <is>
+          <t>※要確認 (上ノ国町役場 0139-55-2311 経由)</t>
         </is>
       </c>
       <c r="F41" s="9" t="inlineStr">
@@ -10345,19 +10356,24 @@
           <t>道南</t>
         </is>
       </c>
-      <c r="B42" s="9" t="inlineStr">
-        <is>
-          <t>株式会社ひこま豚</t>
-        </is>
-      </c>
-      <c r="D42" s="9" t="inlineStr">
-        <is>
-          <t>北海道茅部郡森町</t>
-        </is>
-      </c>
-      <c r="E42" s="9" t="inlineStr">
-        <is>
-          <t>不明</t>
+      <c r="B42" s="18" t="inlineStr">
+        <is>
+          <t>株式会社ひこま豚 / 道南アグロ</t>
+        </is>
+      </c>
+      <c r="C42" s="12" t="inlineStr">
+        <is>
+          <t>https://www.hikomabuta.com/</t>
+        </is>
+      </c>
+      <c r="D42" s="18" t="inlineStr">
+        <is>
+          <t>北海道茅部郡森町 ※Row 38 道南アグロのブランド・統合検討</t>
+        </is>
+      </c>
+      <c r="E42" s="18" t="inlineStr">
+        <is>
+          <t>01374-2-3939 ※Row 38と同一実体</t>
         </is>
       </c>
       <c r="F42" s="9" t="inlineStr">
@@ -10548,19 +10564,20 @@
           <t>道南</t>
         </is>
       </c>
-      <c r="B44" s="9" t="inlineStr">
+      <c r="B44" s="18" t="inlineStr">
         <is>
           <t>はこだてSinアグリファーム</t>
         </is>
       </c>
-      <c r="D44" s="9" t="inlineStr">
-        <is>
-          <t>北海道函館市</t>
-        </is>
-      </c>
-      <c r="E44" s="9" t="inlineStr">
-        <is>
-          <t>不明</t>
+      <c r="C44" s="14" t="inlineStr"/>
+      <c r="D44" s="18" t="inlineStr">
+        <is>
+          <t>北海道函館市 ※詳細要確認</t>
+        </is>
+      </c>
+      <c r="E44" s="18" t="inlineStr">
+        <is>
+          <t>※要確認</t>
         </is>
       </c>
       <c r="F44" s="9" t="inlineStr">
@@ -10647,19 +10664,24 @@
           <t>道南</t>
         </is>
       </c>
-      <c r="B45" s="9" t="inlineStr">
-        <is>
-          <t>小澤牧場</t>
-        </is>
-      </c>
-      <c r="D45" s="9" t="inlineStr">
-        <is>
-          <t>北海道七飯町</t>
-        </is>
-      </c>
-      <c r="E45" s="9" t="inlineStr">
-        <is>
-          <t>不明</t>
+      <c r="B45" s="18" t="inlineStr">
+        <is>
+          <t>小澤牧場 (大沼肉牛ファーム)</t>
+        </is>
+      </c>
+      <c r="C45" s="12" t="inlineStr">
+        <is>
+          <t>https://www.onuma-nikugyu-farm.com/</t>
+        </is>
+      </c>
+      <c r="D45" s="18" t="inlineStr">
+        <is>
+          <t>北海道亀田郡七飯町上軍川619-4 (〒041-1353)</t>
+        </is>
+      </c>
+      <c r="E45" s="18" t="inlineStr">
+        <is>
+          <t>0138-67-3600 / 0138-67-2127</t>
         </is>
       </c>
       <c r="F45" s="9" t="inlineStr">
@@ -10746,19 +10768,20 @@
           <t>道南</t>
         </is>
       </c>
-      <c r="B46" s="9" t="inlineStr">
-        <is>
-          <t>鈴木牧場</t>
-        </is>
-      </c>
-      <c r="D46" s="9" t="inlineStr">
-        <is>
-          <t>北海道北斗市</t>
-        </is>
-      </c>
-      <c r="E46" s="9" t="inlineStr">
-        <is>
-          <t>不明</t>
+      <c r="B46" s="18" t="inlineStr">
+        <is>
+          <t>鈴木牧場 (北斗市)</t>
+        </is>
+      </c>
+      <c r="C46" s="14" t="inlineStr"/>
+      <c r="D46" s="18" t="inlineStr">
+        <is>
+          <t>北海道北斗市向野3丁目1-21</t>
+        </is>
+      </c>
+      <c r="E46" s="18" t="inlineStr">
+        <is>
+          <t>0138-77-8241</t>
         </is>
       </c>
       <c r="F46" s="9" t="inlineStr">
@@ -10845,19 +10868,20 @@
           <t>道南</t>
         </is>
       </c>
-      <c r="B47" s="9" t="inlineStr">
-        <is>
-          <t>有限会社八雲ファーム</t>
-        </is>
-      </c>
-      <c r="D47" s="9" t="inlineStr">
-        <is>
-          <t>北海道二海郡八雲町</t>
-        </is>
-      </c>
-      <c r="E47" s="9" t="inlineStr">
-        <is>
-          <t>不明</t>
+      <c r="B47" s="18" t="inlineStr">
+        <is>
+          <t>※有限会社八雲ファーム → 日本クリーンファーム(株)へ社名変更 (Row 35と統合)</t>
+        </is>
+      </c>
+      <c r="C47" s="14" t="inlineStr"/>
+      <c r="D47" s="18" t="inlineStr">
+        <is>
+          <t>※2023年4月1日に「日本クリーンファーム(株)」に社名変更。Row 35参照</t>
+        </is>
+      </c>
+      <c r="E47" s="18" t="inlineStr">
+        <is>
+          <t>※存続: 日本クリーンファーム</t>
         </is>
       </c>
       <c r="F47" s="9" t="inlineStr">
@@ -10944,19 +10968,24 @@
           <t>道南</t>
         </is>
       </c>
-      <c r="B48" s="9" t="inlineStr">
+      <c r="B48" s="18" t="inlineStr">
         <is>
           <t>日本フードパッカー株式会社 道南工場</t>
         </is>
       </c>
-      <c r="D48" s="9" t="inlineStr">
-        <is>
-          <t>北海道</t>
-        </is>
-      </c>
-      <c r="E48" s="9" t="inlineStr">
-        <is>
-          <t>不明</t>
+      <c r="C48" s="12" t="inlineStr">
+        <is>
+          <t>https://www.foodpacker.jp/</t>
+        </is>
+      </c>
+      <c r="D48" s="18" t="inlineStr">
+        <is>
+          <t>北海道二海郡八雲町立岩356 (〒049-3123)</t>
+        </is>
+      </c>
+      <c r="E48" s="18" t="inlineStr">
+        <is>
+          <t>0137-63-4129</t>
         </is>
       </c>
       <c r="F48" s="9" t="inlineStr">
@@ -14293,30 +14322,35 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C36" r:id="rId29"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C37" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C38" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C43" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C49" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C50" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C51" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C52" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C53" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C55" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C56" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C57" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C58" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C65" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C70" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C87" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C88" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C89" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C90" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C92" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C95" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C96" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C97" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C98" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C99" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C101" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C102" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C39" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C40" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C42" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C43" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C45" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C48" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C49" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C50" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C51" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C52" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C53" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C55" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C56" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C57" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C58" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C65" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C70" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C87" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C88" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C89" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C90" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C92" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C95" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C96" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C97" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C98" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C99" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C101" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C102" r:id="rId60"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
